--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -12,7 +12,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CO$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -21,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -37,6 +38,11 @@
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,11 +73,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -135,61 +136,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,6 +198,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -272,6 +297,108 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO10" headerRowCount="1">
+  <autoFilter ref="A1:CO10"/>
+  <tableColumns count="93">
+    <tableColumn id="1" name="pick_id"/>
+    <tableColumn id="2" name="created_at_utc"/>
+    <tableColumn id="3" name="event_start_utc"/>
+    <tableColumn id="4" name="event_id"/>
+    <tableColumn id="5" name="league"/>
+    <tableColumn id="6" name="away_team"/>
+    <tableColumn id="7" name="home_team"/>
+    <tableColumn id="8" name="market_type"/>
+    <tableColumn id="9" name="selection"/>
+    <tableColumn id="10" name="line"/>
+    <tableColumn id="11" name="sportsbook"/>
+    <tableColumn id="12" name="american_odds"/>
+    <tableColumn id="13" name="decimal_odds"/>
+    <tableColumn id="14" name="market_implied_probability"/>
+    <tableColumn id="15" name="model_probability"/>
+    <tableColumn id="16" name="model_uncertainty"/>
+    <tableColumn id="17" name="edge"/>
+    <tableColumn id="18" name="confidence_score"/>
+    <tableColumn id="19" name="units"/>
+    <tableColumn id="20" name="model_version"/>
+    <tableColumn id="21" name="status"/>
+    <tableColumn id="22" name="result"/>
+    <tableColumn id="23" name="away_score"/>
+    <tableColumn id="24" name="home_score"/>
+    <tableColumn id="25" name="closing_line"/>
+    <tableColumn id="26" name="closing_american_odds"/>
+    <tableColumn id="27" name="closing_implied_probability"/>
+    <tableColumn id="28" name="probability_clv"/>
+    <tableColumn id="29" name="pnl_units"/>
+    <tableColumn id="30" name="settled_at_utc"/>
+    <tableColumn id="31" name="rationale"/>
+    <tableColumn id="32" name="risks"/>
+    <tableColumn id="33" name="review_status"/>
+    <tableColumn id="34" name="loss_classification"/>
+    <tableColumn id="35" name="loss_cause"/>
+    <tableColumn id="36" name="corrective_action"/>
+    <tableColumn id="37" name="call_type"/>
+    <tableColumn id="38" name="ledger_schema_version"/>
+    <tableColumn id="39" name="record_type"/>
+    <tableColumn id="40" name="decision"/>
+    <tableColumn id="41" name="reason_code"/>
+    <tableColumn id="42" name="canonical_away_team_id"/>
+    <tableColumn id="43" name="canonical_away_team_name"/>
+    <tableColumn id="44" name="original_away_team"/>
+    <tableColumn id="45" name="canonical_home_team_id"/>
+    <tableColumn id="46" name="canonical_home_team_name"/>
+    <tableColumn id="47" name="original_home_team"/>
+    <tableColumn id="48" name="banned_team_id"/>
+    <tableColumn id="49" name="banned_team_name"/>
+    <tableColumn id="50" name="model_origin"/>
+    <tableColumn id="51" name="baseline_identifier"/>
+    <tableColumn id="52" name="model_state_at_decision"/>
+    <tableColumn id="53" name="model_artifact_hash"/>
+    <tableColumn id="54" name="calibration_method"/>
+    <tableColumn id="55" name="calibration_version"/>
+    <tableColumn id="56" name="calibration_artifact_hash"/>
+    <tableColumn id="57" name="feature_schema_version"/>
+    <tableColumn id="58" name="entity_map_version"/>
+    <tableColumn id="59" name="code_revision"/>
+    <tableColumn id="60" name="observed_at_utc"/>
+    <tableColumn id="61" name="correlation_tags"/>
+    <tableColumn id="62" name="decision_line"/>
+    <tableColumn id="63" name="decision_american_odds"/>
+    <tableColumn id="64" name="decision_decimal_odds"/>
+    <tableColumn id="65" name="decision_raw_implied_probability"/>
+    <tableColumn id="66" name="decision_no_vig_probability"/>
+    <tableColumn id="67" name="decision_consensus_probability"/>
+    <tableColumn id="68" name="decision_consensus_line"/>
+    <tableColumn id="69" name="closing_decimal_odds"/>
+    <tableColumn id="70" name="closing_raw_implied_probability"/>
+    <tableColumn id="71" name="closing_no_vig_probability"/>
+    <tableColumn id="72" name="closing_consensus_probability"/>
+    <tableColumn id="73" name="closing_consensus_line"/>
+    <tableColumn id="74" name="legacy_units"/>
+    <tableColumn id="75" name="void_reason"/>
+    <tableColumn id="76" name="research_score_units"/>
+    <tableColumn id="77" name="research_pnl_units"/>
+    <tableColumn id="78" name="research_scored_at_utc"/>
+    <tableColumn id="79" name="research_scoring_note"/>
+    <tableColumn id="80" name="migrated_from_version"/>
+    <tableColumn id="81" name="elo_probability"/>
+    <tableColumn id="82" name="trend_gap"/>
+    <tableColumn id="83" name="park_factor"/>
+    <tableColumn id="84" name="weather_factor"/>
+    <tableColumn id="85" name="pitcher_era_gap"/>
+    <tableColumn id="86" name="probable_starter_era_gap"/>
+    <tableColumn id="87" name="unavailable_features"/>
+    <tableColumn id="88" name="defensive_trend_gap"/>
+    <tableColumn id="89" name="neutral_elo_rating_difference"/>
+    <tableColumn id="90" name="rest_disparity"/>
+    <tableColumn id="91" name="back_to_back_gap"/>
+    <tableColumn id="92" name="games_last_7_gap"/>
+    <tableColumn id="93" name="schedule_missingness"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -625,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$2)</f>
+        <f>COUNTA('Picks'!$A$2:$A$10)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$10,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -665,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$2,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$10,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")/(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")/(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$2)/SUM('Picks'!$BX$2:$BX$2),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$10)/SUM('Picks'!$BX$2:$BX$10),0)</f>
         <v/>
       </c>
     </row>
@@ -705,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$2)</f>
+        <f>SUM('Picks'!$BY$2:$BY$10)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$2,"&lt;&gt;",'Picks'!$AB$2:$AB$2),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$10,"&lt;&gt;",'Picks'!$AB$2:$AB$10),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$2,'Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$10,'Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -772,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -788,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -803,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -819,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -834,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -850,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -883,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO1"/>
+  <dimension ref="A1:CO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1448,9 +1575,2444 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>5410b19790cb4158</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:32:13.323625Z</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>60760</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="n"/>
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M2" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N2" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O2" s="28" t="n">
+        <v>0.519337</v>
+      </c>
+      <c r="P2" s="28" t="n"/>
+      <c r="Q2" s="28" t="n">
+        <v>0.109501</v>
+      </c>
+      <c r="R2" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S2" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U2" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="25" t="n"/>
+      <c r="Z2" s="26" t="n"/>
+      <c r="AA2" s="28" t="n"/>
+      <c r="AB2" s="28" t="n"/>
+      <c r="AC2" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:03:46.656501Z</t>
+        </is>
+      </c>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-valorant-beg-hbs-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG2" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH2" s="24" t="n"/>
+      <c r="AI2" s="31" t="n"/>
+      <c r="AJ2" s="31" t="n"/>
+      <c r="AK2" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN2" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO2" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP2" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AQ2" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AR2" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AS2" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="AT2" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="AU2" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="AV2" s="24" t="n"/>
+      <c r="AW2" s="24" t="n"/>
+      <c r="AX2" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY2" s="24" t="n"/>
+      <c r="AZ2" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA2" s="24" t="inlineStr">
+        <is>
+          <t>6cce51743bf5606a4094683b8f88c468e312b6e0f3a4d11913a9997a273d6b86</t>
+        </is>
+      </c>
+      <c r="BB2" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC2" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD2" s="24" t="inlineStr">
+        <is>
+          <t>6cce51743bf5606a4094683b8f88c468e312b6e0f3a4d11913a9997a273d6b86</t>
+        </is>
+      </c>
+      <c r="BE2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG2" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:32:04.945513Z</t>
+        </is>
+      </c>
+      <c r="BI2" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ2" s="25" t="n"/>
+      <c r="BK2" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL2" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM2" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN2" s="28" t="n"/>
+      <c r="BO2" s="28" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
+      <c r="BR2" s="28" t="n"/>
+      <c r="BS2" s="28" t="n"/>
+      <c r="BT2" s="28" t="n"/>
+      <c r="BU2" s="25" t="n"/>
+      <c r="BV2" s="29" t="n"/>
+      <c r="BW2" s="24" t="n"/>
+      <c r="BX2" s="30" t="n"/>
+      <c r="BY2" s="27" t="n"/>
+      <c r="BZ2" s="24" t="n"/>
+      <c r="CA2" s="31" t="n"/>
+      <c r="CB2" s="24" t="n"/>
+      <c r="CC2" s="24" t="n"/>
+      <c r="CD2" s="24" t="n"/>
+      <c r="CE2" s="24" t="n"/>
+      <c r="CF2" s="24" t="n"/>
+      <c r="CG2" s="24" t="n"/>
+      <c r="CH2" s="24" t="n"/>
+      <c r="CI2" s="24" t="n"/>
+      <c r="CJ2" s="24" t="n"/>
+      <c r="CK2" s="24" t="n"/>
+      <c r="CL2" s="24" t="n"/>
+      <c r="CM2" s="24" t="n"/>
+      <c r="CN2" s="24" t="n"/>
+      <c r="CO2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>0aa2021b65f14a53</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:51:39.691788Z</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>61045</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>SaD GC</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>ORA Temper</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L3" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="M3" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N3" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="O3" s="28" t="n">
+        <v>0.5057199999999999</v>
+      </c>
+      <c r="P3" s="28" t="n"/>
+      <c r="Q3" s="28" t="n">
+        <v>0.175687</v>
+      </c>
+      <c r="R3" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S3" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T3" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U3" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W3" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="26" t="n"/>
+      <c r="AA3" s="28" t="n"/>
+      <c r="AB3" s="28" t="n"/>
+      <c r="AC3" s="30" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="AD3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:52:00.762411Z</t>
+        </is>
+      </c>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-valorant-orat-sga-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG3" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH3" s="24" t="n"/>
+      <c r="AI3" s="31" t="n"/>
+      <c r="AJ3" s="31" t="n"/>
+      <c r="AK3" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN3" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO3" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP3" s="24" t="inlineStr">
+        <is>
+          <t>SaD GC</t>
+        </is>
+      </c>
+      <c r="AQ3" s="24" t="inlineStr">
+        <is>
+          <t>SaD GC</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
+          <t>SaD GC</t>
+        </is>
+      </c>
+      <c r="AS3" s="24" t="inlineStr">
+        <is>
+          <t>ORA Temper</t>
+        </is>
+      </c>
+      <c r="AT3" s="24" t="inlineStr">
+        <is>
+          <t>ORA Temper</t>
+        </is>
+      </c>
+      <c r="AU3" s="24" t="inlineStr">
+        <is>
+          <t>ORA Temper</t>
+        </is>
+      </c>
+      <c r="AV3" s="24" t="n"/>
+      <c r="AW3" s="24" t="n"/>
+      <c r="AX3" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY3" s="24" t="n"/>
+      <c r="AZ3" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA3" s="24" t="inlineStr">
+        <is>
+          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+        </is>
+      </c>
+      <c r="BB3" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC3" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD3" s="24" t="inlineStr">
+        <is>
+          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+        </is>
+      </c>
+      <c r="BE3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG3" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:51:33.586186Z</t>
+        </is>
+      </c>
+      <c r="BI3" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ3" s="25" t="n"/>
+      <c r="BK3" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="BL3" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BM3" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="BN3" s="28" t="n"/>
+      <c r="BO3" s="28" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
+      <c r="BR3" s="28" t="n"/>
+      <c r="BS3" s="28" t="n"/>
+      <c r="BT3" s="28" t="n"/>
+      <c r="BU3" s="25" t="n"/>
+      <c r="BV3" s="29" t="n"/>
+      <c r="BW3" s="24" t="n"/>
+      <c r="BX3" s="30" t="n"/>
+      <c r="BY3" s="27" t="n"/>
+      <c r="BZ3" s="24" t="n"/>
+      <c r="CA3" s="31" t="n"/>
+      <c r="CB3" s="24" t="n"/>
+      <c r="CC3" s="24" t="n"/>
+      <c r="CD3" s="24" t="n"/>
+      <c r="CE3" s="24" t="n"/>
+      <c r="CF3" s="24" t="n"/>
+      <c r="CG3" s="24" t="n"/>
+      <c r="CH3" s="24" t="n"/>
+      <c r="CI3" s="24" t="n"/>
+      <c r="CJ3" s="24" t="n"/>
+      <c r="CK3" s="24" t="n"/>
+      <c r="CL3" s="24" t="n"/>
+      <c r="CM3" s="24" t="n"/>
+      <c r="CN3" s="24" t="n"/>
+      <c r="CO3" s="24" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>54c2f7d359844b66</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:51:39.691788Z</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>61046</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 GC</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I4" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L4" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M4" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O4" s="28" t="n">
+        <v>0.53613</v>
+      </c>
+      <c r="P4" s="28" t="n"/>
+      <c r="Q4" s="28" t="n">
+        <v>0.03613</v>
+      </c>
+      <c r="R4" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="S4" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T4" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U4" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V4" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="26" t="n"/>
+      <c r="AA4" s="28" t="n"/>
+      <c r="AB4" s="28" t="n"/>
+      <c r="AC4" s="30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:57:14.441712Z</t>
+        </is>
+      </c>
+      <c r="AE4" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-valorant-c9gc-spi-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF4" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG4" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH4" s="24" t="n"/>
+      <c r="AI4" s="31" t="n"/>
+      <c r="AJ4" s="31" t="n"/>
+      <c r="AK4" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM4" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN4" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO4" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP4" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="AQ4" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="AR4" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="AS4" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 GC</t>
+        </is>
+      </c>
+      <c r="AT4" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 GC</t>
+        </is>
+      </c>
+      <c r="AU4" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 GC</t>
+        </is>
+      </c>
+      <c r="AV4" s="24" t="n"/>
+      <c r="AW4" s="24" t="n"/>
+      <c r="AX4" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY4" s="24" t="n"/>
+      <c r="AZ4" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA4" s="24" t="inlineStr">
+        <is>
+          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+        </is>
+      </c>
+      <c r="BB4" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC4" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD4" s="24" t="inlineStr">
+        <is>
+          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+        </is>
+      </c>
+      <c r="BE4" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF4" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG4" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:51:34.129373Z</t>
+        </is>
+      </c>
+      <c r="BI4" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ4" s="25" t="n"/>
+      <c r="BK4" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL4" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM4" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN4" s="28" t="n"/>
+      <c r="BO4" s="28" t="n"/>
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n"/>
+      <c r="BR4" s="28" t="n"/>
+      <c r="BS4" s="28" t="n"/>
+      <c r="BT4" s="28" t="n"/>
+      <c r="BU4" s="25" t="n"/>
+      <c r="BV4" s="29" t="n"/>
+      <c r="BW4" s="24" t="n"/>
+      <c r="BX4" s="30" t="n"/>
+      <c r="BY4" s="27" t="n"/>
+      <c r="BZ4" s="24" t="n"/>
+      <c r="CA4" s="31" t="n"/>
+      <c r="CB4" s="24" t="n"/>
+      <c r="CC4" s="24" t="n"/>
+      <c r="CD4" s="24" t="n"/>
+      <c r="CE4" s="24" t="n"/>
+      <c r="CF4" s="24" t="n"/>
+      <c r="CG4" s="24" t="n"/>
+      <c r="CH4" s="24" t="n"/>
+      <c r="CI4" s="24" t="n"/>
+      <c r="CJ4" s="24" t="n"/>
+      <c r="CK4" s="24" t="n"/>
+      <c r="CL4" s="24" t="n"/>
+      <c r="CM4" s="24" t="n"/>
+      <c r="CN4" s="24" t="n"/>
+      <c r="CO4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>2262d180fb3749f8</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:51:39.691788Z</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>61048</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Gold</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L5" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O5" s="28" t="n">
+        <v>0.541059</v>
+      </c>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="28" t="n">
+        <v>0.041059</v>
+      </c>
+      <c r="R5" s="26" t="n">
+        <v>41</v>
+      </c>
+      <c r="S5" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U5" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="26" t="n"/>
+      <c r="AA5" s="28" t="n"/>
+      <c r="AB5" s="28" t="n"/>
+      <c r="AC5" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:57:15.596098Z</t>
+        </is>
+      </c>
+      <c r="AE5" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-valorant-srg-swim-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF5" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG5" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH5" s="24" t="n"/>
+      <c r="AI5" s="31" t="n"/>
+      <c r="AJ5" s="31" t="n"/>
+      <c r="AK5" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN5" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO5" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP5" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AQ5" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AR5" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AS5" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Gold</t>
+        </is>
+      </c>
+      <c r="AT5" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Gold</t>
+        </is>
+      </c>
+      <c r="AU5" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Gold</t>
+        </is>
+      </c>
+      <c r="AV5" s="24" t="n"/>
+      <c r="AW5" s="24" t="n"/>
+      <c r="AX5" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY5" s="24" t="n"/>
+      <c r="AZ5" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA5" s="24" t="inlineStr">
+        <is>
+          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+        </is>
+      </c>
+      <c r="BB5" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC5" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD5" s="24" t="inlineStr">
+        <is>
+          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+        </is>
+      </c>
+      <c r="BE5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG5" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:51:34.644041Z</t>
+        </is>
+      </c>
+      <c r="BI5" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ5" s="25" t="n"/>
+      <c r="BK5" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL5" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM5" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN5" s="28" t="n"/>
+      <c r="BO5" s="28" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
+      <c r="BR5" s="28" t="n"/>
+      <c r="BS5" s="28" t="n"/>
+      <c r="BT5" s="28" t="n"/>
+      <c r="BU5" s="25" t="n"/>
+      <c r="BV5" s="29" t="n"/>
+      <c r="BW5" s="24" t="n"/>
+      <c r="BX5" s="30" t="n"/>
+      <c r="BY5" s="27" t="n"/>
+      <c r="BZ5" s="24" t="n"/>
+      <c r="CA5" s="31" t="n"/>
+      <c r="CB5" s="24" t="n"/>
+      <c r="CC5" s="24" t="n"/>
+      <c r="CD5" s="24" t="n"/>
+      <c r="CE5" s="24" t="n"/>
+      <c r="CF5" s="24" t="n"/>
+      <c r="CG5" s="24" t="n"/>
+      <c r="CH5" s="24" t="n"/>
+      <c r="CI5" s="24" t="n"/>
+      <c r="CJ5" s="24" t="n"/>
+      <c r="CK5" s="24" t="n"/>
+      <c r="CL5" s="24" t="n"/>
+      <c r="CM5" s="24" t="n"/>
+      <c r="CN5" s="24" t="n"/>
+      <c r="CO5" s="24" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>54aad50fb6e84432</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:56:56.096115Z</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>61239</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>Los Chudeles</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N6" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="O6" s="28" t="n">
+        <v>0.557051</v>
+      </c>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="28" t="n">
+        <v>0.247453</v>
+      </c>
+      <c r="R6" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S6" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U6" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="25" t="n"/>
+      <c r="Z6" s="26" t="n"/>
+      <c r="AA6" s="28" t="n"/>
+      <c r="AB6" s="28" t="n"/>
+      <c r="AC6" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:57:16.746309Z</t>
+        </is>
+      </c>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-valorant-efa-lcd-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG6" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH6" s="24" t="n"/>
+      <c r="AI6" s="31" t="n"/>
+      <c r="AJ6" s="31" t="n"/>
+      <c r="AK6" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN6" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP6" s="24" t="inlineStr">
+        <is>
+          <t>Los Chudeles</t>
+        </is>
+      </c>
+      <c r="AQ6" s="24" t="inlineStr">
+        <is>
+          <t>Los Chudeles</t>
+        </is>
+      </c>
+      <c r="AR6" s="24" t="inlineStr">
+        <is>
+          <t>Los Chudeles</t>
+        </is>
+      </c>
+      <c r="AS6" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="AT6" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="AU6" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="AV6" s="24" t="n"/>
+      <c r="AW6" s="24" t="n"/>
+      <c r="AX6" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY6" s="24" t="n"/>
+      <c r="AZ6" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA6" s="24" t="inlineStr">
+        <is>
+          <t>e1ac23d99e831b81cddfe7dc2c7cc5dd4b57a35e88319d1f7162fbb6350e11bd</t>
+        </is>
+      </c>
+      <c r="BB6" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC6" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD6" s="24" t="inlineStr">
+        <is>
+          <t>e1ac23d99e831b81cddfe7dc2c7cc5dd4b57a35e88319d1f7162fbb6350e11bd</t>
+        </is>
+      </c>
+      <c r="BE6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG6" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:56:51.769330Z</t>
+        </is>
+      </c>
+      <c r="BI6" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ6" s="25" t="n"/>
+      <c r="BK6" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="BL6" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BM6" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="BN6" s="28" t="n"/>
+      <c r="BO6" s="28" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
+      <c r="BR6" s="28" t="n"/>
+      <c r="BS6" s="28" t="n"/>
+      <c r="BT6" s="28" t="n"/>
+      <c r="BU6" s="25" t="n"/>
+      <c r="BV6" s="29" t="n"/>
+      <c r="BW6" s="24" t="n"/>
+      <c r="BX6" s="30" t="n"/>
+      <c r="BY6" s="27" t="n"/>
+      <c r="BZ6" s="24" t="n"/>
+      <c r="CA6" s="31" t="n"/>
+      <c r="CB6" s="24" t="n"/>
+      <c r="CC6" s="24" t="n"/>
+      <c r="CD6" s="24" t="n"/>
+      <c r="CE6" s="24" t="n"/>
+      <c r="CF6" s="24" t="n"/>
+      <c r="CG6" s="24" t="n"/>
+      <c r="CH6" s="24" t="n"/>
+      <c r="CI6" s="24" t="n"/>
+      <c r="CJ6" s="24" t="n"/>
+      <c r="CK6" s="24" t="n"/>
+      <c r="CL6" s="24" t="n"/>
+      <c r="CM6" s="24" t="n"/>
+      <c r="CN6" s="24" t="n"/>
+      <c r="CO6" s="24" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>c69d9de93d5448d5</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:56:56.096115Z</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>61240</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>Revenge</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>:3</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N7" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="O7" s="28" t="n">
+        <v>0.500347</v>
+      </c>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="28" t="n">
+        <v>0.190749</v>
+      </c>
+      <c r="R7" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S7" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T7" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U7" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="25" t="n"/>
+      <c r="Z7" s="26" t="n"/>
+      <c r="AA7" s="28" t="n"/>
+      <c r="AB7" s="28" t="n"/>
+      <c r="AC7" s="30" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:57:17.963688Z</t>
+        </is>
+      </c>
+      <c r="AE7" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-valorant-meow-rvn-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG7" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH7" s="24" t="n"/>
+      <c r="AI7" s="31" t="n"/>
+      <c r="AJ7" s="31" t="n"/>
+      <c r="AK7" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN7" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO7" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP7" s="24" t="inlineStr">
+        <is>
+          <t>Revenge</t>
+        </is>
+      </c>
+      <c r="AQ7" s="24" t="inlineStr">
+        <is>
+          <t>Revenge</t>
+        </is>
+      </c>
+      <c r="AR7" s="24" t="inlineStr">
+        <is>
+          <t>Revenge</t>
+        </is>
+      </c>
+      <c r="AS7" s="24" t="inlineStr">
+        <is>
+          <t>:3</t>
+        </is>
+      </c>
+      <c r="AT7" s="24" t="inlineStr">
+        <is>
+          <t>:3</t>
+        </is>
+      </c>
+      <c r="AU7" s="24" t="inlineStr">
+        <is>
+          <t>:3</t>
+        </is>
+      </c>
+      <c r="AV7" s="24" t="n"/>
+      <c r="AW7" s="24" t="n"/>
+      <c r="AX7" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY7" s="24" t="n"/>
+      <c r="AZ7" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA7" s="24" t="inlineStr">
+        <is>
+          <t>e1ac23d99e831b81cddfe7dc2c7cc5dd4b57a35e88319d1f7162fbb6350e11bd</t>
+        </is>
+      </c>
+      <c r="BB7" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC7" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD7" s="24" t="inlineStr">
+        <is>
+          <t>e1ac23d99e831b81cddfe7dc2c7cc5dd4b57a35e88319d1f7162fbb6350e11bd</t>
+        </is>
+      </c>
+      <c r="BE7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG7" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:56:52.318174Z</t>
+        </is>
+      </c>
+      <c r="BI7" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ7" s="25" t="n"/>
+      <c r="BK7" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="BL7" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BM7" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="BN7" s="28" t="n"/>
+      <c r="BO7" s="28" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
+      <c r="BR7" s="28" t="n"/>
+      <c r="BS7" s="28" t="n"/>
+      <c r="BT7" s="28" t="n"/>
+      <c r="BU7" s="25" t="n"/>
+      <c r="BV7" s="29" t="n"/>
+      <c r="BW7" s="24" t="n"/>
+      <c r="BX7" s="30" t="n"/>
+      <c r="BY7" s="27" t="n"/>
+      <c r="BZ7" s="24" t="n"/>
+      <c r="CA7" s="31" t="n"/>
+      <c r="CB7" s="24" t="n"/>
+      <c r="CC7" s="24" t="n"/>
+      <c r="CD7" s="24" t="n"/>
+      <c r="CE7" s="24" t="n"/>
+      <c r="CF7" s="24" t="n"/>
+      <c r="CG7" s="24" t="n"/>
+      <c r="CH7" s="24" t="n"/>
+      <c r="CI7" s="24" t="n"/>
+      <c r="CJ7" s="24" t="n"/>
+      <c r="CK7" s="24" t="n"/>
+      <c r="CL7" s="24" t="n"/>
+      <c r="CM7" s="24" t="n"/>
+      <c r="CN7" s="24" t="n"/>
+      <c r="CO7" s="24" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>c936ad2e5bdc4053</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:16.375053Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>61529</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.528676</v>
+      </c>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n">
+        <v>0.067847</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>54</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="n"/>
+      <c r="W8" s="26" t="n"/>
+      <c r="X8" s="26" t="n"/>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="30" t="n"/>
+      <c r="AD8" s="24" t="n"/>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-beg-kcg-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:13.741488Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN8" s="28" t="n"/>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
+      <c r="BR8" s="28" t="n"/>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+      <c r="CB8" s="24" t="n"/>
+      <c r="CC8" s="24" t="n"/>
+      <c r="CD8" s="24" t="n"/>
+      <c r="CE8" s="24" t="n"/>
+      <c r="CF8" s="24" t="n"/>
+      <c r="CG8" s="24" t="n"/>
+      <c r="CH8" s="24" t="n"/>
+      <c r="CI8" s="24" t="n"/>
+      <c r="CJ8" s="24" t="n"/>
+      <c r="CK8" s="24" t="n"/>
+      <c r="CL8" s="24" t="n"/>
+      <c r="CM8" s="24" t="n"/>
+      <c r="CN8" s="24" t="n"/>
+      <c r="CO8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>5331cd947b664e7a</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:16.375053Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>61735</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.619109</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.028945</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-valorant-tmo-hbs-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:15.790363Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>b21f7223d7a847cc</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:16.375053Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>61860</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Black</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>2GAME Esports</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.523043</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>-0.167359</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="n"/>
+      <c r="W10" s="26" t="n"/>
+      <c r="X10" s="26" t="n"/>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n"/>
+      <c r="AD10" s="24" t="n"/>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-2game-srb-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Black</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Black</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Black</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>2GAME Esports</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>2GAME Esports</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>2GAME Esports</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:16.372842Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:CO1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO10" headerRowCount="1">
-  <autoFilter ref="A1:CO10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO8" headerRowCount="1">
+  <autoFilter ref="A1:CO8"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$10)</f>
+        <f>COUNTA('Picks'!$A$2:$A$8)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$8,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$10,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$8,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")/(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")/(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$10)/SUM('Picks'!$BX$2:$BX$10),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$8)/SUM('Picks'!$BX$2:$BX$8),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$10)</f>
+        <f>SUM('Picks'!$BY$2:$BY$8)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$10,"&lt;&gt;",'Picks'!$AB$2:$AB$10),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$8,"&lt;&gt;",'Picks'!$AB$2:$AB$8),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$10,'Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$8,'Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO10"/>
+  <dimension ref="A1:CO8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3228,12 +3228,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>c936ad2e5bdc4053</t>
+          <t>740596cc872a4bbe</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:16.375053Z</t>
+          <t>2026-07-28T14:24:30.873029Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3278,23 +3278,23 @@
         </is>
       </c>
       <c r="L8" s="26" t="n">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.420168</v>
       </c>
       <c r="O8" s="28" t="n">
         <v>0.528676</v>
       </c>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
-        <v>0.067847</v>
+        <v>0.108508</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="S8" s="29" t="n">
         <v>0.75</v>
@@ -3320,7 +3320,7 @@
       <c r="AD8" s="24" t="n"/>
       <c r="AE8" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-beg-kcg-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-beg-kcg-2026-07-28).</t>
         </is>
       </c>
       <c r="AF8" s="31" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
+          <t>cee841572684572d854c56b6d6e919489ee19e082da259a5e2f60f76864ab64f</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
+          <t>cee841572684572d854c56b6d6e919489ee19e082da259a5e2f60f76864ab64f</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:13.741488Z</t>
+          <t>2026-07-28T14:24:24.591584Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3449,13 +3449,13 @@
       </c>
       <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="BL8" s="27" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="BM8" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.420168</v>
       </c>
       <c r="BN8" s="28" t="n"/>
       <c r="BO8" s="28" t="n"/>
@@ -3486,528 +3486,6 @@
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>5331cd947b664e7a</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:16.375053Z</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>61735</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="G9" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I9" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J9" s="25" t="n"/>
-      <c r="K9" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L9" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N9" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O9" s="28" t="n">
-        <v>0.619109</v>
-      </c>
-      <c r="P9" s="28" t="n"/>
-      <c r="Q9" s="28" t="n">
-        <v>0.028945</v>
-      </c>
-      <c r="R9" s="26" t="n">
-        <v>34</v>
-      </c>
-      <c r="S9" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T9" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U9" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
-      <c r="Y9" s="25" t="n"/>
-      <c r="Z9" s="26" t="n"/>
-      <c r="AA9" s="28" t="n"/>
-      <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
-      <c r="AE9" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-valorant-tmo-hbs-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF9" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG9" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH9" s="24" t="n"/>
-      <c r="AI9" s="31" t="n"/>
-      <c r="AJ9" s="31" t="n"/>
-      <c r="AK9" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL9" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM9" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN9" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO9" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP9" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="AQ9" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="AR9" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="AS9" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="AT9" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="AU9" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="AV9" s="24" t="n"/>
-      <c r="AW9" s="24" t="n"/>
-      <c r="AX9" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY9" s="24" t="n"/>
-      <c r="AZ9" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA9" s="24" t="inlineStr">
-        <is>
-          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
-        </is>
-      </c>
-      <c r="BB9" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC9" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD9" s="24" t="inlineStr">
-        <is>
-          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
-        </is>
-      </c>
-      <c r="BE9" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF9" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG9" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH9" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:15.790363Z</t>
-        </is>
-      </c>
-      <c r="BI9" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ9" s="25" t="n"/>
-      <c r="BK9" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL9" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM9" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN9" s="28" t="n"/>
-      <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
-      <c r="BR9" s="28" t="n"/>
-      <c r="BS9" s="28" t="n"/>
-      <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="25" t="n"/>
-      <c r="BV9" s="29" t="n"/>
-      <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n"/>
-      <c r="BY9" s="27" t="n"/>
-      <c r="BZ9" s="24" t="n"/>
-      <c r="CA9" s="31" t="n"/>
-      <c r="CB9" s="24" t="n"/>
-      <c r="CC9" s="24" t="n"/>
-      <c r="CD9" s="24" t="n"/>
-      <c r="CE9" s="24" t="n"/>
-      <c r="CF9" s="24" t="n"/>
-      <c r="CG9" s="24" t="n"/>
-      <c r="CH9" s="24" t="n"/>
-      <c r="CI9" s="24" t="n"/>
-      <c r="CJ9" s="24" t="n"/>
-      <c r="CK9" s="24" t="n"/>
-      <c r="CL9" s="24" t="n"/>
-      <c r="CM9" s="24" t="n"/>
-      <c r="CN9" s="24" t="n"/>
-      <c r="CO9" s="24" t="n"/>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>b21f7223d7a847cc</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:16.375053Z</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T19:00:00Z</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>61860</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>Shopify Rebellion Black</t>
-        </is>
-      </c>
-      <c r="G10" s="24" t="inlineStr">
-        <is>
-          <t>2GAME Esports</t>
-        </is>
-      </c>
-      <c r="H10" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I10" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J10" s="25" t="n"/>
-      <c r="K10" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L10" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M10" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N10" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O10" s="28" t="n">
-        <v>0.523043</v>
-      </c>
-      <c r="P10" s="28" t="n"/>
-      <c r="Q10" s="28" t="n">
-        <v>-0.167359</v>
-      </c>
-      <c r="R10" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U10" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
-      <c r="Y10" s="25" t="n"/>
-      <c r="Z10" s="26" t="n"/>
-      <c r="AA10" s="28" t="n"/>
-      <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
-      <c r="AE10" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-2game-srb-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF10" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG10" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH10" s="24" t="n"/>
-      <c r="AI10" s="31" t="n"/>
-      <c r="AJ10" s="31" t="n"/>
-      <c r="AK10" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL10" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM10" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN10" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO10" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP10" s="24" t="inlineStr">
-        <is>
-          <t>Shopify Rebellion Black</t>
-        </is>
-      </c>
-      <c r="AQ10" s="24" t="inlineStr">
-        <is>
-          <t>Shopify Rebellion Black</t>
-        </is>
-      </c>
-      <c r="AR10" s="24" t="inlineStr">
-        <is>
-          <t>Shopify Rebellion Black</t>
-        </is>
-      </c>
-      <c r="AS10" s="24" t="inlineStr">
-        <is>
-          <t>2GAME Esports</t>
-        </is>
-      </c>
-      <c r="AT10" s="24" t="inlineStr">
-        <is>
-          <t>2GAME Esports</t>
-        </is>
-      </c>
-      <c r="AU10" s="24" t="inlineStr">
-        <is>
-          <t>2GAME Esports</t>
-        </is>
-      </c>
-      <c r="AV10" s="24" t="n"/>
-      <c r="AW10" s="24" t="n"/>
-      <c r="AX10" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY10" s="24" t="n"/>
-      <c r="AZ10" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA10" s="24" t="inlineStr">
-        <is>
-          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
-        </is>
-      </c>
-      <c r="BB10" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC10" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD10" s="24" t="inlineStr">
-        <is>
-          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
-        </is>
-      </c>
-      <c r="BE10" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF10" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG10" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH10" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:16.372842Z</t>
-        </is>
-      </c>
-      <c r="BI10" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ10" s="25" t="n"/>
-      <c r="BK10" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL10" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM10" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN10" s="28" t="n"/>
-      <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
-      <c r="BR10" s="28" t="n"/>
-      <c r="BS10" s="28" t="n"/>
-      <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="25" t="n"/>
-      <c r="BV10" s="29" t="n"/>
-      <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n"/>
-      <c r="BY10" s="27" t="n"/>
-      <c r="BZ10" s="24" t="n"/>
-      <c r="CA10" s="31" t="n"/>
-      <c r="CB10" s="24" t="n"/>
-      <c r="CC10" s="24" t="n"/>
-      <c r="CD10" s="24" t="n"/>
-      <c r="CE10" s="24" t="n"/>
-      <c r="CF10" s="24" t="n"/>
-      <c r="CG10" s="24" t="n"/>
-      <c r="CH10" s="24" t="n"/>
-      <c r="CI10" s="24" t="n"/>
-      <c r="CJ10" s="24" t="n"/>
-      <c r="CK10" s="24" t="n"/>
-      <c r="CL10" s="24" t="n"/>
-      <c r="CM10" s="24" t="n"/>
-      <c r="CN10" s="24" t="n"/>
-      <c r="CO10" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO8" headerRowCount="1">
-  <autoFilter ref="A1:CO8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO20" headerRowCount="1">
+  <autoFilter ref="A1:CO20"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$8)</f>
+        <f>COUNTA('Picks'!$A$2:$A$20)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$8,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$20,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$8,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$20,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")/(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")/(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$8)/SUM('Picks'!$BX$2:$BX$8),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$20)/SUM('Picks'!$BX$2:$BX$20),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$8)</f>
+        <f>SUM('Picks'!$BY$2:$BY$20)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$8,"&lt;&gt;",'Picks'!$AB$2:$AB$8),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$20,"&lt;&gt;",'Picks'!$AB$2:$AB$20),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$8,'Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$20,'Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO8"/>
+  <dimension ref="A1:CO20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3306,18 +3306,32 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="AC8" s="30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:31:22.023631Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-beg-kcg-2026-07-28).</t>
@@ -3330,7 +3344,7 @@
       </c>
       <c r="AG8" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH8" s="24" t="n"/>
@@ -3486,6 +3500,3208 @@
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
     </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>6982ed63989a409f</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:30:31.285539Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>61735</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.619374</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>-0.08032599999999999</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:31:23.104642Z</t>
+        </is>
+      </c>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-valorant-tmo-hbs-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>8c22ec58fb547190beefa169a52f11eae99a49cdfc2b416003beb11aad6b9129</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>8c22ec58fb547190beefa169a52f11eae99a49cdfc2b416003beb11aad6b9129</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:30:26.042854Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>c4c4b0a1d20f4a80</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:30:31.285539Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>61860</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Black</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>2GAME Esports</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.522953</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>-0.167449</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T23:37:10.553380Z</t>
+        </is>
+      </c>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-2game-srb-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Black</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Black</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Black</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>2GAME Esports</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>2GAME Esports</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>2GAME Esports</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>8c22ec58fb547190beefa169a52f11eae99a49cdfc2b416003beb11aad6b9129</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>8c22ec58fb547190beefa169a52f11eae99a49cdfc2b416003beb11aad6b9129</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:30:26.970466Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>398e854789b541a8</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T12:04:22.575418Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>62689</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>G2 Gozen</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.714884</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.234115</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:34:38.982032Z</t>
+        </is>
+      </c>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-valorant-skn-ggo-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>G2 Gozen</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>G2 Gozen</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>G2 Gozen</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>e33860310416f9b2d86e5c1e14a7bffcebc7a1e4c8af04b416cd37235fd4b6cf</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>e33860310416f9b2d86e5c1e14a7bffcebc7a1e4c8af04b416cd37235fd4b6cf</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T12:04:15.273824Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>e4d0445522234209</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:48:33.149264Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>62925</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX GC</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.570358</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>-0.049414</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:12:59.884655Z</t>
+        </is>
+      </c>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-valorant-gxgc-hbs-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX GC</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX GC</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX GC</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>71696e637dd05bc7933e2bdcf627a39cf9f10c85a7ad852765447d083e849a9e</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>71696e637dd05bc7933e2bdcf627a39cf9f10c85a7ad852765447d083e849a9e</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:48:26.246789Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>6bc0a09d5f1d41d8</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:48:33.149264Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>64563</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.827349</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.127649</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-valorant-100t-sen-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>71696e637dd05bc7933e2bdcf627a39cf9f10c85a7ad852765447d083e849a9e</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>71696e637dd05bc7933e2bdcf627a39cf9f10c85a7ad852765447d083e849a9e</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:48:33.146517Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>8b7dbdba26114d37</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:24:48.854145Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>63626</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>DetonatioN FocusMe</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>VARREL</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.604202</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>0.02437</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T13:30:56.650021Z</t>
+        </is>
+      </c>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-valorant-var-dfm-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>DetonatioN FocusMe</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>DetonatioN FocusMe</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>DetonatioN FocusMe</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>VARREL</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>VARREL</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>VARREL</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>065060c5427d777daf1c2c539c66a4917e7e7a09bf311e9c39e713455cc3d93a</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>065060c5427d777daf1c2c539c66a4917e7e7a09bf311e9c39e713455cc3d93a</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:24:41.203557Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>97f817da629d4166</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T13:36:25.155439Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>63802</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.617757</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>-0.05221</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-valorant-skn-hbs-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>19b7365606ae48f9e7f41f552cee9b921f9088cc133ddb61af3a4f42a2a76e52</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>19b7365606ae48f9e7f41f552cee9b921f9088cc133ddb61af3a4f42a2a76e52</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T13:36:18.680042Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>484ca41ac49a4ac6</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:19.984320Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>64030</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>ALTERNATE aTTaX Ruby</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX GC</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.609158</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>-0.020472</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-valorant-gxgc-aar-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>ALTERNATE aTTaX Ruby</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>ALTERNATE aTTaX Ruby</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>ALTERNATE aTTaX Ruby</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX GC</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX GC</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX GC</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:14.958060Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>908c342fe2bc4f74</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:19.984320Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>64031</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.645767</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>-0.044635</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="n"/>
+      <c r="W17" s="26" t="n"/>
+      <c r="X17" s="26" t="n"/>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n"/>
+      <c r="AD17" s="24" t="n"/>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-ef-fnc-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:15.464790Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>3a87da19646040bf</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:19.984320Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>64807</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Global Esports</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.581239</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>0.062008</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>51</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="n"/>
+      <c r="W18" s="26" t="n"/>
+      <c r="X18" s="26" t="n"/>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n"/>
+      <c r="AD18" s="24" t="n"/>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-valorant-ge-geng-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>Global Esports</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>Global Esports</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>Global Esports</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:17.979503Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>b63e4b0f3a044d57</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:19.984320Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>64940</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>BBL Esports</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.603976</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>0.044505</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>42</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="n"/>
+      <c r="W19" s="26" t="n"/>
+      <c r="X19" s="26" t="n"/>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n"/>
+      <c r="AD19" s="24" t="n"/>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-valorant-bbl-gm-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>BBL Esports</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>BBL Esports</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>BBL Esports</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:18.461860Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>2bd4a13560814372</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:19.984320Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>65506</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.648906</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>0.109735</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="n"/>
+      <c r="W20" s="26" t="n"/>
+      <c r="X20" s="26" t="n"/>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n"/>
+      <c r="AD20" s="24" t="n"/>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-valorant-c9-loud-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:19.463536Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO20" headerRowCount="1">
-  <autoFilter ref="A1:CO20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO21" headerRowCount="1">
+  <autoFilter ref="A1:CO21"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$20)</f>
+        <f>COUNTA('Picks'!$A$2:$A$21)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$20,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$21,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$20,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$21,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")/(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")/(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$20)/SUM('Picks'!$BX$2:$BX$20),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$21)/SUM('Picks'!$BX$2:$BX$21),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$20)</f>
+        <f>SUM('Picks'!$BY$2:$BY$21)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$20,"&lt;&gt;",'Picks'!$AB$2:$AB$20),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$21,"&lt;&gt;",'Picks'!$AB$2:$AB$21),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$20,'Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$21,'Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO20"/>
+  <dimension ref="A1:CO21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5217,18 +5217,32 @@
       </c>
       <c r="U15" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y15" s="25" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
+      <c r="AC15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:22:57.072609Z</t>
+        </is>
+      </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-valorant-skn-hbs-2026-07-30).</t>
@@ -5400,12 +5414,12 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>484ca41ac49a4ac6</t>
+          <t>d42c0ad9f724415c</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:19.984320Z</t>
+          <t>2026-07-30T17:22:29.306490Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -5459,14 +5473,14 @@
         <v>0.62963</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.609158</v>
+        <v>0.608585</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>-0.020472</v>
+        <v>-0.021045</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S16" s="29" t="n">
         <v>0</v>
@@ -5576,7 +5590,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5591,7 +5605,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5611,7 +5625,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:14.958060Z</t>
+          <t>2026-07-30T17:22:23.567804Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5661,12 +5675,12 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>908c342fe2bc4f74</t>
+          <t>8dc6415227db4821</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:19.984320Z</t>
+          <t>2026-07-30T17:22:29.306490Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -5711,20 +5725,20 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-223</v>
+        <v>-233</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.429185</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.6997</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.645767</v>
+        <v>0.645947</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>-0.044635</v>
+        <v>-0.053753</v>
       </c>
       <c r="R17" s="26" t="n">
         <v>0</v>
@@ -5753,7 +5767,7 @@
       <c r="AD17" s="24" t="n"/>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-ef-fnc-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-valorant-ef-fnc-2026-07-30).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -5837,7 +5851,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -5852,7 +5866,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -5872,7 +5886,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:15.464790Z</t>
+          <t>2026-07-30T17:22:24.164133Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -5882,13 +5896,13 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>-223</v>
+        <v>-233</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.429185</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.6997</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
@@ -5922,22 +5936,22 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>3a87da19646040bf</t>
+          <t>72dda7a0f1704bf6</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:19.984320Z</t>
+          <t>2026-07-30T17:22:29.306490Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T11:00:00Z</t>
+          <t>2026-07-30T18:00:00Z</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>64807</t>
+          <t>64028</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -5947,12 +5961,12 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>G2 Gozen</t>
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr">
@@ -5962,7 +5976,7 @@
       </c>
       <c r="I18" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J18" s="25" t="n"/>
@@ -5972,26 +5986,26 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>-108</v>
+        <v>-163</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.613497</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.619772</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.581239</v>
+        <v>0.6363760000000001</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.062008</v>
+        <v>0.016604</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T18" s="24" t="inlineStr">
         <is>
@@ -6014,7 +6028,7 @@
       <c r="AD18" s="24" t="n"/>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-valorant-ge-geng-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-valorant-ggo-tmo-2026-07-30).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6032,7 +6046,7 @@
       <c r="AJ18" s="31" t="n"/>
       <c r="AK18" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL18" s="26" t="n">
@@ -6040,47 +6054,47 @@
       </c>
       <c r="AM18" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN18" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO18" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP18" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AQ18" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AR18" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AS18" s="24" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>G2 Gozen</t>
         </is>
       </c>
       <c r="AT18" s="24" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>G2 Gozen</t>
         </is>
       </c>
       <c r="AU18" s="24" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>G2 Gozen</t>
         </is>
       </c>
       <c r="AV18" s="24" t="n"/>
@@ -6098,7 +6112,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6113,7 +6127,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6133,7 +6147,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:17.979503Z</t>
+          <t>2026-07-30T17:22:24.813759Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6143,13 +6157,13 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>-108</v>
+        <v>-163</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.613497</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.619772</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
@@ -6183,22 +6197,22 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>b63e4b0f3a044d57</t>
+          <t>157a3a3d83394d99</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:19.984320Z</t>
+          <t>2026-07-30T17:22:29.306490Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T15:00:00Z</t>
+          <t>2026-07-31T11:00:00Z</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>64940</t>
+          <t>64807</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -6208,12 +6222,12 @@
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="G19" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="H19" s="24" t="inlineStr">
@@ -6223,7 +6237,7 @@
       </c>
       <c r="I19" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J19" s="25" t="n"/>
@@ -6233,26 +6247,26 @@
         </is>
       </c>
       <c r="L19" s="26" t="n">
-        <v>-127</v>
+        <v>-108</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.925926</v>
       </c>
       <c r="N19" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.519231</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.603976</v>
+        <v>0.581533</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>0.044505</v>
+        <v>0.062302</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="S19" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T19" s="24" t="inlineStr">
         <is>
@@ -6275,7 +6289,7 @@
       <c r="AD19" s="24" t="n"/>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-valorant-bbl-gm-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-valorant-ge-geng-2026-07-31).</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6316,32 +6330,32 @@
       </c>
       <c r="AP19" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="AQ19" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="AR19" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="AS19" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="AT19" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="AU19" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="AV19" s="24" t="n"/>
@@ -6359,7 +6373,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6374,7 +6388,7 @@
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6394,7 +6408,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:18.461860Z</t>
+          <t>2026-07-30T17:22:27.119043Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6404,13 +6418,13 @@
       </c>
       <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
-        <v>-127</v>
+        <v>-108</v>
       </c>
       <c r="BL19" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.925926</v>
       </c>
       <c r="BM19" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.519231</v>
       </c>
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
@@ -6444,22 +6458,22 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>2bd4a13560814372</t>
+          <t>23b6d9b8dfa945df</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:19.984320Z</t>
+          <t>2026-07-30T17:22:29.306490Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T21:00:00Z</t>
+          <t>2026-07-31T15:00:00Z</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>65506</t>
+          <t>64940</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -6469,12 +6483,12 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -6484,7 +6498,7 @@
       </c>
       <c r="I20" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J20" s="25" t="n"/>
@@ -6494,26 +6508,26 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-117</v>
+        <v>-127</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.787402</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.648906</v>
+        <v>0.6034080000000001</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>0.109735</v>
+        <v>0.043937</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="S20" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T20" s="24" t="inlineStr">
         <is>
@@ -6536,7 +6550,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-valorant-c9-loud-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-valorant-bbl-gm-2026-07-31).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6577,32 +6591,32 @@
       </c>
       <c r="AP20" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="AQ20" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="AR20" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="AS20" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="AT20" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="AU20" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="AV20" s="24" t="n"/>
@@ -6620,7 +6634,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6635,7 +6649,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6655,7 +6669,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:19.463536Z</t>
+          <t>2026-07-30T17:22:27.586615Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6665,13 +6679,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-117</v>
+        <v>-127</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.787402</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -6702,6 +6716,267 @@
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>ff514f138b3e42c6</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:22:29.306490Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>65506</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.649081</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>0.10991</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-valorant-c9-loud-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:22:28.738967Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -5414,12 +5414,12 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>d42c0ad9f724415c</t>
+          <t>1113ab0c534445c4</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:29.306490Z</t>
+          <t>2026-07-30T17:40:05.919152Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:23.567804Z</t>
+          <t>2026-07-30T17:40:00.750113Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5675,12 +5675,12 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>8dc6415227db4821</t>
+          <t>68a535f0c5a74e04</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:29.306490Z</t>
+          <t>2026-07-30T17:40:05.919152Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -5725,26 +5725,26 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-233</v>
+        <v>-122</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.819672</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.54955</v>
       </c>
       <c r="O17" s="28" t="n">
         <v>0.645947</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>-0.053753</v>
+        <v>0.096397</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
       <c r="AD17" s="24" t="n"/>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-valorant-ef-fnc-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-valorant-ef-fnc-2026-07-30).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -5785,7 +5785,7 @@
       <c r="AJ17" s="31" t="n"/>
       <c r="AK17" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL17" s="26" t="n">
@@ -5793,17 +5793,17 @@
       </c>
       <c r="AM17" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN17" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO17" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP17" s="24" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:24.164133Z</t>
+          <t>2026-07-30T17:40:01.228013Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -5896,13 +5896,13 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>-233</v>
+        <v>-122</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.819672</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.54955</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
@@ -5936,12 +5936,12 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>72dda7a0f1704bf6</t>
+          <t>e719fd5d68c24cb2</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:29.306490Z</t>
+          <t>2026-07-30T17:40:05.919152Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -5986,26 +5986,26 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>-163</v>
+        <v>127</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.27</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.440529</v>
       </c>
       <c r="O18" s="28" t="n">
         <v>0.6363760000000001</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.016604</v>
+        <v>0.195847</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T18" s="24" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
       <c r="AD18" s="24" t="n"/>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-valorant-ggo-tmo-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-valorant-ggo-tmo-2026-07-30).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6046,7 +6046,7 @@
       <c r="AJ18" s="31" t="n"/>
       <c r="AK18" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL18" s="26" t="n">
@@ -6054,17 +6054,17 @@
       </c>
       <c r="AM18" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN18" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO18" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP18" s="24" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:24.813759Z</t>
+          <t>2026-07-30T17:40:01.726408Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6157,13 +6157,13 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>-163</v>
+        <v>127</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.27</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.440529</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
@@ -6197,12 +6197,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>157a3a3d83394d99</t>
+          <t>d25d1add789a4af4</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:29.306490Z</t>
+          <t>2026-07-30T17:40:05.919152Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:27.119043Z</t>
+          <t>2026-07-30T17:40:03.847842Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6458,12 +6458,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>23b6d9b8dfa945df</t>
+          <t>ae6059556eb94566</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:29.306490Z</t>
+          <t>2026-07-30T17:40:05.919152Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -6508,23 +6508,23 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="O20" s="28" t="n">
         <v>0.6034080000000001</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>0.043937</v>
+        <v>0.032593</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="S20" s="29" t="n">
         <v>1.5</v>
@@ -6550,7 +6550,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-valorant-bbl-gm-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-valorant-bbl-gm-2026-07-31).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:27.586615Z</t>
+          <t>2026-07-30T17:40:04.331936Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6679,13 +6679,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -6719,12 +6719,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>ff514f138b3e42c6</t>
+          <t>0a9580a1a6d04bfb</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:29.306490Z</t>
+          <t>2026-07-30T17:40:05.919152Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:28.738967Z</t>
+          <t>2026-07-30T17:40:05.383273Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO21" headerRowCount="1">
-  <autoFilter ref="A1:CO21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO12" headerRowCount="1">
+  <autoFilter ref="A1:CO12"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$21)</f>
+        <f>COUNTA('Picks'!$A$2:$A$12)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$21,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$12,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$21,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$12,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")/(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")/(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$21)/SUM('Picks'!$BX$2:$BX$21),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$12)/SUM('Picks'!$BX$2:$BX$12),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$21)</f>
+        <f>SUM('Picks'!$BY$2:$BY$12)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$21,"&lt;&gt;",'Picks'!$AB$2:$AB$21),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$12,"&lt;&gt;",'Picks'!$AB$2:$AB$12),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$21,'Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$12,'Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO21"/>
+  <dimension ref="A1:CO12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1578,22 +1578,22 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>5410b19790cb4158</t>
+          <t>0c9b461f54a54b67</t>
         </is>
       </c>
       <c r="B2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T13:32:13.323625Z</t>
+          <t>2026-07-31T10:46:58.818420Z</t>
         </is>
       </c>
       <c r="C2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T15:00:00Z</t>
+          <t>2026-07-31T11:00:00Z</t>
         </is>
       </c>
       <c r="D2" s="24" t="inlineStr">
         <is>
-          <t>60760</t>
+          <t>64807</t>
         </is>
       </c>
       <c r="E2" s="24" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="F2" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="G2" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="H2" s="24" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="I2" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J2" s="25" t="n"/>
@@ -1628,30 +1628,30 @@
         </is>
       </c>
       <c r="L2" s="26" t="n">
-        <v>144</v>
+        <v>203</v>
       </c>
       <c r="M2" s="27" t="n">
-        <v>2.44</v>
+        <v>3.03</v>
       </c>
       <c r="N2" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.330033</v>
       </c>
       <c r="O2" s="28" t="n">
-        <v>0.519337</v>
+        <v>0.574963</v>
       </c>
       <c r="P2" s="28" t="n"/>
       <c r="Q2" s="28" t="n">
-        <v>0.109501</v>
+        <v>0.24493</v>
       </c>
       <c r="R2" s="26" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="S2" s="29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T2" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U2" s="24" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="V2" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W2" s="26" t="n">
@@ -1671,20 +1671,26 @@
         <v>0</v>
       </c>
       <c r="Y2" s="25" t="n"/>
-      <c r="Z2" s="26" t="n"/>
-      <c r="AA2" s="28" t="n"/>
-      <c r="AB2" s="28" t="n"/>
+      <c r="Z2" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="AA2" s="28" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AB2" s="28" t="n">
+        <v>0.009967</v>
+      </c>
       <c r="AC2" s="30" t="n">
-        <v>0</v>
+        <v>2.5375</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T17:03:46.656501Z</t>
+          <t>2026-07-31T13:38:58.560220Z</t>
         </is>
       </c>
       <c r="AE2" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-valorant-beg-hbs-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-valorant-ge-geng-2026-07-31).</t>
         </is>
       </c>
       <c r="AF2" s="31" t="inlineStr">
@@ -1694,7 +1700,7 @@
       </c>
       <c r="AG2" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH2" s="24" t="n"/>
@@ -1702,7 +1708,7 @@
       <c r="AJ2" s="31" t="n"/>
       <c r="AK2" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL2" s="26" t="n">
@@ -1710,47 +1716,47 @@
       </c>
       <c r="AM2" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN2" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO2" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP2" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="AQ2" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="AR2" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="AS2" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="AT2" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="AU2" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="AV2" s="24" t="n"/>
@@ -1768,7 +1774,7 @@
       </c>
       <c r="BA2" s="24" t="inlineStr">
         <is>
-          <t>6cce51743bf5606a4094683b8f88c468e312b6e0f3a4d11913a9997a273d6b86</t>
+          <t>316f14757ba7b67513d2e43f0e5432e02d1d1af04a03ed2b8a0b070efbf6c94e</t>
         </is>
       </c>
       <c r="BB2" s="24" t="inlineStr">
@@ -1778,12 +1784,12 @@
       </c>
       <c r="BC2" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD2" s="24" t="inlineStr">
         <is>
-          <t>6cce51743bf5606a4094683b8f88c468e312b6e0f3a4d11913a9997a273d6b86</t>
+          <t>316f14757ba7b67513d2e43f0e5432e02d1d1af04a03ed2b8a0b070efbf6c94e</t>
         </is>
       </c>
       <c r="BE2" s="24" t="inlineStr">
@@ -1798,12 +1804,12 @@
       </c>
       <c r="BG2" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T13:32:04.945513Z</t>
+          <t>2026-07-31T10:46:53.940374Z</t>
         </is>
       </c>
       <c r="BI2" s="24" t="inlineStr">
@@ -1813,19 +1819,23 @@
       </c>
       <c r="BJ2" s="25" t="n"/>
       <c r="BK2" s="26" t="n">
-        <v>144</v>
+        <v>203</v>
       </c>
       <c r="BL2" s="27" t="n">
-        <v>2.44</v>
+        <v>3.03</v>
       </c>
       <c r="BM2" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.330033</v>
       </c>
       <c r="BN2" s="28" t="n"/>
       <c r="BO2" s="28" t="n"/>
       <c r="BP2" s="25" t="n"/>
-      <c r="BQ2" s="27" t="n"/>
-      <c r="BR2" s="28" t="n"/>
+      <c r="BQ2" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BR2" s="28" t="n">
+        <v>0.34</v>
+      </c>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
       <c r="BU2" s="25" t="n"/>
@@ -1853,22 +1863,22 @@
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>0aa2021b65f14a53</t>
+          <t>0e9f1583a76a4fd2</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T19:51:39.691788Z</t>
+          <t>2026-07-31T13:44:08.052962Z</t>
         </is>
       </c>
       <c r="C3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T21:00:00Z</t>
+          <t>2026-07-31T15:00:00Z</t>
         </is>
       </c>
       <c r="D3" s="24" t="inlineStr">
         <is>
-          <t>61045</t>
+          <t>64940</t>
         </is>
       </c>
       <c r="E3" s="24" t="inlineStr">
@@ -1878,12 +1888,12 @@
       </c>
       <c r="F3" s="24" t="inlineStr">
         <is>
-          <t>SaD GC</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="G3" s="24" t="inlineStr">
         <is>
-          <t>ORA Temper</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="H3" s="24" t="inlineStr">
@@ -1903,30 +1913,30 @@
         </is>
       </c>
       <c r="L3" s="26" t="n">
-        <v>203</v>
+        <v>-127</v>
       </c>
       <c r="M3" s="27" t="n">
-        <v>3.03</v>
+        <v>1.787402</v>
       </c>
       <c r="N3" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O3" s="28" t="n">
-        <v>0.5057199999999999</v>
+        <v>0.589785</v>
       </c>
       <c r="P3" s="28" t="n"/>
       <c r="Q3" s="28" t="n">
-        <v>0.175687</v>
+        <v>0.030314</v>
       </c>
       <c r="R3" s="26" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="S3" s="29" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="T3" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U3" s="24" t="inlineStr">
@@ -1946,20 +1956,26 @@
         <v>1</v>
       </c>
       <c r="Y3" s="25" t="n"/>
-      <c r="Z3" s="26" t="n"/>
-      <c r="AA3" s="28" t="n"/>
-      <c r="AB3" s="28" t="n"/>
+      <c r="Z3" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA3" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB3" s="28" t="n">
+        <v>0.000529</v>
+      </c>
       <c r="AC3" s="30" t="n">
-        <v>1.015</v>
+        <v>0.9843</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T22:52:00.762411Z</t>
+          <t>2026-07-31T19:51:22.532394Z</t>
         </is>
       </c>
       <c r="AE3" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-valorant-orat-sga-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-valorant-bbl-gm-2026-07-31).</t>
         </is>
       </c>
       <c r="AF3" s="31" t="inlineStr">
@@ -2000,32 +2016,32 @@
       </c>
       <c r="AP3" s="24" t="inlineStr">
         <is>
-          <t>SaD GC</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="AQ3" s="24" t="inlineStr">
         <is>
-          <t>SaD GC</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="AR3" s="24" t="inlineStr">
         <is>
-          <t>SaD GC</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="AS3" s="24" t="inlineStr">
         <is>
-          <t>ORA Temper</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="AT3" s="24" t="inlineStr">
         <is>
-          <t>ORA Temper</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="AU3" s="24" t="inlineStr">
         <is>
-          <t>ORA Temper</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="AV3" s="24" t="n"/>
@@ -2043,7 +2059,7 @@
       </c>
       <c r="BA3" s="24" t="inlineStr">
         <is>
-          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+          <t>139f8fd81efcd2fb54fc3e158052d3e9c04fc7442a0b372b18e645e84996b74c</t>
         </is>
       </c>
       <c r="BB3" s="24" t="inlineStr">
@@ -2053,12 +2069,12 @@
       </c>
       <c r="BC3" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD3" s="24" t="inlineStr">
         <is>
-          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+          <t>139f8fd81efcd2fb54fc3e158052d3e9c04fc7442a0b372b18e645e84996b74c</t>
         </is>
       </c>
       <c r="BE3" s="24" t="inlineStr">
@@ -2073,12 +2089,12 @@
       </c>
       <c r="BG3" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T19:51:33.586186Z</t>
+          <t>2026-07-31T13:44:03.465992Z</t>
         </is>
       </c>
       <c r="BI3" s="24" t="inlineStr">
@@ -2088,19 +2104,23 @@
       </c>
       <c r="BJ3" s="25" t="n"/>
       <c r="BK3" s="26" t="n">
-        <v>203</v>
+        <v>-127</v>
       </c>
       <c r="BL3" s="27" t="n">
-        <v>3.03</v>
+        <v>1.787402</v>
       </c>
       <c r="BM3" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN3" s="28" t="n"/>
       <c r="BO3" s="28" t="n"/>
       <c r="BP3" s="25" t="n"/>
-      <c r="BQ3" s="27" t="n"/>
-      <c r="BR3" s="28" t="n"/>
+      <c r="BQ3" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR3" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
       <c r="BU3" s="25" t="n"/>
@@ -2128,22 +2148,22 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>54c2f7d359844b66</t>
+          <t>992f00d317164d2a</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T19:51:39.691788Z</t>
+          <t>2026-07-31T19:57:00.316597Z</t>
         </is>
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T21:00:00Z</t>
+          <t>2026-07-31T21:00:00Z</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>61046</t>
+          <t>65506</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
@@ -2153,12 +2173,12 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
         <is>
-          <t>Cloud9 GC</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="H4" s="24" t="inlineStr">
@@ -2168,7 +2188,7 @@
       </c>
       <c r="I4" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J4" s="25" t="n"/>
@@ -2178,30 +2198,30 @@
         </is>
       </c>
       <c r="L4" s="26" t="n">
-        <v>100</v>
+        <v>-122</v>
       </c>
       <c r="M4" s="27" t="n">
-        <v>2</v>
+        <v>1.819672</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>0.5</v>
+        <v>0.54955</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>0.53613</v>
+        <v>0.558389</v>
       </c>
       <c r="P4" s="28" t="n"/>
       <c r="Q4" s="28" t="n">
-        <v>0.03613</v>
+        <v>0.008839</v>
       </c>
       <c r="R4" s="26" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S4" s="29" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="T4" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U4" s="24" t="inlineStr">
@@ -2211,7 +2231,7 @@
       </c>
       <c r="V4" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W4" s="26" t="n">
@@ -2221,20 +2241,26 @@
         <v>0</v>
       </c>
       <c r="Y4" s="25" t="n"/>
-      <c r="Z4" s="26" t="n"/>
-      <c r="AA4" s="28" t="n"/>
-      <c r="AB4" s="28" t="n"/>
+      <c r="Z4" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="AA4" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AB4" s="28" t="n">
+        <v>0.00045</v>
+      </c>
       <c r="AC4" s="30" t="n">
-        <v>-0.75</v>
+        <v>0.8197</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:57:14.441712Z</t>
+          <t>2026-08-01T03:00:18.104800Z</t>
         </is>
       </c>
       <c r="AE4" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-valorant-c9gc-spi-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-valorant-c9-loud-2026-07-31).</t>
         </is>
       </c>
       <c r="AF4" s="31" t="inlineStr">
@@ -2244,7 +2270,7 @@
       </c>
       <c r="AG4" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH4" s="24" t="n"/>
@@ -2252,7 +2278,7 @@
       <c r="AJ4" s="31" t="n"/>
       <c r="AK4" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL4" s="26" t="n">
@@ -2260,47 +2286,47 @@
       </c>
       <c r="AM4" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN4" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO4" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP4" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="AQ4" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="AR4" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="AS4" s="24" t="inlineStr">
         <is>
-          <t>Cloud9 GC</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="AT4" s="24" t="inlineStr">
         <is>
-          <t>Cloud9 GC</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="AU4" s="24" t="inlineStr">
         <is>
-          <t>Cloud9 GC</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="AV4" s="24" t="n"/>
@@ -2318,7 +2344,7 @@
       </c>
       <c r="BA4" s="24" t="inlineStr">
         <is>
-          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+          <t>c495285eb3dce15d5f7b197559c746544440f7a87fe5550e2c24625e309d8dd6</t>
         </is>
       </c>
       <c r="BB4" s="24" t="inlineStr">
@@ -2328,12 +2354,12 @@
       </c>
       <c r="BC4" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD4" s="24" t="inlineStr">
         <is>
-          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+          <t>c495285eb3dce15d5f7b197559c746544440f7a87fe5550e2c24625e309d8dd6</t>
         </is>
       </c>
       <c r="BE4" s="24" t="inlineStr">
@@ -2348,12 +2374,12 @@
       </c>
       <c r="BG4" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T19:51:34.129373Z</t>
+          <t>2026-07-31T19:56:56.353476Z</t>
         </is>
       </c>
       <c r="BI4" s="24" t="inlineStr">
@@ -2363,19 +2389,23 @@
       </c>
       <c r="BJ4" s="25" t="n"/>
       <c r="BK4" s="26" t="n">
-        <v>100</v>
+        <v>-122</v>
       </c>
       <c r="BL4" s="27" t="n">
-        <v>2</v>
+        <v>1.819672</v>
       </c>
       <c r="BM4" s="28" t="n">
-        <v>0.5</v>
+        <v>0.54955</v>
       </c>
       <c r="BN4" s="28" t="n"/>
       <c r="BO4" s="28" t="n"/>
       <c r="BP4" s="25" t="n"/>
-      <c r="BQ4" s="27" t="n"/>
-      <c r="BR4" s="28" t="n"/>
+      <c r="BQ4" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BR4" s="28" t="n">
+        <v>0.55</v>
+      </c>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
       <c r="BU4" s="25" t="n"/>
@@ -2403,22 +2433,22 @@
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>2262d180fb3749f8</t>
+          <t>3e99dffb22ef4292</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T19:51:39.691788Z</t>
+          <t>2026-08-01T10:23:18.378580Z</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T21:00:00Z</t>
+          <t>2026-08-01T11:00:00Z</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>61048</t>
+          <t>65894</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -2428,12 +2458,12 @@
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>Rex Regum Qeon</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion Gold</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="H5" s="24" t="inlineStr">
@@ -2443,7 +2473,7 @@
       </c>
       <c r="I5" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J5" s="25" t="n"/>
@@ -2453,30 +2483,30 @@
         </is>
       </c>
       <c r="L5" s="26" t="n">
-        <v>100</v>
+        <v>-150</v>
       </c>
       <c r="M5" s="27" t="n">
-        <v>2</v>
+        <v>1.666667</v>
       </c>
       <c r="N5" s="28" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O5" s="28" t="n">
-        <v>0.541059</v>
+        <v>0.552961</v>
       </c>
       <c r="P5" s="28" t="n"/>
       <c r="Q5" s="28" t="n">
-        <v>0.041059</v>
+        <v>-0.047039</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="S5" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T5" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U5" s="24" t="inlineStr">
@@ -2486,7 +2516,7 @@
       </c>
       <c r="V5" s="24" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W5" s="26" t="n">
@@ -2496,20 +2526,26 @@
         <v>0</v>
       </c>
       <c r="Y5" s="25" t="n"/>
-      <c r="Z5" s="26" t="n"/>
-      <c r="AA5" s="28" t="n"/>
-      <c r="AB5" s="28" t="n"/>
+      <c r="Z5" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="AA5" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB5" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="AC5" s="30" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:57:15.596098Z</t>
+          <t>2026-08-01T16:48:17.244830Z</t>
         </is>
       </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-valorant-srg-swim-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-valorant-fs-rrq-2026-08-01).</t>
         </is>
       </c>
       <c r="AF5" s="31" t="inlineStr">
@@ -2519,7 +2555,7 @@
       </c>
       <c r="AG5" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH5" s="24" t="n"/>
@@ -2527,7 +2563,7 @@
       <c r="AJ5" s="31" t="n"/>
       <c r="AK5" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL5" s="26" t="n">
@@ -2535,47 +2571,47 @@
       </c>
       <c r="AM5" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN5" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO5" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP5" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>Rex Regum Qeon</t>
         </is>
       </c>
       <c r="AQ5" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>Rex Regum Qeon</t>
         </is>
       </c>
       <c r="AR5" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>Rex Regum Qeon</t>
         </is>
       </c>
       <c r="AS5" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion Gold</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="AT5" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion Gold</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="AU5" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion Gold</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="AV5" s="24" t="n"/>
@@ -2593,7 +2629,7 @@
       </c>
       <c r="BA5" s="24" t="inlineStr">
         <is>
-          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+          <t>8b020a3d72d15d0d6b9a3580f54f87b4bba53a58d9087c0149f9da2085413676</t>
         </is>
       </c>
       <c r="BB5" s="24" t="inlineStr">
@@ -2603,12 +2639,12 @@
       </c>
       <c r="BC5" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD5" s="24" t="inlineStr">
         <is>
-          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+          <t>8b020a3d72d15d0d6b9a3580f54f87b4bba53a58d9087c0149f9da2085413676</t>
         </is>
       </c>
       <c r="BE5" s="24" t="inlineStr">
@@ -2623,12 +2659,12 @@
       </c>
       <c r="BG5" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T19:51:34.644041Z</t>
+          <t>2026-08-01T10:23:13.032551Z</t>
         </is>
       </c>
       <c r="BI5" s="24" t="inlineStr">
@@ -2638,19 +2674,23 @@
       </c>
       <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
-        <v>100</v>
+        <v>-150</v>
       </c>
       <c r="BL5" s="27" t="n">
-        <v>2</v>
+        <v>1.666667</v>
       </c>
       <c r="BM5" s="28" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BN5" s="28" t="n"/>
       <c r="BO5" s="28" t="n"/>
       <c r="BP5" s="25" t="n"/>
-      <c r="BQ5" s="27" t="n"/>
-      <c r="BR5" s="28" t="n"/>
+      <c r="BQ5" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BR5" s="28" t="n">
+        <v>0.6</v>
+      </c>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
       <c r="BU5" s="25" t="n"/>
@@ -2678,22 +2718,22 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>54aad50fb6e84432</t>
+          <t>67352456a8884132</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T22:56:56.096115Z</t>
+          <t>2026-08-01T13:46:54.819019Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T23:30:00Z</t>
+          <t>2026-08-01T15:00:00Z</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>61239</t>
+          <t>65953</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -2703,12 +2743,12 @@
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>Los Chudeles</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>Eternal Focus Amethyst</t>
+          <t>FUT Esports</t>
         </is>
       </c>
       <c r="H6" s="24" t="inlineStr">
@@ -2718,7 +2758,7 @@
       </c>
       <c r="I6" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J6" s="25" t="n"/>
@@ -2728,30 +2768,30 @@
         </is>
       </c>
       <c r="L6" s="26" t="n">
-        <v>223</v>
+        <v>-194</v>
       </c>
       <c r="M6" s="27" t="n">
-        <v>3.23</v>
+        <v>1.515464</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.659864</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>0.557051</v>
+        <v>0.566738</v>
       </c>
       <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n">
-        <v>0.247453</v>
+        <v>-0.093126</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S6" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T6" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U6" s="24" t="inlineStr">
@@ -2761,7 +2801,7 @@
       </c>
       <c r="V6" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W6" s="26" t="n">
@@ -2771,20 +2811,26 @@
         <v>0</v>
       </c>
       <c r="Y6" s="25" t="n"/>
-      <c r="Z6" s="26" t="n"/>
-      <c r="AA6" s="28" t="n"/>
-      <c r="AB6" s="28" t="n"/>
+      <c r="Z6" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="AA6" s="28" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB6" s="28" t="n">
+        <v>0.000136</v>
+      </c>
       <c r="AC6" s="30" t="n">
-        <v>-1</v>
+        <v>0.5155</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:57:16.746309Z</t>
+          <t>2026-08-01T18:35:40.219599Z</t>
         </is>
       </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-valorant-efa-lcd-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-fut-vit-2026-08-01).</t>
         </is>
       </c>
       <c r="AF6" s="31" t="inlineStr">
@@ -2794,7 +2840,7 @@
       </c>
       <c r="AG6" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH6" s="24" t="n"/>
@@ -2802,7 +2848,7 @@
       <c r="AJ6" s="31" t="n"/>
       <c r="AK6" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL6" s="26" t="n">
@@ -2810,47 +2856,47 @@
       </c>
       <c r="AM6" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN6" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO6" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP6" s="24" t="inlineStr">
         <is>
-          <t>Los Chudeles</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="AQ6" s="24" t="inlineStr">
         <is>
-          <t>Los Chudeles</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="AR6" s="24" t="inlineStr">
         <is>
-          <t>Los Chudeles</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="AS6" s="24" t="inlineStr">
         <is>
-          <t>Eternal Focus Amethyst</t>
+          <t>FUT Esports</t>
         </is>
       </c>
       <c r="AT6" s="24" t="inlineStr">
         <is>
-          <t>Eternal Focus Amethyst</t>
+          <t>FUT Esports</t>
         </is>
       </c>
       <c r="AU6" s="24" t="inlineStr">
         <is>
-          <t>Eternal Focus Amethyst</t>
+          <t>FUT Esports</t>
         </is>
       </c>
       <c r="AV6" s="24" t="n"/>
@@ -2868,7 +2914,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>e1ac23d99e831b81cddfe7dc2c7cc5dd4b57a35e88319d1f7162fbb6350e11bd</t>
+          <t>5f7adb9e3af3e4b9370360107475e66be29da0c570d1ec14af5f7846257b6ab8</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2878,12 +2924,12 @@
       </c>
       <c r="BC6" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>e1ac23d99e831b81cddfe7dc2c7cc5dd4b57a35e88319d1f7162fbb6350e11bd</t>
+          <t>5f7adb9e3af3e4b9370360107475e66be29da0c570d1ec14af5f7846257b6ab8</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2898,12 +2944,12 @@
       </c>
       <c r="BG6" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T22:56:51.769330Z</t>
+          <t>2026-08-01T13:46:50.499962Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">
@@ -2913,19 +2959,23 @@
       </c>
       <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
-        <v>223</v>
+        <v>-194</v>
       </c>
       <c r="BL6" s="27" t="n">
-        <v>3.23</v>
+        <v>1.515464</v>
       </c>
       <c r="BM6" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.659864</v>
       </c>
       <c r="BN6" s="28" t="n"/>
       <c r="BO6" s="28" t="n"/>
       <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
-      <c r="BR6" s="28" t="n"/>
+      <c r="BQ6" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BR6" s="28" t="n">
+        <v>0.66</v>
+      </c>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
       <c r="BU6" s="25" t="n"/>
@@ -2953,22 +3003,22 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>c69d9de93d5448d5</t>
+          <t>49d2571015064442</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T22:56:56.096115Z</t>
+          <t>2026-08-01T16:54:19.279565Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T23:30:00Z</t>
+          <t>2026-08-01T18:00:00Z</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>61240</t>
+          <t>66138</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -2978,12 +3028,12 @@
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>Revenge</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>:3</t>
+          <t>Karmine Corp</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr">
@@ -3003,30 +3053,30 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>223</v>
+        <v>-113</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>3.23</v>
+        <v>1.884956</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.530516</v>
       </c>
       <c r="O7" s="28" t="n">
-        <v>0.500347</v>
+        <v>0.500941</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.190749</v>
+        <v>-0.029575</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="S7" s="29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T7" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U7" s="24" t="inlineStr">
@@ -3046,20 +3096,26 @@
         <v>1</v>
       </c>
       <c r="Y7" s="25" t="n"/>
-      <c r="Z7" s="26" t="n"/>
-      <c r="AA7" s="28" t="n"/>
-      <c r="AB7" s="28" t="n"/>
+      <c r="Z7" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA7" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB7" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
       <c r="AC7" s="30" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:57:17.963688Z</t>
+          <t>2026-08-01T21:41:01.737935Z</t>
         </is>
       </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-valorant-meow-rvn-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-valorant-kc-tl-2026-08-01).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3077,7 +3133,7 @@
       <c r="AJ7" s="31" t="n"/>
       <c r="AK7" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL7" s="26" t="n">
@@ -3085,47 +3141,47 @@
       </c>
       <c r="AM7" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN7" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO7" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP7" s="24" t="inlineStr">
         <is>
-          <t>Revenge</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AQ7" s="24" t="inlineStr">
         <is>
-          <t>Revenge</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AR7" s="24" t="inlineStr">
         <is>
-          <t>Revenge</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AS7" s="24" t="inlineStr">
         <is>
-          <t>:3</t>
+          <t>Karmine Corp</t>
         </is>
       </c>
       <c r="AT7" s="24" t="inlineStr">
         <is>
-          <t>:3</t>
+          <t>Karmine Corp</t>
         </is>
       </c>
       <c r="AU7" s="24" t="inlineStr">
         <is>
-          <t>:3</t>
+          <t>Karmine Corp</t>
         </is>
       </c>
       <c r="AV7" s="24" t="n"/>
@@ -3143,7 +3199,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>e1ac23d99e831b81cddfe7dc2c7cc5dd4b57a35e88319d1f7162fbb6350e11bd</t>
+          <t>de211ba59b87f7f994811cc2b95e7fa0909c8c2bfb3ba4be0f9ef98b999ead5f</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3153,12 +3209,12 @@
       </c>
       <c r="BC7" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>e1ac23d99e831b81cddfe7dc2c7cc5dd4b57a35e88319d1f7162fbb6350e11bd</t>
+          <t>de211ba59b87f7f994811cc2b95e7fa0909c8c2bfb3ba4be0f9ef98b999ead5f</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3173,12 +3229,12 @@
       </c>
       <c r="BG7" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T22:56:52.318174Z</t>
+          <t>2026-08-01T16:54:15.399177Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3188,19 +3244,23 @@
       </c>
       <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>223</v>
+        <v>-113</v>
       </c>
       <c r="BL7" s="27" t="n">
-        <v>3.23</v>
+        <v>1.884956</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.530516</v>
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
       <c r="BP7" s="25" t="n"/>
-      <c r="BQ7" s="27" t="n"/>
-      <c r="BR7" s="28" t="n"/>
+      <c r="BQ7" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR7" s="28" t="n">
+        <v>0.53</v>
+      </c>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
       <c r="BU7" s="25" t="n"/>
@@ -3228,22 +3288,22 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>740596cc872a4bbe</t>
+          <t>e8a1cf4b6b8646cf</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T14:24:30.873029Z</t>
+          <t>2026-08-01T20:18:52.629033Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T15:00:00Z</t>
+          <t>2026-08-03T00:00:00Z</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>61529</t>
+          <t>67386</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -3253,12 +3313,12 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp GC</t>
+          <t>Sentinels</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="H8" s="24" t="inlineStr">
@@ -3278,63 +3338,49 @@
         </is>
       </c>
       <c r="L8" s="26" t="n">
-        <v>138</v>
+        <v>-156</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>2.38</v>
+        <v>1.641026</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.609375</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>0.528676</v>
+        <v>0.626556</v>
       </c>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
-        <v>0.108508</v>
+        <v>0.017181</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="S8" s="29" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="T8" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W8" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" s="26" t="n">
-        <v>0</v>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="n"/>
+      <c r="W8" s="26" t="n"/>
+      <c r="X8" s="26" t="n"/>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AD8" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T20:31:22.023631Z</t>
-        </is>
-      </c>
+      <c r="AC8" s="30" t="n"/>
+      <c r="AD8" s="24" t="n"/>
       <c r="AE8" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-beg-kcg-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-valorant-g2-sen-2026-08-03).</t>
         </is>
       </c>
       <c r="AF8" s="31" t="inlineStr">
@@ -3344,7 +3390,7 @@
       </c>
       <c r="AG8" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH8" s="24" t="n"/>
@@ -3352,7 +3398,7 @@
       <c r="AJ8" s="31" t="n"/>
       <c r="AK8" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL8" s="26" t="n">
@@ -3360,47 +3406,47 @@
       </c>
       <c r="AM8" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN8" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO8" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP8" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp GC</t>
+          <t>Sentinels</t>
         </is>
       </c>
       <c r="AQ8" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp GC</t>
+          <t>Sentinels</t>
         </is>
       </c>
       <c r="AR8" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp GC</t>
+          <t>Sentinels</t>
         </is>
       </c>
       <c r="AS8" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="AT8" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="AU8" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="AV8" s="24" t="n"/>
@@ -3418,7 +3464,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>cee841572684572d854c56b6d6e919489ee19e082da259a5e2f60f76864ab64f</t>
+          <t>380fd5a8849c0ab4c0739f37636ab4ad8bb9ee7fab81eb341719f39d4f324b58</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3428,12 +3474,12 @@
       </c>
       <c r="BC8" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>cee841572684572d854c56b6d6e919489ee19e082da259a5e2f60f76864ab64f</t>
+          <t>380fd5a8849c0ab4c0739f37636ab4ad8bb9ee7fab81eb341719f39d4f324b58</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3448,12 +3494,12 @@
       </c>
       <c r="BG8" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T14:24:24.591584Z</t>
+          <t>2026-08-01T20:18:52.627150Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3463,13 +3509,13 @@
       </c>
       <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
-        <v>138</v>
+        <v>-156</v>
       </c>
       <c r="BL8" s="27" t="n">
-        <v>2.38</v>
+        <v>1.641026</v>
       </c>
       <c r="BM8" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.609375</v>
       </c>
       <c r="BN8" s="28" t="n"/>
       <c r="BO8" s="28" t="n"/>
@@ -3503,22 +3549,22 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>6982ed63989a409f</t>
+          <t>7710d3db4fcb40b0</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T17:30:31.285539Z</t>
+          <t>2026-08-01T20:33:11.238423Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T18:00:00Z</t>
+          <t>2026-08-03T15:00:00Z</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>61735</t>
+          <t>67569</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -3528,12 +3574,12 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>Twisted Minds Orchid</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -3553,63 +3599,49 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>-233</v>
+        <v>-203</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.492611</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.669967</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.619374</v>
+        <v>0.76553</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>-0.08032599999999999</v>
+        <v>0.095563</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="S9" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T9" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W9" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" s="26" t="n">
-        <v>0</v>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T20:31:23.104642Z</t>
-        </is>
-      </c>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-valorant-tmo-hbs-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3619,7 +3651,7 @@
       </c>
       <c r="AG9" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH9" s="24" t="n"/>
@@ -3627,7 +3659,7 @@
       <c r="AJ9" s="31" t="n"/>
       <c r="AK9" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL9" s="26" t="n">
@@ -3635,47 +3667,47 @@
       </c>
       <c r="AM9" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN9" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO9" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP9" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="AQ9" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="AR9" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="AS9" s="24" t="inlineStr">
         <is>
-          <t>Twisted Minds Orchid</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="AT9" s="24" t="inlineStr">
         <is>
-          <t>Twisted Minds Orchid</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="AU9" s="24" t="inlineStr">
         <is>
-          <t>Twisted Minds Orchid</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="AV9" s="24" t="n"/>
@@ -3693,7 +3725,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>8c22ec58fb547190beefa169a52f11eae99a49cdfc2b416003beb11aad6b9129</t>
+          <t>6c2fe30bde2e3d49744e134c7d83a04f47b0437d09b6f8743e0023be67965171</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3703,12 +3735,12 @@
       </c>
       <c r="BC9" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>8c22ec58fb547190beefa169a52f11eae99a49cdfc2b416003beb11aad6b9129</t>
+          <t>6c2fe30bde2e3d49744e134c7d83a04f47b0437d09b6f8743e0023be67965171</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3723,12 +3755,12 @@
       </c>
       <c r="BG9" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T17:30:26.042854Z</t>
+          <t>2026-08-01T20:33:06.494162Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3738,13 +3770,13 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>-233</v>
+        <v>-203</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.492611</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.669967</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
@@ -3778,22 +3810,22 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>c4c4b0a1d20f4a80</t>
+          <t>612fd0dd1f434502</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T17:30:31.285539Z</t>
+          <t>2026-08-01T21:24:40.423686Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T19:00:00Z</t>
+          <t>2026-08-02T08:00:00Z</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>61860</t>
+          <t>66788</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -3803,12 +3835,12 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion Black</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>2GAME Esports</t>
+          <t>VARREL</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr">
@@ -3828,63 +3860,49 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>-223</v>
+        <v>-138</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.724638</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.579832</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.522953</v>
+        <v>0.677597</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>-0.167449</v>
+        <v>0.097765</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="S10" s="29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T10" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U10" s="24" t="inlineStr">
         <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="W10" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" s="26" t="n">
-        <v>0</v>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="n"/>
+      <c r="W10" s="26" t="n"/>
+      <c r="X10" s="26" t="n"/>
       <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T23:37:10.553380Z</t>
-        </is>
-      </c>
+      <c r="AC10" s="30" t="n"/>
+      <c r="AD10" s="24" t="n"/>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-2game-srb-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-valorant-var-krx-2026-08-02).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -3902,7 +3920,7 @@
       <c r="AJ10" s="31" t="n"/>
       <c r="AK10" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL10" s="26" t="n">
@@ -3910,47 +3928,47 @@
       </c>
       <c r="AM10" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN10" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO10" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP10" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion Black</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AQ10" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion Black</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AR10" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion Black</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AS10" s="24" t="inlineStr">
         <is>
-          <t>2GAME Esports</t>
+          <t>VARREL</t>
         </is>
       </c>
       <c r="AT10" s="24" t="inlineStr">
         <is>
-          <t>2GAME Esports</t>
+          <t>VARREL</t>
         </is>
       </c>
       <c r="AU10" s="24" t="inlineStr">
         <is>
-          <t>2GAME Esports</t>
+          <t>VARREL</t>
         </is>
       </c>
       <c r="AV10" s="24" t="n"/>
@@ -3968,7 +3986,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>8c22ec58fb547190beefa169a52f11eae99a49cdfc2b416003beb11aad6b9129</t>
+          <t>3d9fb2e99557b8380ebae212c50f062d30d580c0a2a0d2fab1fc8860b2260810</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -3978,12 +3996,12 @@
       </c>
       <c r="BC10" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>8c22ec58fb547190beefa169a52f11eae99a49cdfc2b416003beb11aad6b9129</t>
+          <t>3d9fb2e99557b8380ebae212c50f062d30d580c0a2a0d2fab1fc8860b2260810</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -3998,12 +4016,12 @@
       </c>
       <c r="BG10" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T17:30:26.970466Z</t>
+          <t>2026-08-01T21:24:32.281041Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4013,13 +4031,13 @@
       </c>
       <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
-        <v>-223</v>
+        <v>-138</v>
       </c>
       <c r="BL10" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.724638</v>
       </c>
       <c r="BM10" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.579832</v>
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
@@ -4053,22 +4071,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>398e854789b541a8</t>
+          <t>ff19a597303a4200</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-29T12:04:22.575418Z</t>
+          <t>2026-08-01T21:24:40.423686Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-29T15:00:00Z</t>
+          <t>2026-08-02T18:00:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>62689</t>
+          <t>66957</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -4078,12 +4096,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>G2 Gozen</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4093,7 +4111,7 @@
       </c>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J11" s="25" t="n"/>
@@ -4103,63 +4121,49 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>108</v>
+        <v>-122</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>2.08</v>
+        <v>1.819672</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.54955</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.714884</v>
+        <v>0.538226</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.234115</v>
+        <v>-0.011324</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="S11" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U11" s="24" t="inlineStr">
         <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W11" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" s="26" t="n">
-        <v>0</v>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
       <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AD11" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-29T17:34:38.982032Z</t>
-        </is>
-      </c>
+      <c r="AC11" s="30" t="n"/>
+      <c r="AD11" s="24" t="n"/>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-valorant-skn-ggo-2026-07-29).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-valorant-fnc-th-2026-08-02).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4169,7 +4173,7 @@
       </c>
       <c r="AG11" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH11" s="24" t="n"/>
@@ -4177,7 +4181,7 @@
       <c r="AJ11" s="31" t="n"/>
       <c r="AK11" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL11" s="26" t="n">
@@ -4185,47 +4189,47 @@
       </c>
       <c r="AM11" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN11" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO11" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>G2 Gozen</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>G2 Gozen</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>G2 Gozen</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4243,7 +4247,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>e33860310416f9b2d86e5c1e14a7bffcebc7a1e4c8af04b416cd37235fd4b6cf</t>
+          <t>3d9fb2e99557b8380ebae212c50f062d30d580c0a2a0d2fab1fc8860b2260810</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4253,12 +4257,12 @@
       </c>
       <c r="BC11" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>e33860310416f9b2d86e5c1e14a7bffcebc7a1e4c8af04b416cd37235fd4b6cf</t>
+          <t>3d9fb2e99557b8380ebae212c50f062d30d580c0a2a0d2fab1fc8860b2260810</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4273,12 +4277,12 @@
       </c>
       <c r="BG11" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-29T12:04:15.273824Z</t>
+          <t>2026-08-01T21:24:33.723797Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4288,13 +4292,13 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>108</v>
+        <v>-122</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>2.08</v>
+        <v>1.819672</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.54955</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
@@ -4328,22 +4332,22 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>e4d0445522234209</t>
+          <t>fa5cdd9d69684e07</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-29T17:48:33.149264Z</t>
+          <t>2026-08-01T21:24:40.423686Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-29T18:00:00Z</t>
+          <t>2026-08-02T21:00:00Z</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>62925</t>
+          <t>67311</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4353,12 +4357,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>KRÜ Esports</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>GIANTX GC</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4368,7 +4372,7 @@
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J12" s="25" t="n"/>
@@ -4378,63 +4382,49 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-163</v>
+        <v>133</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.33</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.429185</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.570358</v>
+        <v>0.518417</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>-0.049414</v>
+        <v>0.08923200000000001</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S12" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="W12" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" s="26" t="n">
-        <v>0</v>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="26" t="n"/>
       <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T04:12:59.884655Z</t>
-        </is>
-      </c>
+      <c r="AC12" s="30" t="n"/>
+      <c r="AD12" s="24" t="n"/>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-valorant-gxgc-hbs-2026-07-29).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-valorant-c9-kr-2026-08-02).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4475,32 +4465,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>KRÜ Esports</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>KRÜ Esports</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>KRÜ Esports</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>GIANTX GC</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>GIANTX GC</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>GIANTX GC</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4518,7 +4508,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>71696e637dd05bc7933e2bdcf627a39cf9f10c85a7ad852765447d083e849a9e</t>
+          <t>3d9fb2e99557b8380ebae212c50f062d30d580c0a2a0d2fab1fc8860b2260810</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4528,12 +4518,12 @@
       </c>
       <c r="BC12" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>71696e637dd05bc7933e2bdcf627a39cf9f10c85a7ad852765447d083e849a9e</t>
+          <t>3d9fb2e99557b8380ebae212c50f062d30d580c0a2a0d2fab1fc8860b2260810</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4548,12 +4538,12 @@
       </c>
       <c r="BG12" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-29T17:48:26.246789Z</t>
+          <t>2026-08-01T21:24:34.260410Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4563,13 +4553,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-163</v>
+        <v>133</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.33</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.429185</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
@@ -4600,2383 +4590,6 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
     </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>6bc0a09d5f1d41d8</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-29T17:48:33.149264Z</t>
-        </is>
-      </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>64563</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F13" s="24" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="G13" s="24" t="inlineStr">
-        <is>
-          <t>100 Thieves</t>
-        </is>
-      </c>
-      <c r="H13" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I13" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J13" s="25" t="n"/>
-      <c r="K13" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L13" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="M13" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="N13" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="O13" s="28" t="n">
-        <v>0.827349</v>
-      </c>
-      <c r="P13" s="28" t="n"/>
-      <c r="Q13" s="28" t="n">
-        <v>0.127649</v>
-      </c>
-      <c r="R13" s="26" t="n">
-        <v>84</v>
-      </c>
-      <c r="S13" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U13" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
-      <c r="Y13" s="25" t="n"/>
-      <c r="Z13" s="26" t="n"/>
-      <c r="AA13" s="28" t="n"/>
-      <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
-      <c r="AE13" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-valorant-100t-sen-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF13" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG13" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH13" s="24" t="n"/>
-      <c r="AI13" s="31" t="n"/>
-      <c r="AJ13" s="31" t="n"/>
-      <c r="AK13" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL13" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM13" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN13" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO13" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP13" s="24" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="AQ13" s="24" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="AR13" s="24" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="AS13" s="24" t="inlineStr">
-        <is>
-          <t>100 Thieves</t>
-        </is>
-      </c>
-      <c r="AT13" s="24" t="inlineStr">
-        <is>
-          <t>100 Thieves</t>
-        </is>
-      </c>
-      <c r="AU13" s="24" t="inlineStr">
-        <is>
-          <t>100 Thieves</t>
-        </is>
-      </c>
-      <c r="AV13" s="24" t="n"/>
-      <c r="AW13" s="24" t="n"/>
-      <c r="AX13" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY13" s="24" t="n"/>
-      <c r="AZ13" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA13" s="24" t="inlineStr">
-        <is>
-          <t>71696e637dd05bc7933e2bdcf627a39cf9f10c85a7ad852765447d083e849a9e</t>
-        </is>
-      </c>
-      <c r="BB13" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC13" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD13" s="24" t="inlineStr">
-        <is>
-          <t>71696e637dd05bc7933e2bdcf627a39cf9f10c85a7ad852765447d083e849a9e</t>
-        </is>
-      </c>
-      <c r="BE13" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF13" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG13" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH13" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-29T17:48:33.146517Z</t>
-        </is>
-      </c>
-      <c r="BI13" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ13" s="25" t="n"/>
-      <c r="BK13" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="BL13" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="BM13" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="BN13" s="28" t="n"/>
-      <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
-      <c r="BR13" s="28" t="n"/>
-      <c r="BS13" s="28" t="n"/>
-      <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="25" t="n"/>
-      <c r="BV13" s="29" t="n"/>
-      <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="30" t="n"/>
-      <c r="BY13" s="27" t="n"/>
-      <c r="BZ13" s="24" t="n"/>
-      <c r="CA13" s="31" t="n"/>
-      <c r="CB13" s="24" t="n"/>
-      <c r="CC13" s="24" t="n"/>
-      <c r="CD13" s="24" t="n"/>
-      <c r="CE13" s="24" t="n"/>
-      <c r="CF13" s="24" t="n"/>
-      <c r="CG13" s="24" t="n"/>
-      <c r="CH13" s="24" t="n"/>
-      <c r="CI13" s="24" t="n"/>
-      <c r="CJ13" s="24" t="n"/>
-      <c r="CK13" s="24" t="n"/>
-      <c r="CL13" s="24" t="n"/>
-      <c r="CM13" s="24" t="n"/>
-      <c r="CN13" s="24" t="n"/>
-      <c r="CO13" s="24" t="n"/>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>8b7dbdba26114d37</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T07:24:48.854145Z</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>63626</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F14" s="24" t="inlineStr">
-        <is>
-          <t>DetonatioN FocusMe</t>
-        </is>
-      </c>
-      <c r="G14" s="24" t="inlineStr">
-        <is>
-          <t>VARREL</t>
-        </is>
-      </c>
-      <c r="H14" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L14" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="M14" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="N14" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="O14" s="28" t="n">
-        <v>0.604202</v>
-      </c>
-      <c r="P14" s="28" t="n"/>
-      <c r="Q14" s="28" t="n">
-        <v>0.02437</v>
-      </c>
-      <c r="R14" s="26" t="n">
-        <v>32</v>
-      </c>
-      <c r="S14" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T14" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U14" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W14" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="25" t="n"/>
-      <c r="Z14" s="26" t="n"/>
-      <c r="AA14" s="28" t="n"/>
-      <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AD14" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T13:30:56.650021Z</t>
-        </is>
-      </c>
-      <c r="AE14" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-valorant-var-dfm-2026-07-30).</t>
-        </is>
-      </c>
-      <c r="AF14" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG14" s="24" t="inlineStr">
-        <is>
-          <t>review_required</t>
-        </is>
-      </c>
-      <c r="AH14" s="24" t="n"/>
-      <c r="AI14" s="31" t="n"/>
-      <c r="AJ14" s="31" t="n"/>
-      <c r="AK14" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL14" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM14" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN14" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO14" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP14" s="24" t="inlineStr">
-        <is>
-          <t>DetonatioN FocusMe</t>
-        </is>
-      </c>
-      <c r="AQ14" s="24" t="inlineStr">
-        <is>
-          <t>DetonatioN FocusMe</t>
-        </is>
-      </c>
-      <c r="AR14" s="24" t="inlineStr">
-        <is>
-          <t>DetonatioN FocusMe</t>
-        </is>
-      </c>
-      <c r="AS14" s="24" t="inlineStr">
-        <is>
-          <t>VARREL</t>
-        </is>
-      </c>
-      <c r="AT14" s="24" t="inlineStr">
-        <is>
-          <t>VARREL</t>
-        </is>
-      </c>
-      <c r="AU14" s="24" t="inlineStr">
-        <is>
-          <t>VARREL</t>
-        </is>
-      </c>
-      <c r="AV14" s="24" t="n"/>
-      <c r="AW14" s="24" t="n"/>
-      <c r="AX14" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY14" s="24" t="n"/>
-      <c r="AZ14" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA14" s="24" t="inlineStr">
-        <is>
-          <t>065060c5427d777daf1c2c539c66a4917e7e7a09bf311e9c39e713455cc3d93a</t>
-        </is>
-      </c>
-      <c r="BB14" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC14" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD14" s="24" t="inlineStr">
-        <is>
-          <t>065060c5427d777daf1c2c539c66a4917e7e7a09bf311e9c39e713455cc3d93a</t>
-        </is>
-      </c>
-      <c r="BE14" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF14" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG14" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH14" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T07:24:41.203557Z</t>
-        </is>
-      </c>
-      <c r="BI14" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ14" s="25" t="n"/>
-      <c r="BK14" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="BL14" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="BM14" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="BN14" s="28" t="n"/>
-      <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
-      <c r="BR14" s="28" t="n"/>
-      <c r="BS14" s="28" t="n"/>
-      <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="25" t="n"/>
-      <c r="BV14" s="29" t="n"/>
-      <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="30" t="n"/>
-      <c r="BY14" s="27" t="n"/>
-      <c r="BZ14" s="24" t="n"/>
-      <c r="CA14" s="31" t="n"/>
-      <c r="CB14" s="24" t="n"/>
-      <c r="CC14" s="24" t="n"/>
-      <c r="CD14" s="24" t="n"/>
-      <c r="CE14" s="24" t="n"/>
-      <c r="CF14" s="24" t="n"/>
-      <c r="CG14" s="24" t="n"/>
-      <c r="CH14" s="24" t="n"/>
-      <c r="CI14" s="24" t="n"/>
-      <c r="CJ14" s="24" t="n"/>
-      <c r="CK14" s="24" t="n"/>
-      <c r="CL14" s="24" t="n"/>
-      <c r="CM14" s="24" t="n"/>
-      <c r="CN14" s="24" t="n"/>
-      <c r="CO14" s="24" t="n"/>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>97f817da629d4166</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T13:36:25.155439Z</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>63802</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="G15" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L15" s="26" t="n">
-        <v>-203</v>
-      </c>
-      <c r="M15" s="27" t="n">
-        <v>1.492611</v>
-      </c>
-      <c r="N15" s="28" t="n">
-        <v>0.669967</v>
-      </c>
-      <c r="O15" s="28" t="n">
-        <v>0.617757</v>
-      </c>
-      <c r="P15" s="28" t="n"/>
-      <c r="Q15" s="28" t="n">
-        <v>-0.05221</v>
-      </c>
-      <c r="R15" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U15" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="W15" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:22:57.072609Z</t>
-        </is>
-      </c>
-      <c r="AE15" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-valorant-skn-hbs-2026-07-30).</t>
-        </is>
-      </c>
-      <c r="AF15" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG15" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH15" s="24" t="n"/>
-      <c r="AI15" s="31" t="n"/>
-      <c r="AJ15" s="31" t="n"/>
-      <c r="AK15" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL15" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM15" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN15" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO15" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP15" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="AQ15" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="AR15" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="AS15" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="AT15" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="AU15" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="AV15" s="24" t="n"/>
-      <c r="AW15" s="24" t="n"/>
-      <c r="AX15" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY15" s="24" t="n"/>
-      <c r="AZ15" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA15" s="24" t="inlineStr">
-        <is>
-          <t>19b7365606ae48f9e7f41f552cee9b921f9088cc133ddb61af3a4f42a2a76e52</t>
-        </is>
-      </c>
-      <c r="BB15" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC15" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD15" s="24" t="inlineStr">
-        <is>
-          <t>19b7365606ae48f9e7f41f552cee9b921f9088cc133ddb61af3a4f42a2a76e52</t>
-        </is>
-      </c>
-      <c r="BE15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG15" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH15" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T13:36:18.680042Z</t>
-        </is>
-      </c>
-      <c r="BI15" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ15" s="25" t="n"/>
-      <c r="BK15" s="26" t="n">
-        <v>-203</v>
-      </c>
-      <c r="BL15" s="27" t="n">
-        <v>1.492611</v>
-      </c>
-      <c r="BM15" s="28" t="n">
-        <v>0.669967</v>
-      </c>
-      <c r="BN15" s="28" t="n"/>
-      <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
-      <c r="BS15" s="28" t="n"/>
-      <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
-      <c r="BV15" s="29" t="n"/>
-      <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n"/>
-      <c r="BY15" s="27" t="n"/>
-      <c r="BZ15" s="24" t="n"/>
-      <c r="CA15" s="31" t="n"/>
-      <c r="CB15" s="24" t="n"/>
-      <c r="CC15" s="24" t="n"/>
-      <c r="CD15" s="24" t="n"/>
-      <c r="CE15" s="24" t="n"/>
-      <c r="CF15" s="24" t="n"/>
-      <c r="CG15" s="24" t="n"/>
-      <c r="CH15" s="24" t="n"/>
-      <c r="CI15" s="24" t="n"/>
-      <c r="CJ15" s="24" t="n"/>
-      <c r="CK15" s="24" t="n"/>
-      <c r="CL15" s="24" t="n"/>
-      <c r="CM15" s="24" t="n"/>
-      <c r="CN15" s="24" t="n"/>
-      <c r="CO15" s="24" t="n"/>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>1113ab0c534445c4</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:40:05.919152Z</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>64030</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>ALTERNATE aTTaX Ruby</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>GIANTX GC</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L16" s="26" t="n">
-        <v>-170</v>
-      </c>
-      <c r="M16" s="27" t="n">
-        <v>1.588235</v>
-      </c>
-      <c r="N16" s="28" t="n">
-        <v>0.62963</v>
-      </c>
-      <c r="O16" s="28" t="n">
-        <v>0.608585</v>
-      </c>
-      <c r="P16" s="28" t="n"/>
-      <c r="Q16" s="28" t="n">
-        <v>-0.021045</v>
-      </c>
-      <c r="R16" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="S16" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U16" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
-      <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
-      <c r="AE16" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-valorant-gxgc-aar-2026-07-30).</t>
-        </is>
-      </c>
-      <c r="AF16" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG16" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH16" s="24" t="n"/>
-      <c r="AI16" s="31" t="n"/>
-      <c r="AJ16" s="31" t="n"/>
-      <c r="AK16" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL16" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM16" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN16" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO16" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP16" s="24" t="inlineStr">
-        <is>
-          <t>ALTERNATE aTTaX Ruby</t>
-        </is>
-      </c>
-      <c r="AQ16" s="24" t="inlineStr">
-        <is>
-          <t>ALTERNATE aTTaX Ruby</t>
-        </is>
-      </c>
-      <c r="AR16" s="24" t="inlineStr">
-        <is>
-          <t>ALTERNATE aTTaX Ruby</t>
-        </is>
-      </c>
-      <c r="AS16" s="24" t="inlineStr">
-        <is>
-          <t>GIANTX GC</t>
-        </is>
-      </c>
-      <c r="AT16" s="24" t="inlineStr">
-        <is>
-          <t>GIANTX GC</t>
-        </is>
-      </c>
-      <c r="AU16" s="24" t="inlineStr">
-        <is>
-          <t>GIANTX GC</t>
-        </is>
-      </c>
-      <c r="AV16" s="24" t="n"/>
-      <c r="AW16" s="24" t="n"/>
-      <c r="AX16" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY16" s="24" t="n"/>
-      <c r="AZ16" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA16" s="24" t="inlineStr">
-        <is>
-          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
-        </is>
-      </c>
-      <c r="BB16" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC16" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD16" s="24" t="inlineStr">
-        <is>
-          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
-        </is>
-      </c>
-      <c r="BE16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG16" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH16" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:40:00.750113Z</t>
-        </is>
-      </c>
-      <c r="BI16" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ16" s="25" t="n"/>
-      <c r="BK16" s="26" t="n">
-        <v>-170</v>
-      </c>
-      <c r="BL16" s="27" t="n">
-        <v>1.588235</v>
-      </c>
-      <c r="BM16" s="28" t="n">
-        <v>0.62963</v>
-      </c>
-      <c r="BN16" s="28" t="n"/>
-      <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
-      <c r="BS16" s="28" t="n"/>
-      <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
-      <c r="BV16" s="29" t="n"/>
-      <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n"/>
-      <c r="BY16" s="27" t="n"/>
-      <c r="BZ16" s="24" t="n"/>
-      <c r="CA16" s="31" t="n"/>
-      <c r="CB16" s="24" t="n"/>
-      <c r="CC16" s="24" t="n"/>
-      <c r="CD16" s="24" t="n"/>
-      <c r="CE16" s="24" t="n"/>
-      <c r="CF16" s="24" t="n"/>
-      <c r="CG16" s="24" t="n"/>
-      <c r="CH16" s="24" t="n"/>
-      <c r="CI16" s="24" t="n"/>
-      <c r="CJ16" s="24" t="n"/>
-      <c r="CK16" s="24" t="n"/>
-      <c r="CL16" s="24" t="n"/>
-      <c r="CM16" s="24" t="n"/>
-      <c r="CN16" s="24" t="n"/>
-      <c r="CO16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>68a535f0c5a74e04</t>
-        </is>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:40:05.919152Z</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>64031</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F17" s="24" t="inlineStr">
-        <is>
-          <t>Fnatic</t>
-        </is>
-      </c>
-      <c r="G17" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Fire</t>
-        </is>
-      </c>
-      <c r="H17" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L17" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="M17" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="N17" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="O17" s="28" t="n">
-        <v>0.645947</v>
-      </c>
-      <c r="P17" s="28" t="n"/>
-      <c r="Q17" s="28" t="n">
-        <v>0.096397</v>
-      </c>
-      <c r="R17" s="26" t="n">
-        <v>68</v>
-      </c>
-      <c r="S17" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U17" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
-      <c r="Y17" s="25" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n"/>
-      <c r="AD17" s="24" t="n"/>
-      <c r="AE17" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-valorant-ef-fnc-2026-07-30).</t>
-        </is>
-      </c>
-      <c r="AF17" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG17" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH17" s="24" t="n"/>
-      <c r="AI17" s="31" t="n"/>
-      <c r="AJ17" s="31" t="n"/>
-      <c r="AK17" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL17" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM17" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN17" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO17" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP17" s="24" t="inlineStr">
-        <is>
-          <t>Fnatic</t>
-        </is>
-      </c>
-      <c r="AQ17" s="24" t="inlineStr">
-        <is>
-          <t>Fnatic</t>
-        </is>
-      </c>
-      <c r="AR17" s="24" t="inlineStr">
-        <is>
-          <t>Fnatic</t>
-        </is>
-      </c>
-      <c r="AS17" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Fire</t>
-        </is>
-      </c>
-      <c r="AT17" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Fire</t>
-        </is>
-      </c>
-      <c r="AU17" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Fire</t>
-        </is>
-      </c>
-      <c r="AV17" s="24" t="n"/>
-      <c r="AW17" s="24" t="n"/>
-      <c r="AX17" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY17" s="24" t="n"/>
-      <c r="AZ17" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA17" s="24" t="inlineStr">
-        <is>
-          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
-        </is>
-      </c>
-      <c r="BB17" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC17" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD17" s="24" t="inlineStr">
-        <is>
-          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
-        </is>
-      </c>
-      <c r="BE17" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF17" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG17" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH17" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:40:01.228013Z</t>
-        </is>
-      </c>
-      <c r="BI17" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ17" s="25" t="n"/>
-      <c r="BK17" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="BL17" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="BM17" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="BN17" s="28" t="n"/>
-      <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
-      <c r="BR17" s="28" t="n"/>
-      <c r="BS17" s="28" t="n"/>
-      <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="25" t="n"/>
-      <c r="BV17" s="29" t="n"/>
-      <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="30" t="n"/>
-      <c r="BY17" s="27" t="n"/>
-      <c r="BZ17" s="24" t="n"/>
-      <c r="CA17" s="31" t="n"/>
-      <c r="CB17" s="24" t="n"/>
-      <c r="CC17" s="24" t="n"/>
-      <c r="CD17" s="24" t="n"/>
-      <c r="CE17" s="24" t="n"/>
-      <c r="CF17" s="24" t="n"/>
-      <c r="CG17" s="24" t="n"/>
-      <c r="CH17" s="24" t="n"/>
-      <c r="CI17" s="24" t="n"/>
-      <c r="CJ17" s="24" t="n"/>
-      <c r="CK17" s="24" t="n"/>
-      <c r="CL17" s="24" t="n"/>
-      <c r="CM17" s="24" t="n"/>
-      <c r="CN17" s="24" t="n"/>
-      <c r="CO17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>e719fd5d68c24cb2</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:40:05.919152Z</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>64028</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="G18" s="24" t="inlineStr">
-        <is>
-          <t>G2 Gozen</t>
-        </is>
-      </c>
-      <c r="H18" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J18" s="25" t="n"/>
-      <c r="K18" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L18" s="26" t="n">
-        <v>127</v>
-      </c>
-      <c r="M18" s="27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="N18" s="28" t="n">
-        <v>0.440529</v>
-      </c>
-      <c r="O18" s="28" t="n">
-        <v>0.6363760000000001</v>
-      </c>
-      <c r="P18" s="28" t="n"/>
-      <c r="Q18" s="28" t="n">
-        <v>0.195847</v>
-      </c>
-      <c r="R18" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S18" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T18" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U18" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
-      <c r="Y18" s="25" t="n"/>
-      <c r="Z18" s="26" t="n"/>
-      <c r="AA18" s="28" t="n"/>
-      <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n"/>
-      <c r="AD18" s="24" t="n"/>
-      <c r="AE18" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-valorant-ggo-tmo-2026-07-30).</t>
-        </is>
-      </c>
-      <c r="AF18" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG18" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH18" s="24" t="n"/>
-      <c r="AI18" s="31" t="n"/>
-      <c r="AJ18" s="31" t="n"/>
-      <c r="AK18" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL18" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM18" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN18" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO18" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP18" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="AQ18" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="AR18" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="AS18" s="24" t="inlineStr">
-        <is>
-          <t>G2 Gozen</t>
-        </is>
-      </c>
-      <c r="AT18" s="24" t="inlineStr">
-        <is>
-          <t>G2 Gozen</t>
-        </is>
-      </c>
-      <c r="AU18" s="24" t="inlineStr">
-        <is>
-          <t>G2 Gozen</t>
-        </is>
-      </c>
-      <c r="AV18" s="24" t="n"/>
-      <c r="AW18" s="24" t="n"/>
-      <c r="AX18" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY18" s="24" t="n"/>
-      <c r="AZ18" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA18" s="24" t="inlineStr">
-        <is>
-          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
-        </is>
-      </c>
-      <c r="BB18" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC18" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD18" s="24" t="inlineStr">
-        <is>
-          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
-        </is>
-      </c>
-      <c r="BE18" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF18" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG18" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH18" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:40:01.726408Z</t>
-        </is>
-      </c>
-      <c r="BI18" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ18" s="25" t="n"/>
-      <c r="BK18" s="26" t="n">
-        <v>127</v>
-      </c>
-      <c r="BL18" s="27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BM18" s="28" t="n">
-        <v>0.440529</v>
-      </c>
-      <c r="BN18" s="28" t="n"/>
-      <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
-      <c r="BR18" s="28" t="n"/>
-      <c r="BS18" s="28" t="n"/>
-      <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="25" t="n"/>
-      <c r="BV18" s="29" t="n"/>
-      <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="30" t="n"/>
-      <c r="BY18" s="27" t="n"/>
-      <c r="BZ18" s="24" t="n"/>
-      <c r="CA18" s="31" t="n"/>
-      <c r="CB18" s="24" t="n"/>
-      <c r="CC18" s="24" t="n"/>
-      <c r="CD18" s="24" t="n"/>
-      <c r="CE18" s="24" t="n"/>
-      <c r="CF18" s="24" t="n"/>
-      <c r="CG18" s="24" t="n"/>
-      <c r="CH18" s="24" t="n"/>
-      <c r="CI18" s="24" t="n"/>
-      <c r="CJ18" s="24" t="n"/>
-      <c r="CK18" s="24" t="n"/>
-      <c r="CL18" s="24" t="n"/>
-      <c r="CM18" s="24" t="n"/>
-      <c r="CN18" s="24" t="n"/>
-      <c r="CO18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>d25d1add789a4af4</t>
-        </is>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:40:05.919152Z</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>64807</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F19" s="24" t="inlineStr">
-        <is>
-          <t>Gen.G Esports</t>
-        </is>
-      </c>
-      <c r="G19" s="24" t="inlineStr">
-        <is>
-          <t>Global Esports</t>
-        </is>
-      </c>
-      <c r="H19" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J19" s="25" t="n"/>
-      <c r="K19" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L19" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="M19" s="27" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="N19" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="O19" s="28" t="n">
-        <v>0.581533</v>
-      </c>
-      <c r="P19" s="28" t="n"/>
-      <c r="Q19" s="28" t="n">
-        <v>0.062302</v>
-      </c>
-      <c r="R19" s="26" t="n">
-        <v>51</v>
-      </c>
-      <c r="S19" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T19" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U19" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
-      <c r="Y19" s="25" t="n"/>
-      <c r="Z19" s="26" t="n"/>
-      <c r="AA19" s="28" t="n"/>
-      <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n"/>
-      <c r="AD19" s="24" t="n"/>
-      <c r="AE19" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-valorant-ge-geng-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF19" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG19" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH19" s="24" t="n"/>
-      <c r="AI19" s="31" t="n"/>
-      <c r="AJ19" s="31" t="n"/>
-      <c r="AK19" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL19" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM19" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN19" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO19" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP19" s="24" t="inlineStr">
-        <is>
-          <t>Gen.G Esports</t>
-        </is>
-      </c>
-      <c r="AQ19" s="24" t="inlineStr">
-        <is>
-          <t>Gen.G Esports</t>
-        </is>
-      </c>
-      <c r="AR19" s="24" t="inlineStr">
-        <is>
-          <t>Gen.G Esports</t>
-        </is>
-      </c>
-      <c r="AS19" s="24" t="inlineStr">
-        <is>
-          <t>Global Esports</t>
-        </is>
-      </c>
-      <c r="AT19" s="24" t="inlineStr">
-        <is>
-          <t>Global Esports</t>
-        </is>
-      </c>
-      <c r="AU19" s="24" t="inlineStr">
-        <is>
-          <t>Global Esports</t>
-        </is>
-      </c>
-      <c r="AV19" s="24" t="n"/>
-      <c r="AW19" s="24" t="n"/>
-      <c r="AX19" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY19" s="24" t="n"/>
-      <c r="AZ19" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA19" s="24" t="inlineStr">
-        <is>
-          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
-        </is>
-      </c>
-      <c r="BB19" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC19" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD19" s="24" t="inlineStr">
-        <is>
-          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
-        </is>
-      </c>
-      <c r="BE19" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF19" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG19" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH19" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:40:03.847842Z</t>
-        </is>
-      </c>
-      <c r="BI19" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ19" s="25" t="n"/>
-      <c r="BK19" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="BL19" s="27" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="BM19" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="BN19" s="28" t="n"/>
-      <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
-      <c r="BR19" s="28" t="n"/>
-      <c r="BS19" s="28" t="n"/>
-      <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="25" t="n"/>
-      <c r="BV19" s="29" t="n"/>
-      <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="30" t="n"/>
-      <c r="BY19" s="27" t="n"/>
-      <c r="BZ19" s="24" t="n"/>
-      <c r="CA19" s="31" t="n"/>
-      <c r="CB19" s="24" t="n"/>
-      <c r="CC19" s="24" t="n"/>
-      <c r="CD19" s="24" t="n"/>
-      <c r="CE19" s="24" t="n"/>
-      <c r="CF19" s="24" t="n"/>
-      <c r="CG19" s="24" t="n"/>
-      <c r="CH19" s="24" t="n"/>
-      <c r="CI19" s="24" t="n"/>
-      <c r="CJ19" s="24" t="n"/>
-      <c r="CK19" s="24" t="n"/>
-      <c r="CL19" s="24" t="n"/>
-      <c r="CM19" s="24" t="n"/>
-      <c r="CN19" s="24" t="n"/>
-      <c r="CO19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>ae6059556eb94566</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:40:05.919152Z</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>64940</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F20" s="24" t="inlineStr">
-        <is>
-          <t>Gentle Mates</t>
-        </is>
-      </c>
-      <c r="G20" s="24" t="inlineStr">
-        <is>
-          <t>BBL Esports</t>
-        </is>
-      </c>
-      <c r="H20" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="n"/>
-      <c r="K20" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L20" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="M20" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="N20" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="O20" s="28" t="n">
-        <v>0.6034080000000001</v>
-      </c>
-      <c r="P20" s="28" t="n"/>
-      <c r="Q20" s="28" t="n">
-        <v>0.032593</v>
-      </c>
-      <c r="R20" s="26" t="n">
-        <v>36</v>
-      </c>
-      <c r="S20" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T20" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U20" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V20" s="24" t="n"/>
-      <c r="W20" s="26" t="n"/>
-      <c r="X20" s="26" t="n"/>
-      <c r="Y20" s="25" t="n"/>
-      <c r="Z20" s="26" t="n"/>
-      <c r="AA20" s="28" t="n"/>
-      <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n"/>
-      <c r="AD20" s="24" t="n"/>
-      <c r="AE20" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-valorant-bbl-gm-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF20" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG20" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH20" s="24" t="n"/>
-      <c r="AI20" s="31" t="n"/>
-      <c r="AJ20" s="31" t="n"/>
-      <c r="AK20" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL20" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM20" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN20" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO20" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP20" s="24" t="inlineStr">
-        <is>
-          <t>Gentle Mates</t>
-        </is>
-      </c>
-      <c r="AQ20" s="24" t="inlineStr">
-        <is>
-          <t>Gentle Mates</t>
-        </is>
-      </c>
-      <c r="AR20" s="24" t="inlineStr">
-        <is>
-          <t>Gentle Mates</t>
-        </is>
-      </c>
-      <c r="AS20" s="24" t="inlineStr">
-        <is>
-          <t>BBL Esports</t>
-        </is>
-      </c>
-      <c r="AT20" s="24" t="inlineStr">
-        <is>
-          <t>BBL Esports</t>
-        </is>
-      </c>
-      <c r="AU20" s="24" t="inlineStr">
-        <is>
-          <t>BBL Esports</t>
-        </is>
-      </c>
-      <c r="AV20" s="24" t="n"/>
-      <c r="AW20" s="24" t="n"/>
-      <c r="AX20" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY20" s="24" t="n"/>
-      <c r="AZ20" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA20" s="24" t="inlineStr">
-        <is>
-          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
-        </is>
-      </c>
-      <c r="BB20" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC20" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD20" s="24" t="inlineStr">
-        <is>
-          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
-        </is>
-      </c>
-      <c r="BE20" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF20" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG20" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH20" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:40:04.331936Z</t>
-        </is>
-      </c>
-      <c r="BI20" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ20" s="25" t="n"/>
-      <c r="BK20" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="BL20" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="BM20" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="BN20" s="28" t="n"/>
-      <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
-      <c r="BR20" s="28" t="n"/>
-      <c r="BS20" s="28" t="n"/>
-      <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="25" t="n"/>
-      <c r="BV20" s="29" t="n"/>
-      <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="30" t="n"/>
-      <c r="BY20" s="27" t="n"/>
-      <c r="BZ20" s="24" t="n"/>
-      <c r="CA20" s="31" t="n"/>
-      <c r="CB20" s="24" t="n"/>
-      <c r="CC20" s="24" t="n"/>
-      <c r="CD20" s="24" t="n"/>
-      <c r="CE20" s="24" t="n"/>
-      <c r="CF20" s="24" t="n"/>
-      <c r="CG20" s="24" t="n"/>
-      <c r="CH20" s="24" t="n"/>
-      <c r="CI20" s="24" t="n"/>
-      <c r="CJ20" s="24" t="n"/>
-      <c r="CK20" s="24" t="n"/>
-      <c r="CL20" s="24" t="n"/>
-      <c r="CM20" s="24" t="n"/>
-      <c r="CN20" s="24" t="n"/>
-      <c r="CO20" s="24" t="n"/>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>0a9580a1a6d04bfb</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:40:05.919152Z</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>65506</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F21" s="24" t="inlineStr">
-        <is>
-          <t>LOUD</t>
-        </is>
-      </c>
-      <c r="G21" s="24" t="inlineStr">
-        <is>
-          <t>Cloud9</t>
-        </is>
-      </c>
-      <c r="H21" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I21" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J21" s="25" t="n"/>
-      <c r="K21" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L21" s="26" t="n">
-        <v>-117</v>
-      </c>
-      <c r="M21" s="27" t="n">
-        <v>1.854701</v>
-      </c>
-      <c r="N21" s="28" t="n">
-        <v>0.539171</v>
-      </c>
-      <c r="O21" s="28" t="n">
-        <v>0.649081</v>
-      </c>
-      <c r="P21" s="28" t="n"/>
-      <c r="Q21" s="28" t="n">
-        <v>0.10991</v>
-      </c>
-      <c r="R21" s="26" t="n">
-        <v>75</v>
-      </c>
-      <c r="S21" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U21" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
-      <c r="Y21" s="25" t="n"/>
-      <c r="Z21" s="26" t="n"/>
-      <c r="AA21" s="28" t="n"/>
-      <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n"/>
-      <c r="AD21" s="24" t="n"/>
-      <c r="AE21" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-valorant-c9-loud-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF21" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG21" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH21" s="24" t="n"/>
-      <c r="AI21" s="31" t="n"/>
-      <c r="AJ21" s="31" t="n"/>
-      <c r="AK21" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL21" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM21" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN21" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO21" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP21" s="24" t="inlineStr">
-        <is>
-          <t>LOUD</t>
-        </is>
-      </c>
-      <c r="AQ21" s="24" t="inlineStr">
-        <is>
-          <t>LOUD</t>
-        </is>
-      </c>
-      <c r="AR21" s="24" t="inlineStr">
-        <is>
-          <t>LOUD</t>
-        </is>
-      </c>
-      <c r="AS21" s="24" t="inlineStr">
-        <is>
-          <t>Cloud9</t>
-        </is>
-      </c>
-      <c r="AT21" s="24" t="inlineStr">
-        <is>
-          <t>Cloud9</t>
-        </is>
-      </c>
-      <c r="AU21" s="24" t="inlineStr">
-        <is>
-          <t>Cloud9</t>
-        </is>
-      </c>
-      <c r="AV21" s="24" t="n"/>
-      <c r="AW21" s="24" t="n"/>
-      <c r="AX21" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY21" s="24" t="n"/>
-      <c r="AZ21" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA21" s="24" t="inlineStr">
-        <is>
-          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
-        </is>
-      </c>
-      <c r="BB21" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC21" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD21" s="24" t="inlineStr">
-        <is>
-          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
-        </is>
-      </c>
-      <c r="BE21" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF21" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG21" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH21" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:40:05.383273Z</t>
-        </is>
-      </c>
-      <c r="BI21" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ21" s="25" t="n"/>
-      <c r="BK21" s="26" t="n">
-        <v>-117</v>
-      </c>
-      <c r="BL21" s="27" t="n">
-        <v>1.854701</v>
-      </c>
-      <c r="BM21" s="28" t="n">
-        <v>0.539171</v>
-      </c>
-      <c r="BN21" s="28" t="n"/>
-      <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
-      <c r="BR21" s="28" t="n"/>
-      <c r="BS21" s="28" t="n"/>
-      <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="25" t="n"/>
-      <c r="BV21" s="29" t="n"/>
-      <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n"/>
-      <c r="BY21" s="27" t="n"/>
-      <c r="BZ21" s="24" t="n"/>
-      <c r="CA21" s="31" t="n"/>
-      <c r="CB21" s="24" t="n"/>
-      <c r="CC21" s="24" t="n"/>
-      <c r="CD21" s="24" t="n"/>
-      <c r="CE21" s="24" t="n"/>
-      <c r="CF21" s="24" t="n"/>
-      <c r="CG21" s="24" t="n"/>
-      <c r="CH21" s="24" t="n"/>
-      <c r="CI21" s="24" t="n"/>
-      <c r="CJ21" s="24" t="n"/>
-      <c r="CK21" s="24" t="n"/>
-      <c r="CL21" s="24" t="n"/>
-      <c r="CM21" s="24" t="n"/>
-      <c r="CN21" s="24" t="n"/>
-      <c r="CO21" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO12" headerRowCount="1">
-  <autoFilter ref="A1:CO12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO13" headerRowCount="1">
+  <autoFilter ref="A1:CO13"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$12)</f>
+        <f>COUNTA('Picks'!$A$2:$A$13)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$13,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$12,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$13,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")/(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")/(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$12)/SUM('Picks'!$BX$2:$BX$12),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$13)/SUM('Picks'!$BX$2:$BX$13),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$12)</f>
+        <f>SUM('Picks'!$BY$2:$BY$13)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$12,"&lt;&gt;",'Picks'!$AB$2:$AB$12),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$13,"&lt;&gt;",'Picks'!$AB$2:$AB$13),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$12,'Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$13,'Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO12"/>
+  <dimension ref="A1:CO13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3288,22 +3288,22 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>e8a1cf4b6b8646cf</t>
+          <t>f24cec6b572d41e6</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:18:52.629033Z</t>
+          <t>2026-08-01T23:55:04.278999Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T00:00:00Z</t>
+          <t>2026-08-02T00:00:00Z</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>67386</t>
+          <t>66659</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>Sentinels</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>Leviatán Esports</t>
         </is>
       </c>
       <c r="H8" s="24" t="inlineStr">
@@ -3338,23 +3338,23 @@
         </is>
       </c>
       <c r="L8" s="26" t="n">
-        <v>-156</v>
+        <v>-138</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.724638</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.579832</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>0.626556</v>
+        <v>0.608104</v>
       </c>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
-        <v>0.017181</v>
+        <v>0.028272</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S8" s="29" t="n">
         <v>1.5</v>
@@ -3366,21 +3366,41 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
-      <c r="Z8" s="26" t="n"/>
-      <c r="AA8" s="28" t="n"/>
-      <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="Z8" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="AA8" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB8" s="28" t="n">
+        <v>0.000168</v>
+      </c>
+      <c r="AC8" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T04:26:23.368285Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-valorant-g2-sen-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-valorant-lev-nrg-2026-08-02).</t>
         </is>
       </c>
       <c r="AF8" s="31" t="inlineStr">
@@ -3390,7 +3410,7 @@
       </c>
       <c r="AG8" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH8" s="24" t="n"/>
@@ -3398,7 +3418,7 @@
       <c r="AJ8" s="31" t="n"/>
       <c r="AK8" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL8" s="26" t="n">
@@ -3406,47 +3426,47 @@
       </c>
       <c r="AM8" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN8" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO8" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP8" s="24" t="inlineStr">
         <is>
-          <t>Sentinels</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="AQ8" s="24" t="inlineStr">
         <is>
-          <t>Sentinels</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="AR8" s="24" t="inlineStr">
         <is>
-          <t>Sentinels</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="AS8" s="24" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>Leviatán Esports</t>
         </is>
       </c>
       <c r="AT8" s="24" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>Leviatán Esports</t>
         </is>
       </c>
       <c r="AU8" s="24" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>Leviatán Esports</t>
         </is>
       </c>
       <c r="AV8" s="24" t="n"/>
@@ -3464,7 +3484,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>380fd5a8849c0ab4c0739f37636ab4ad8bb9ee7fab81eb341719f39d4f324b58</t>
+          <t>4e9833fa3108f9876de728871233bbb749924096e4b6984ae7ee11ff9d8be0d1</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3479,7 +3499,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>380fd5a8849c0ab4c0739f37636ab4ad8bb9ee7fab81eb341719f39d4f324b58</t>
+          <t>4e9833fa3108f9876de728871233bbb749924096e4b6984ae7ee11ff9d8be0d1</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3499,7 +3519,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:18:52.627150Z</t>
+          <t>2026-08-01T23:55:01.262855Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3509,19 +3529,23 @@
       </c>
       <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
-        <v>-156</v>
+        <v>-138</v>
       </c>
       <c r="BL8" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.724638</v>
       </c>
       <c r="BM8" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.579832</v>
       </c>
       <c r="BN8" s="28" t="n"/>
       <c r="BO8" s="28" t="n"/>
       <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
-      <c r="BR8" s="28" t="n"/>
+      <c r="BQ8" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BR8" s="28" t="n">
+        <v>0.58</v>
+      </c>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
       <c r="BU8" s="25" t="n"/>
@@ -3549,22 +3573,22 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>7710d3db4fcb40b0</t>
+          <t>f5ae220015ea4850</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:33:11.238423Z</t>
+          <t>2026-08-02T07:16:42.752833Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00Z</t>
+          <t>2026-08-02T08:00:00Z</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>67569</t>
+          <t>66788</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -3574,12 +3598,12 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>VARREL</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -3589,7 +3613,7 @@
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J9" s="25" t="n"/>
@@ -3599,26 +3623,26 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>-203</v>
+        <v>-150</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.666667</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.6</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.76553</v>
+        <v>0.676998</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.095563</v>
+        <v>0.076998</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="S9" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T9" s="24" t="inlineStr">
         <is>
@@ -3641,7 +3665,7 @@
       <c r="AD9" s="24" t="n"/>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-valorant-var-krx-2026-08-02).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3682,32 +3706,32 @@
       </c>
       <c r="AP9" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AQ9" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AR9" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AS9" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>VARREL</t>
         </is>
       </c>
       <c r="AT9" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>VARREL</t>
         </is>
       </c>
       <c r="AU9" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>VARREL</t>
         </is>
       </c>
       <c r="AV9" s="24" t="n"/>
@@ -3725,7 +3749,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>6c2fe30bde2e3d49744e134c7d83a04f47b0437d09b6f8743e0023be67965171</t>
+          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3740,7 +3764,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>6c2fe30bde2e3d49744e134c7d83a04f47b0437d09b6f8743e0023be67965171</t>
+          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3760,7 +3784,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:33:06.494162Z</t>
+          <t>2026-08-02T07:16:34.729300Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3770,13 +3794,13 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>-203</v>
+        <v>-150</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.666667</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.6</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
@@ -3810,22 +3834,22 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>612fd0dd1f434502</t>
+          <t>3e7f1f677a4e44e5</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:40.423686Z</t>
+          <t>2026-08-02T07:16:42.752833Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:00:00Z</t>
+          <t>2026-08-02T18:00:00Z</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>66788</t>
+          <t>66957</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -3835,12 +3859,12 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>VARREL</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr">
@@ -3860,26 +3884,26 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>-138</v>
+        <v>-122</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.819672</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.54955</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.677597</v>
+        <v>0.537801</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>0.097765</v>
+        <v>-0.011749</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="S10" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T10" s="24" t="inlineStr">
         <is>
@@ -3902,7 +3926,7 @@
       <c r="AD10" s="24" t="n"/>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-valorant-var-krx-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-valorant-fnc-th-2026-08-02).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -3920,7 +3944,7 @@
       <c r="AJ10" s="31" t="n"/>
       <c r="AK10" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL10" s="26" t="n">
@@ -3928,47 +3952,47 @@
       </c>
       <c r="AM10" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN10" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO10" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP10" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="AQ10" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="AR10" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="AS10" s="24" t="inlineStr">
         <is>
-          <t>VARREL</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="AT10" s="24" t="inlineStr">
         <is>
-          <t>VARREL</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="AU10" s="24" t="inlineStr">
         <is>
-          <t>VARREL</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="AV10" s="24" t="n"/>
@@ -3986,7 +4010,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>3d9fb2e99557b8380ebae212c50f062d30d580c0a2a0d2fab1fc8860b2260810</t>
+          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -4001,7 +4025,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>3d9fb2e99557b8380ebae212c50f062d30d580c0a2a0d2fab1fc8860b2260810</t>
+          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4021,7 +4045,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:32.281041Z</t>
+          <t>2026-08-02T07:16:36.237945Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4031,13 +4055,13 @@
       </c>
       <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
-        <v>-138</v>
+        <v>-122</v>
       </c>
       <c r="BL10" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.819672</v>
       </c>
       <c r="BM10" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.54955</v>
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
@@ -4071,22 +4095,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>ff19a597303a4200</t>
+          <t>3374d480410a4f42</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:40.423686Z</t>
+          <t>2026-08-02T07:16:42.752833Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00:00Z</t>
+          <t>2026-08-02T21:00:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>66957</t>
+          <t>67311</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -4096,12 +4120,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics</t>
+          <t>KRÜ Esports</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>Fnatic</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4111,7 +4135,7 @@
       </c>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J11" s="25" t="n"/>
@@ -4121,23 +4145,23 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>-122</v>
+        <v>133</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.33</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.429185</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.538226</v>
+        <v>0.518849</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>-0.011324</v>
+        <v>0.08966399999999999</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="S11" s="29" t="n">
         <v>1</v>
@@ -4163,7 +4187,7 @@
       <c r="AD11" s="24" t="n"/>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-valorant-fnc-th-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-valorant-c9-kr-2026-08-02).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4204,32 +4228,32 @@
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics</t>
+          <t>KRÜ Esports</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics</t>
+          <t>KRÜ Esports</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics</t>
+          <t>KRÜ Esports</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>Fnatic</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>Fnatic</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>Fnatic</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4247,7 +4271,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>3d9fb2e99557b8380ebae212c50f062d30d580c0a2a0d2fab1fc8860b2260810</t>
+          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4262,7 +4286,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>3d9fb2e99557b8380ebae212c50f062d30d580c0a2a0d2fab1fc8860b2260810</t>
+          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4282,7 +4306,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:33.723797Z</t>
+          <t>2026-08-02T07:16:36.771361Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4292,13 +4316,13 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>-122</v>
+        <v>133</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.33</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.429185</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
@@ -4332,22 +4356,22 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>fa5cdd9d69684e07</t>
+          <t>45eb7297ecc74761</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:40.423686Z</t>
+          <t>2026-08-02T07:16:42.752833Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T21:00:00Z</t>
+          <t>2026-08-03T00:00:00Z</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>67311</t>
+          <t>67386</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4357,12 +4381,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>KRÜ Esports</t>
+          <t>Sentinels</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4382,26 +4406,26 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>133</v>
+        <v>-163</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>2.33</v>
+        <v>1.613497</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.619772</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.518417</v>
+        <v>0.626674</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.08923200000000001</v>
+        <v>0.006902</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="S12" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
@@ -4424,7 +4448,7 @@
       <c r="AD12" s="24" t="n"/>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-valorant-c9-kr-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-valorant-g2-sen-2026-08-03).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4465,32 +4489,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>KRÜ Esports</t>
+          <t>Sentinels</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>KRÜ Esports</t>
+          <t>Sentinels</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>KRÜ Esports</t>
+          <t>Sentinels</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4508,7 +4532,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>3d9fb2e99557b8380ebae212c50f062d30d580c0a2a0d2fab1fc8860b2260810</t>
+          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4523,7 +4547,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>3d9fb2e99557b8380ebae212c50f062d30d580c0a2a0d2fab1fc8860b2260810</t>
+          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4543,7 +4567,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:34.260410Z</t>
+          <t>2026-08-02T07:16:37.262004Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4553,13 +4577,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>133</v>
+        <v>-163</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>2.33</v>
+        <v>1.613497</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.619772</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
@@ -4590,6 +4614,267 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
     </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>d65be6a07b2f4cb9</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:42.752833Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.765271</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.08476</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:38.239558Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -3834,12 +3834,12 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>3e7f1f677a4e44e5</t>
+          <t>013f09b3e3f94421</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:42.752833Z</t>
+          <t>2026-08-02T08:19:54.418500Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:36.237945Z</t>
+          <t>2026-08-02T08:19:47.956153Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4095,12 +4095,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>3374d480410a4f42</t>
+          <t>97e91eeb6b244f34</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:42.752833Z</t>
+          <t>2026-08-02T08:19:54.418500Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:36.771361Z</t>
+          <t>2026-08-02T08:19:48.417087Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4356,12 +4356,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>45eb7297ecc74761</t>
+          <t>2d2f190eb3584d82</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:42.752833Z</t>
+          <t>2026-08-02T08:19:54.418500Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:37.262004Z</t>
+          <t>2026-08-02T08:19:48.924206Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4617,12 +4617,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>d65be6a07b2f4cb9</t>
+          <t>e8362622e86343fe</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:42.752833Z</t>
+          <t>2026-08-02T08:19:54.418500Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:38.239558Z</t>
+          <t>2026-08-02T08:19:49.952914Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO13" headerRowCount="1">
-  <autoFilter ref="A1:CO13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO14" headerRowCount="1">
+  <autoFilter ref="A1:CO14"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$13)</f>
+        <f>COUNTA('Picks'!$A$2:$A$14)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$13,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$13,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$14,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")/(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")/(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$13)/SUM('Picks'!$BX$2:$BX$13),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$14)/SUM('Picks'!$BX$2:$BX$14),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$13)</f>
+        <f>SUM('Picks'!$BY$2:$BY$14)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$13,"&lt;&gt;",'Picks'!$AB$2:$AB$13),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$14,"&lt;&gt;",'Picks'!$AB$2:$AB$14),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$13,'Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$14,'Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO13"/>
+  <dimension ref="A1:CO14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3834,12 +3834,12 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>013f09b3e3f94421</t>
+          <t>5fee57cd5a804198</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:54.418500Z</t>
+          <t>2026-08-02T10:00:21.466032Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -3884,23 +3884,23 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.787402</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O10" s="28" t="n">
         <v>0.537801</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>-0.011749</v>
+        <v>-0.02167</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="S10" s="29" t="n">
         <v>1</v>
@@ -3926,7 +3926,7 @@
       <c r="AD10" s="24" t="n"/>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-valorant-fnc-th-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-valorant-fnc-th-2026-08-02).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
+          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
+          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:47.956153Z</t>
+          <t>2026-08-02T10:00:14.883504Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4055,13 +4055,13 @@
       </c>
       <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="BL10" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.787402</v>
       </c>
       <c r="BM10" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
@@ -4095,12 +4095,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>97e91eeb6b244f34</t>
+          <t>00ce3fdc75a8467a</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:54.418500Z</t>
+          <t>2026-08-02T10:00:21.466032Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
+          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
+          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:48.417087Z</t>
+          <t>2026-08-02T10:00:15.339792Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4356,12 +4356,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>2d2f190eb3584d82</t>
+          <t>74ad56603381489b</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:54.418500Z</t>
+          <t>2026-08-02T10:00:21.466032Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
+          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
+          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:48.924206Z</t>
+          <t>2026-08-02T10:00:15.826886Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4617,12 +4617,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>e8362622e86343fe</t>
+          <t>dffa0c1b766e414b</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:54.418500Z</t>
+          <t>2026-08-02T10:00:21.466032Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
+          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
+          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:49.952914Z</t>
+          <t>2026-08-02T10:00:16.849872Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4875,6 +4875,267 @@
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
     </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>6122c97e7ba04e51</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T10:00:21.466032Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>67989</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.569278</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>-0.060352</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="n"/>
+      <c r="W14" s="26" t="n"/>
+      <c r="X14" s="26" t="n"/>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n"/>
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-valorant-flyr-swim-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T10:00:19.402068Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO14" headerRowCount="1">
-  <autoFilter ref="A1:CO14"/>
-  <tableColumns count="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP14" headerRowCount="1">
+  <autoFilter ref="A1:CP14"/>
+  <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,6 +396,7 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
+    <tableColumn id="94" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1010,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO14"/>
+  <dimension ref="A1:CP14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,6 +1107,7 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="17" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1572,6 +1574,11 @@
       <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
+        </is>
+      </c>
+      <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>trade_candidate</t>
         </is>
       </c>
     </row>
@@ -1859,6 +1866,7 @@
       <c r="CM2" s="24" t="n"/>
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2144,6 +2152,7 @@
       <c r="CM3" s="24" t="n"/>
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2429,6 +2438,7 @@
       <c r="CM4" s="24" t="n"/>
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
+      <c r="CP4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2714,6 +2724,7 @@
       <c r="CM5" s="24" t="n"/>
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
+      <c r="CP5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -2999,6 +3010,7 @@
       <c r="CM6" s="24" t="n"/>
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
+      <c r="CP6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3284,6 +3296,7 @@
       <c r="CM7" s="24" t="n"/>
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
+      <c r="CP7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3569,6 +3582,7 @@
       <c r="CM8" s="24" t="n"/>
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
+      <c r="CP8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3651,18 +3665,38 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
-      <c r="Z9" s="26" t="n"/>
-      <c r="AA9" s="28" t="n"/>
-      <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="Z9" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="AA9" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T11:45:29.283046Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-valorant-var-krx-2026-08-02).</t>
@@ -3675,7 +3709,7 @@
       </c>
       <c r="AG9" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH9" s="24" t="n"/>
@@ -3805,8 +3839,12 @@
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
       <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
-      <c r="BR9" s="28" t="n"/>
+      <c r="BQ9" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BR9" s="28" t="n">
+        <v>0.6</v>
+      </c>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
       <c r="BU9" s="25" t="n"/>
@@ -3830,16 +3868,17 @@
       <c r="CM9" s="24" t="n"/>
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>5fee57cd5a804198</t>
+          <t>9529a1118eb4488c</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:21.466032Z</t>
+          <t>2026-08-02T13:08:03.938703Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -3893,11 +3932,11 @@
         <v>0.5594710000000001</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.537801</v>
+        <v>0.537404</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>-0.02167</v>
+        <v>-0.022067</v>
       </c>
       <c r="R10" s="26" t="n">
         <v>9</v>
@@ -4010,7 +4049,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
+          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -4025,7 +4064,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
+          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4045,7 +4084,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:14.883504Z</t>
+          <t>2026-08-02T13:07:57.633865Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4091,16 +4130,17 @@
       <c r="CM10" s="24" t="n"/>
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>00ce3fdc75a8467a</t>
+          <t>d3c73e55fb4f4bee</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:21.466032Z</t>
+          <t>2026-08-02T13:08:03.938703Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4154,11 +4194,11 @@
         <v>0.429185</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.518849</v>
+        <v>0.519193</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.08966399999999999</v>
+        <v>0.090008</v>
       </c>
       <c r="R11" s="26" t="n">
         <v>65</v>
@@ -4271,7 +4311,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
+          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4286,7 +4326,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
+          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4306,7 +4346,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:15.339792Z</t>
+          <t>2026-08-02T13:07:58.097458Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4352,16 +4392,17 @@
       <c r="CM11" s="24" t="n"/>
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>74ad56603381489b</t>
+          <t>9100e5c0808744ff</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:21.466032Z</t>
+          <t>2026-08-02T13:08:03.938703Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4415,14 +4456,14 @@
         <v>0.619772</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.626674</v>
+        <v>0.626902</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.006902</v>
+        <v>0.00713</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S12" s="29" t="n">
         <v>1.5</v>
@@ -4532,7 +4573,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
+          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4547,7 +4588,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
+          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4567,7 +4608,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:15.826886Z</t>
+          <t>2026-08-02T13:07:58.631245Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4613,16 +4654,17 @@
       <c r="CM12" s="24" t="n"/>
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>dffa0c1b766e414b</t>
+          <t>1b11e4a18f9a4d05</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:21.466032Z</t>
+          <t>2026-08-02T13:08:03.938703Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4676,11 +4718,11 @@
         <v>0.680511</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.765271</v>
+        <v>0.765342</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.08476</v>
+        <v>0.084831</v>
       </c>
       <c r="R13" s="26" t="n">
         <v>62</v>
@@ -4793,7 +4835,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
+          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4808,7 +4850,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
+          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4828,7 +4870,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:16.849872Z</t>
+          <t>2026-08-02T13:07:59.600687Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4874,16 +4916,17 @@
       <c r="CM13" s="24" t="n"/>
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>6122c97e7ba04e51</t>
+          <t>67a26dad0d0a4b98</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:21.466032Z</t>
+          <t>2026-08-02T13:08:03.938703Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -4928,20 +4971,20 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>-170</v>
+        <v>-213</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.469484</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.680511</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.569278</v>
+        <v>0.568858</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>-0.060352</v>
+        <v>-0.111653</v>
       </c>
       <c r="R14" s="26" t="n">
         <v>0</v>
@@ -4970,7 +5013,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-valorant-flyr-swim-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-valorant-flyr-swim-2026-08-03).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5054,7 +5097,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
+          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5069,7 +5112,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
+          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5089,7 +5132,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:19.402068Z</t>
+          <t>2026-08-02T13:08:01.936766Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5099,13 +5142,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>-170</v>
+        <v>-213</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.469484</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.680511</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5135,6 +5178,7 @@
       <c r="CM14" s="24" t="n"/>
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP14" headerRowCount="1">
-  <autoFilter ref="A1:CP14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP15" headerRowCount="1">
+  <autoFilter ref="A1:CP15"/>
   <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -753,19 +753,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$14)</f>
+        <f>COUNTA('Picks'!$A$2:$A$15)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$14,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -793,19 +793,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$14,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")/(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$14)/SUM('Picks'!$BX$2:$BX$14),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
         <v/>
       </c>
     </row>
@@ -833,19 +833,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$14)</f>
+        <f>SUM('Picks'!$BY$2:$BY$15)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$14,"&lt;&gt;",'Picks'!$AB$2:$AB$14),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$14,'Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -900,15 +900,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -916,11 +916,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -931,15 +931,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -947,11 +947,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -962,15 +962,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -978,11 +978,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP14"/>
+  <dimension ref="A1:CP15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3873,12 +3873,12 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>9529a1118eb4488c</t>
+          <t>1ee348a7b52145b5</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:08:03.938703Z</t>
+          <t>2026-08-02T15:51:56.481863Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -3932,11 +3932,11 @@
         <v>0.5594710000000001</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.537404</v>
+        <v>0.537865</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>-0.022067</v>
+        <v>-0.021606</v>
       </c>
       <c r="R10" s="26" t="n">
         <v>9</v>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
+          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
+          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:57.633865Z</t>
+          <t>2026-08-02T15:51:49.615172Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4130,17 +4130,21 @@
       <c r="CM10" s="24" t="n"/>
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
-      <c r="CP10" s="24" t="n"/>
+      <c r="CP10" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>d3c73e55fb4f4bee</t>
+          <t>b9adb6209dcf4b51</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:08:03.938703Z</t>
+          <t>2026-08-02T15:51:56.481863Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4185,23 +4189,23 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.420168</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.519193</v>
+        <v>0.518772</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.090008</v>
+        <v>0.098604</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="S11" s="29" t="n">
         <v>1</v>
@@ -4227,7 +4231,7 @@
       <c r="AD11" s="24" t="n"/>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-valorant-c9-kr-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-c9-kr-2026-08-02).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4311,7 +4315,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
+          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4326,7 +4330,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
+          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4346,7 +4350,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:58.097458Z</t>
+          <t>2026-08-02T15:51:50.083593Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4356,13 +4360,13 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.420168</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
@@ -4392,17 +4396,21 @@
       <c r="CM11" s="24" t="n"/>
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
-      <c r="CP11" s="24" t="n"/>
+      <c r="CP11" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>9100e5c0808744ff</t>
+          <t>10a34658b50c4482</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:08:03.938703Z</t>
+          <t>2026-08-02T15:51:56.481863Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4447,23 +4455,23 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-163</v>
+        <v>-178</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.561798</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.640288</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.626902</v>
+        <v>0.626584</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.00713</v>
+        <v>-0.013704</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="S12" s="29" t="n">
         <v>1.5</v>
@@ -4489,7 +4497,7 @@
       <c r="AD12" s="24" t="n"/>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-valorant-g2-sen-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-g2-sen-2026-08-03).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4573,7 +4581,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
+          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4588,7 +4596,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
+          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4608,7 +4616,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:58.631245Z</t>
+          <t>2026-08-02T15:51:50.605689Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4618,13 +4626,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-163</v>
+        <v>-178</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.561798</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.640288</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
@@ -4654,17 +4662,21 @@
       <c r="CM12" s="24" t="n"/>
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
-      <c r="CP12" s="24" t="n"/>
+      <c r="CP12" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>1b11e4a18f9a4d05</t>
+          <t>c99bfa1cdea74a99</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:08:03.938703Z</t>
+          <t>2026-08-02T15:51:56.481863Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4718,11 +4730,11 @@
         <v>0.680511</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.765342</v>
+        <v>0.765185</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.084831</v>
+        <v>0.084674</v>
       </c>
       <c r="R13" s="26" t="n">
         <v>62</v>
@@ -4835,7 +4847,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
+          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4850,7 +4862,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
+          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4870,7 +4882,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:59.600687Z</t>
+          <t>2026-08-02T15:51:51.645392Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4916,17 +4928,21 @@
       <c r="CM13" s="24" t="n"/>
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
-      <c r="CP13" s="24" t="n"/>
+      <c r="CP13" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>67a26dad0d0a4b98</t>
+          <t>05a304ffe21a4621</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:08:03.938703Z</t>
+          <t>2026-08-02T15:51:56.481863Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -4936,7 +4952,7 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>67989</t>
+          <t>67987</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -4946,12 +4962,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -4961,7 +4977,7 @@
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J14" s="25" t="n"/>
@@ -4971,26 +4987,26 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>-213</v>
+        <v>113</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>1.469484</v>
+        <v>2.13</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.469484</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.568858</v>
+        <v>0.520495</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>-0.111653</v>
+        <v>0.051011</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
@@ -5013,7 +5029,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-valorant-flyr-swim-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-valorant-him-spi-2026-08-03).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5054,32 +5070,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5097,7 +5113,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
+          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5112,7 +5128,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
+          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5132,7 +5148,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:08:01.936766Z</t>
+          <t>2026-08-02T15:51:53.269044Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5142,13 +5158,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>-213</v>
+        <v>113</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>1.469484</v>
+        <v>2.13</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.469484</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5178,7 +5194,277 @@
       <c r="CM14" s="24" t="n"/>
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
-      <c r="CP14" s="24" t="n"/>
+      <c r="CP14" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>99860081c1e642e9</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:56.481863Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>67989</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.569339</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>-0.09052499999999999</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-flyr-swim-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:54.232011Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP15" headerRowCount="1">
-  <autoFilter ref="A1:CP15"/>
-  <tableColumns count="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ17" headerRowCount="1">
+  <autoFilter ref="A1:CQ17"/>
+  <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,7 +396,8 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="trade_candidate"/>
+    <tableColumn id="94" name="market_residual_probability"/>
+    <tableColumn id="95" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -753,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$15)</f>
+        <f>COUNTA('Picks'!$A$2:$A$17)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$17,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -793,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$17,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")/(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$17)/SUM('Picks'!$BX$2:$BX$17),0)</f>
         <v/>
       </c>
     </row>
@@ -833,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$15)</f>
+        <f>SUM('Picks'!$BY$2:$BY$17)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$17,"&lt;&gt;",'Picks'!$AB$2:$AB$17),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$17,'Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -900,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -916,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -931,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -947,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -962,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -978,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1011,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP15"/>
+  <dimension ref="A1:CQ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1107,7 +1108,8 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
-    <col width="17" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="17" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1577,6 +1579,11 @@
         </is>
       </c>
       <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>market_residual_probability</t>
+        </is>
+      </c>
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1867,6 +1874,7 @@
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2153,6 +2161,7 @@
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
+      <c r="CQ3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2439,6 +2448,7 @@
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
+      <c r="CQ4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2725,6 +2735,7 @@
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
+      <c r="CQ5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3011,6 +3022,7 @@
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
+      <c r="CQ6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3297,6 +3309,7 @@
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
+      <c r="CQ7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3583,6 +3596,7 @@
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
+      <c r="CQ8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3869,16 +3883,17 @@
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>1ee348a7b52145b5</t>
+          <t>e14e2a0725b94c94</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:56.481863Z</t>
+          <t>2026-08-02T16:15:29.850559Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -4049,7 +4064,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -4064,7 +4079,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4084,7 +4099,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:49.615172Z</t>
+          <t>2026-08-02T16:15:22.804516Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4130,7 +4145,8 @@
       <c r="CM10" s="24" t="n"/>
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
-      <c r="CP10" s="24" t="inlineStr">
+      <c r="CP10" s="24" t="n"/>
+      <c r="CQ10" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4139,12 +4155,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>b9adb6209dcf4b51</t>
+          <t>d47072ec02654714</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:56.481863Z</t>
+          <t>2026-08-02T16:15:29.850559Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4315,7 +4331,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4330,7 +4346,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4350,7 +4366,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:50.083593Z</t>
+          <t>2026-08-02T16:15:23.359845Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4396,7 +4412,8 @@
       <c r="CM11" s="24" t="n"/>
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
-      <c r="CP11" s="24" t="inlineStr">
+      <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4405,12 +4422,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>10a34658b50c4482</t>
+          <t>e9050da802eb4df3</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:56.481863Z</t>
+          <t>2026-08-02T16:15:29.850559Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4581,7 +4598,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4596,7 +4613,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4616,7 +4633,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:50.605689Z</t>
+          <t>2026-08-02T16:15:23.904156Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4662,7 +4679,8 @@
       <c r="CM12" s="24" t="n"/>
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
-      <c r="CP12" s="24" t="inlineStr">
+      <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4671,12 +4689,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>c99bfa1cdea74a99</t>
+          <t>efd2e32974e4400a</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:56.481863Z</t>
+          <t>2026-08-02T16:15:29.850559Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4847,7 +4865,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4862,7 +4880,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4882,7 +4900,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:51.645392Z</t>
+          <t>2026-08-02T16:15:24.994619Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4928,7 +4946,8 @@
       <c r="CM13" s="24" t="n"/>
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
-      <c r="CP13" s="24" t="inlineStr">
+      <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4937,22 +4956,22 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>05a304ffe21a4621</t>
+          <t>c5637dcb44404186</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:56.481863Z</t>
+          <t>2026-08-02T16:15:29.850559Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T21:00:00Z</t>
+          <t>2026-08-03T18:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>67987</t>
+          <t>67658</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -4962,12 +4981,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>Barça eSports GC</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>HIMMERS</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -4987,26 +5006,26 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>113</v>
+        <v>-233</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>2.13</v>
+        <v>1.429185</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.6997</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.520495</v>
+        <v>0.692093</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.051011</v>
+        <v>-0.007607</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
@@ -5029,7 +5048,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-valorant-him-spi-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-valorant-tmo-beg-2026-08-03).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5070,32 +5089,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>Barça eSports GC</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>Barça eSports GC</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>Barça eSports GC</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>HIMMERS</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>HIMMERS</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>HIMMERS</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5113,7 +5132,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5128,7 +5147,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5148,7 +5167,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:53.269044Z</t>
+          <t>2026-08-02T16:15:26.008727Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5158,13 +5177,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>113</v>
+        <v>-233</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>2.13</v>
+        <v>1.429185</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.6997</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5194,21 +5213,22 @@
       <c r="CM14" s="24" t="n"/>
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
-      <c r="CP14" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>99860081c1e642e9</t>
+          <t>9057970a424b46aa</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:56.481863Z</t>
+          <t>2026-08-02T16:15:29.850559Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -5218,7 +5238,7 @@
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>67989</t>
+          <t>67987</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -5228,12 +5248,12 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -5243,7 +5263,7 @@
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J15" s="25" t="n"/>
@@ -5253,26 +5273,26 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>-194</v>
+        <v>113</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>1.515464</v>
+        <v>2.13</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.469484</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.569339</v>
+        <v>0.520495</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>-0.09052499999999999</v>
+        <v>0.051011</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="S15" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T15" s="24" t="inlineStr">
         <is>
@@ -5295,7 +5315,7 @@
       <c r="AD15" s="24" t="n"/>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-flyr-swim-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-valorant-him-spi-2026-08-03).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5336,32 +5356,32 @@
       </c>
       <c r="AP15" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="AQ15" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="AR15" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="AS15" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="AT15" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="AU15" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="AV15" s="24" t="n"/>
@@ -5379,7 +5399,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5394,7 +5414,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5414,7 +5434,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:54.232011Z</t>
+          <t>2026-08-02T16:15:26.573553Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5424,13 +5444,13 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>-194</v>
+        <v>113</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>1.515464</v>
+        <v>2.13</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.469484</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
@@ -5460,7 +5480,542 @@
       <c r="CM15" s="24" t="n"/>
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
-      <c r="CP15" s="24" t="inlineStr">
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>7239ae726f2c4cc7</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:29.850559Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>67989</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.569339</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>-0.09052499999999999</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-flyr-swim-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:27.625205Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>3f41b263d837419e</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:29.850559Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>68097</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Revitalize GC</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.563407</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>-0.036593</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="n"/>
+      <c r="W17" s="26" t="n"/>
+      <c r="X17" s="26" t="n"/>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n"/>
+      <c r="AD17" s="24" t="n"/>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-valorant-efa-rev-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>Revitalize GC</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>Revitalize GC</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>Revitalize GC</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:29.848917Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ17" headerRowCount="1">
-  <autoFilter ref="A1:CQ17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ16" headerRowCount="1">
+  <autoFilter ref="A1:CQ16"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$17)</f>
+        <f>COUNTA('Picks'!$A$2:$A$16)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$17,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$16,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$17,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$16,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")/(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")/(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$17)/SUM('Picks'!$BX$2:$BX$17),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$16)/SUM('Picks'!$BX$2:$BX$16),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$17)</f>
+        <f>SUM('Picks'!$BY$2:$BY$16)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$17,"&lt;&gt;",'Picks'!$AB$2:$AB$17),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$16,"&lt;&gt;",'Picks'!$AB$2:$AB$16),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$17,'Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$16,'Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ17"/>
+  <dimension ref="A1:CQ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3888,12 +3888,12 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>e14e2a0725b94c94</t>
+          <t>6755683982be4362</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:29.850559Z</t>
+          <t>2026-08-02T16:53:48.546068Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:22.804516Z</t>
+          <t>2026-08-02T16:53:41.949275Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4155,12 +4155,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>d47072ec02654714</t>
+          <t>1523276642c7488b</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:29.850559Z</t>
+          <t>2026-08-02T16:53:48.546068Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:23.359845Z</t>
+          <t>2026-08-02T16:53:42.402563Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4422,12 +4422,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>e9050da802eb4df3</t>
+          <t>3327695c91744534</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:29.850559Z</t>
+          <t>2026-08-02T16:53:48.546068Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:23.904156Z</t>
+          <t>2026-08-02T16:53:42.939409Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4689,12 +4689,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>efd2e32974e4400a</t>
+          <t>67e734c757684e31</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:29.850559Z</t>
+          <t>2026-08-02T16:53:48.546068Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:24.994619Z</t>
+          <t>2026-08-02T16:53:43.967259Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4956,22 +4956,22 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>c5637dcb44404186</t>
+          <t>68ea0465031e495b</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:29.850559Z</t>
+          <t>2026-08-02T16:53:48.546068Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T18:00:00Z</t>
+          <t>2026-08-03T21:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>67658</t>
+          <t>67987</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>Twisted Minds Orchid</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -5006,26 +5006,26 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>-233</v>
+        <v>113</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>1.429185</v>
+        <v>2.13</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.469484</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.692093</v>
+        <v>0.520495</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>-0.007607</v>
+        <v>0.051011</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-valorant-tmo-beg-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-valorant-him-spi-2026-08-03).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>Barça eSports GC</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>Twisted Minds Orchid</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>Twisted Minds Orchid</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>Twisted Minds Orchid</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:26.008727Z</t>
+          <t>2026-08-02T16:53:45.603247Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5177,13 +5177,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>-233</v>
+        <v>113</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>1.429185</v>
+        <v>2.13</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.469484</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5216,19 +5216,19 @@
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>9057970a424b46aa</t>
+          <t>e4df25237f55473f</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:29.850559Z</t>
+          <t>2026-08-02T16:53:48.546068Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>67987</t>
+          <t>67989</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>SwimTrek Blue</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>HIMMERS</t>
+          <t>FlyQuest RED</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J15" s="25" t="n"/>
@@ -5273,26 +5273,26 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>113</v>
+        <v>-194</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>2.13</v>
+        <v>1.515464</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.659864</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.520495</v>
+        <v>0.569339</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.051011</v>
+        <v>-0.09052499999999999</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="S15" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T15" s="24" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
       <c r="AD15" s="24" t="n"/>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-valorant-him-spi-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-flyr-swim-2026-08-03).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5356,32 +5356,32 @@
       </c>
       <c r="AP15" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>SwimTrek Blue</t>
         </is>
       </c>
       <c r="AQ15" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>SwimTrek Blue</t>
         </is>
       </c>
       <c r="AR15" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>SwimTrek Blue</t>
         </is>
       </c>
       <c r="AS15" s="24" t="inlineStr">
         <is>
-          <t>HIMMERS</t>
+          <t>FlyQuest RED</t>
         </is>
       </c>
       <c r="AT15" s="24" t="inlineStr">
         <is>
-          <t>HIMMERS</t>
+          <t>FlyQuest RED</t>
         </is>
       </c>
       <c r="AU15" s="24" t="inlineStr">
         <is>
-          <t>HIMMERS</t>
+          <t>FlyQuest RED</t>
         </is>
       </c>
       <c r="AV15" s="24" t="n"/>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:26.573553Z</t>
+          <t>2026-08-02T16:53:46.542257Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5444,13 +5444,13 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>113</v>
+        <v>-194</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>2.13</v>
+        <v>1.515464</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.659864</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
@@ -5483,29 +5483,29 @@
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>7239ae726f2c4cc7</t>
+          <t>cfdd59d2171e426f</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:29.850559Z</t>
+          <t>2026-08-02T16:53:48.546068Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T21:00:00Z</t>
+          <t>2026-08-03T23:30:00Z</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>67989</t>
+          <t>68097</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>Revitalize GC</t>
         </is>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>Eternal Focus Amethyst</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -5540,26 +5540,26 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>-194</v>
+        <v>-178</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.561798</v>
       </c>
       <c r="N16" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.640288</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.569339</v>
+        <v>0.563407</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>-0.09052499999999999</v>
+        <v>-0.076881</v>
       </c>
       <c r="R16" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T16" s="24" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
       <c r="AD16" s="24" t="n"/>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-flyr-swim-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-efa-rev-2026-08-03).</t>
         </is>
       </c>
       <c r="AF16" s="31" t="inlineStr">
@@ -5618,37 +5618,37 @@
       </c>
       <c r="AO16" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP16" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>Revitalize GC</t>
         </is>
       </c>
       <c r="AQ16" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>Revitalize GC</t>
         </is>
       </c>
       <c r="AR16" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>Revitalize GC</t>
         </is>
       </c>
       <c r="AS16" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>Eternal Focus Amethyst</t>
         </is>
       </c>
       <c r="AT16" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>Eternal Focus Amethyst</t>
         </is>
       </c>
       <c r="AU16" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>Eternal Focus Amethyst</t>
         </is>
       </c>
       <c r="AV16" s="24" t="n"/>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:27.625205Z</t>
+          <t>2026-08-02T16:53:48.544086Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5711,13 +5711,13 @@
       </c>
       <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
-        <v>-194</v>
+        <v>-178</v>
       </c>
       <c r="BL16" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.561798</v>
       </c>
       <c r="BM16" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.640288</v>
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
@@ -5754,273 +5754,6 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>3f41b263d837419e</t>
-        </is>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:15:29.850559Z</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T23:30:00Z</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>68097</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F17" s="24" t="inlineStr">
-        <is>
-          <t>Revitalize GC</t>
-        </is>
-      </c>
-      <c r="G17" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Focus Amethyst</t>
-        </is>
-      </c>
-      <c r="H17" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L17" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="M17" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="N17" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O17" s="28" t="n">
-        <v>0.563407</v>
-      </c>
-      <c r="P17" s="28" t="n"/>
-      <c r="Q17" s="28" t="n">
-        <v>-0.036593</v>
-      </c>
-      <c r="R17" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U17" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
-      <c r="Y17" s="25" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n"/>
-      <c r="AD17" s="24" t="n"/>
-      <c r="AE17" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-valorant-efa-rev-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF17" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG17" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH17" s="24" t="n"/>
-      <c r="AI17" s="31" t="n"/>
-      <c r="AJ17" s="31" t="n"/>
-      <c r="AK17" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL17" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM17" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN17" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO17" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP17" s="24" t="inlineStr">
-        <is>
-          <t>Revitalize GC</t>
-        </is>
-      </c>
-      <c r="AQ17" s="24" t="inlineStr">
-        <is>
-          <t>Revitalize GC</t>
-        </is>
-      </c>
-      <c r="AR17" s="24" t="inlineStr">
-        <is>
-          <t>Revitalize GC</t>
-        </is>
-      </c>
-      <c r="AS17" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Focus Amethyst</t>
-        </is>
-      </c>
-      <c r="AT17" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Focus Amethyst</t>
-        </is>
-      </c>
-      <c r="AU17" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Focus Amethyst</t>
-        </is>
-      </c>
-      <c r="AV17" s="24" t="n"/>
-      <c r="AW17" s="24" t="n"/>
-      <c r="AX17" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY17" s="24" t="n"/>
-      <c r="AZ17" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA17" s="24" t="inlineStr">
-        <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
-        </is>
-      </c>
-      <c r="BB17" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC17" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD17" s="24" t="inlineStr">
-        <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
-        </is>
-      </c>
-      <c r="BE17" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF17" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG17" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH17" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:15:29.848917Z</t>
-        </is>
-      </c>
-      <c r="BI17" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ17" s="25" t="n"/>
-      <c r="BK17" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="BL17" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="BM17" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BN17" s="28" t="n"/>
-      <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
-      <c r="BR17" s="28" t="n"/>
-      <c r="BS17" s="28" t="n"/>
-      <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="25" t="n"/>
-      <c r="BV17" s="29" t="n"/>
-      <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="30" t="n"/>
-      <c r="BY17" s="27" t="n"/>
-      <c r="BZ17" s="24" t="n"/>
-      <c r="CA17" s="31" t="n"/>
-      <c r="CB17" s="24" t="n"/>
-      <c r="CC17" s="24" t="n"/>
-      <c r="CD17" s="24" t="n"/>
-      <c r="CE17" s="24" t="n"/>
-      <c r="CF17" s="24" t="n"/>
-      <c r="CG17" s="24" t="n"/>
-      <c r="CH17" s="24" t="n"/>
-      <c r="CI17" s="24" t="n"/>
-      <c r="CJ17" s="24" t="n"/>
-      <c r="CK17" s="24" t="n"/>
-      <c r="CL17" s="24" t="n"/>
-      <c r="CM17" s="24" t="n"/>
-      <c r="CN17" s="24" t="n"/>
-      <c r="CO17" s="24" t="n"/>
-      <c r="CP17" s="24" t="n"/>
-      <c r="CQ17" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ16" headerRowCount="1">
-  <autoFilter ref="A1:CQ16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ9" headerRowCount="1">
+  <autoFilter ref="A1:CQ9"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$16)</f>
+        <f>COUNTA('Picks'!$A$2:$A$9)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$16,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$9,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$16,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$9,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")/(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")/(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$16)/SUM('Picks'!$BX$2:$BX$16),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$9)/SUM('Picks'!$BX$2:$BX$9),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$16)</f>
+        <f>SUM('Picks'!$BY$2:$BY$9)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$16,"&lt;&gt;",'Picks'!$AB$2:$AB$16),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$9,"&lt;&gt;",'Picks'!$AB$2:$AB$9),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$16,'Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$9,'Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ16"/>
+  <dimension ref="A1:CQ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3885,1875 +3885,6 @@
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
     </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>6755683982be4362</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:48.546068Z</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>66957</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>Team Heretics</t>
-        </is>
-      </c>
-      <c r="G10" s="24" t="inlineStr">
-        <is>
-          <t>Fnatic</t>
-        </is>
-      </c>
-      <c r="H10" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I10" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J10" s="25" t="n"/>
-      <c r="K10" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L10" s="26" t="n">
-        <v>-127</v>
-      </c>
-      <c r="M10" s="27" t="n">
-        <v>1.787402</v>
-      </c>
-      <c r="N10" s="28" t="n">
-        <v>0.5594710000000001</v>
-      </c>
-      <c r="O10" s="28" t="n">
-        <v>0.537865</v>
-      </c>
-      <c r="P10" s="28" t="n"/>
-      <c r="Q10" s="28" t="n">
-        <v>-0.021606</v>
-      </c>
-      <c r="R10" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="S10" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U10" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
-      <c r="Y10" s="25" t="n"/>
-      <c r="Z10" s="26" t="n"/>
-      <c r="AA10" s="28" t="n"/>
-      <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
-      <c r="AE10" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-valorant-fnc-th-2026-08-02).</t>
-        </is>
-      </c>
-      <c r="AF10" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG10" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH10" s="24" t="n"/>
-      <c r="AI10" s="31" t="n"/>
-      <c r="AJ10" s="31" t="n"/>
-      <c r="AK10" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL10" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM10" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN10" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO10" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP10" s="24" t="inlineStr">
-        <is>
-          <t>Team Heretics</t>
-        </is>
-      </c>
-      <c r="AQ10" s="24" t="inlineStr">
-        <is>
-          <t>Team Heretics</t>
-        </is>
-      </c>
-      <c r="AR10" s="24" t="inlineStr">
-        <is>
-          <t>Team Heretics</t>
-        </is>
-      </c>
-      <c r="AS10" s="24" t="inlineStr">
-        <is>
-          <t>Fnatic</t>
-        </is>
-      </c>
-      <c r="AT10" s="24" t="inlineStr">
-        <is>
-          <t>Fnatic</t>
-        </is>
-      </c>
-      <c r="AU10" s="24" t="inlineStr">
-        <is>
-          <t>Fnatic</t>
-        </is>
-      </c>
-      <c r="AV10" s="24" t="n"/>
-      <c r="AW10" s="24" t="n"/>
-      <c r="AX10" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY10" s="24" t="n"/>
-      <c r="AZ10" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA10" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BB10" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC10" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD10" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BE10" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF10" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG10" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH10" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:41.949275Z</t>
-        </is>
-      </c>
-      <c r="BI10" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ10" s="25" t="n"/>
-      <c r="BK10" s="26" t="n">
-        <v>-127</v>
-      </c>
-      <c r="BL10" s="27" t="n">
-        <v>1.787402</v>
-      </c>
-      <c r="BM10" s="28" t="n">
-        <v>0.5594710000000001</v>
-      </c>
-      <c r="BN10" s="28" t="n"/>
-      <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
-      <c r="BR10" s="28" t="n"/>
-      <c r="BS10" s="28" t="n"/>
-      <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="25" t="n"/>
-      <c r="BV10" s="29" t="n"/>
-      <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n"/>
-      <c r="BY10" s="27" t="n"/>
-      <c r="BZ10" s="24" t="n"/>
-      <c r="CA10" s="31" t="n"/>
-      <c r="CB10" s="24" t="n"/>
-      <c r="CC10" s="24" t="n"/>
-      <c r="CD10" s="24" t="n"/>
-      <c r="CE10" s="24" t="n"/>
-      <c r="CF10" s="24" t="n"/>
-      <c r="CG10" s="24" t="n"/>
-      <c r="CH10" s="24" t="n"/>
-      <c r="CI10" s="24" t="n"/>
-      <c r="CJ10" s="24" t="n"/>
-      <c r="CK10" s="24" t="n"/>
-      <c r="CL10" s="24" t="n"/>
-      <c r="CM10" s="24" t="n"/>
-      <c r="CN10" s="24" t="n"/>
-      <c r="CO10" s="24" t="n"/>
-      <c r="CP10" s="24" t="n"/>
-      <c r="CQ10" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>1523276642c7488b</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:48.546068Z</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>67311</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t>KRÜ Esports</t>
-        </is>
-      </c>
-      <c r="G11" s="24" t="inlineStr">
-        <is>
-          <t>Cloud9</t>
-        </is>
-      </c>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I11" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L11" s="26" t="n">
-        <v>138</v>
-      </c>
-      <c r="M11" s="27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="N11" s="28" t="n">
-        <v>0.420168</v>
-      </c>
-      <c r="O11" s="28" t="n">
-        <v>0.518772</v>
-      </c>
-      <c r="P11" s="28" t="n"/>
-      <c r="Q11" s="28" t="n">
-        <v>0.098604</v>
-      </c>
-      <c r="R11" s="26" t="n">
-        <v>69</v>
-      </c>
-      <c r="S11" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U11" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
-      <c r="Y11" s="25" t="n"/>
-      <c r="Z11" s="26" t="n"/>
-      <c r="AA11" s="28" t="n"/>
-      <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
-      <c r="AE11" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-c9-kr-2026-08-02).</t>
-        </is>
-      </c>
-      <c r="AF11" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG11" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH11" s="24" t="n"/>
-      <c r="AI11" s="31" t="n"/>
-      <c r="AJ11" s="31" t="n"/>
-      <c r="AK11" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL11" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM11" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN11" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO11" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP11" s="24" t="inlineStr">
-        <is>
-          <t>KRÜ Esports</t>
-        </is>
-      </c>
-      <c r="AQ11" s="24" t="inlineStr">
-        <is>
-          <t>KRÜ Esports</t>
-        </is>
-      </c>
-      <c r="AR11" s="24" t="inlineStr">
-        <is>
-          <t>KRÜ Esports</t>
-        </is>
-      </c>
-      <c r="AS11" s="24" t="inlineStr">
-        <is>
-          <t>Cloud9</t>
-        </is>
-      </c>
-      <c r="AT11" s="24" t="inlineStr">
-        <is>
-          <t>Cloud9</t>
-        </is>
-      </c>
-      <c r="AU11" s="24" t="inlineStr">
-        <is>
-          <t>Cloud9</t>
-        </is>
-      </c>
-      <c r="AV11" s="24" t="n"/>
-      <c r="AW11" s="24" t="n"/>
-      <c r="AX11" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY11" s="24" t="n"/>
-      <c r="AZ11" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA11" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BB11" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC11" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD11" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BE11" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF11" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG11" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH11" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:42.402563Z</t>
-        </is>
-      </c>
-      <c r="BI11" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ11" s="25" t="n"/>
-      <c r="BK11" s="26" t="n">
-        <v>138</v>
-      </c>
-      <c r="BL11" s="27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BM11" s="28" t="n">
-        <v>0.420168</v>
-      </c>
-      <c r="BN11" s="28" t="n"/>
-      <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
-      <c r="BR11" s="28" t="n"/>
-      <c r="BS11" s="28" t="n"/>
-      <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="25" t="n"/>
-      <c r="BV11" s="29" t="n"/>
-      <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n"/>
-      <c r="BY11" s="27" t="n"/>
-      <c r="BZ11" s="24" t="n"/>
-      <c r="CA11" s="31" t="n"/>
-      <c r="CB11" s="24" t="n"/>
-      <c r="CC11" s="24" t="n"/>
-      <c r="CD11" s="24" t="n"/>
-      <c r="CE11" s="24" t="n"/>
-      <c r="CF11" s="24" t="n"/>
-      <c r="CG11" s="24" t="n"/>
-      <c r="CH11" s="24" t="n"/>
-      <c r="CI11" s="24" t="n"/>
-      <c r="CJ11" s="24" t="n"/>
-      <c r="CK11" s="24" t="n"/>
-      <c r="CL11" s="24" t="n"/>
-      <c r="CM11" s="24" t="n"/>
-      <c r="CN11" s="24" t="n"/>
-      <c r="CO11" s="24" t="n"/>
-      <c r="CP11" s="24" t="n"/>
-      <c r="CQ11" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>3327695c91744534</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:48.546068Z</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>67386</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F12" s="24" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="G12" s="24" t="inlineStr">
-        <is>
-          <t>G2 Esports</t>
-        </is>
-      </c>
-      <c r="H12" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I12" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J12" s="25" t="n"/>
-      <c r="K12" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L12" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M12" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N12" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O12" s="28" t="n">
-        <v>0.626584</v>
-      </c>
-      <c r="P12" s="28" t="n"/>
-      <c r="Q12" s="28" t="n">
-        <v>-0.013704</v>
-      </c>
-      <c r="R12" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="S12" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T12" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U12" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
-      <c r="Y12" s="25" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="28" t="n"/>
-      <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
-      <c r="AE12" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-g2-sen-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF12" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG12" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH12" s="24" t="n"/>
-      <c r="AI12" s="31" t="n"/>
-      <c r="AJ12" s="31" t="n"/>
-      <c r="AK12" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL12" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM12" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN12" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO12" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP12" s="24" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="AQ12" s="24" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="AR12" s="24" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="AS12" s="24" t="inlineStr">
-        <is>
-          <t>G2 Esports</t>
-        </is>
-      </c>
-      <c r="AT12" s="24" t="inlineStr">
-        <is>
-          <t>G2 Esports</t>
-        </is>
-      </c>
-      <c r="AU12" s="24" t="inlineStr">
-        <is>
-          <t>G2 Esports</t>
-        </is>
-      </c>
-      <c r="AV12" s="24" t="n"/>
-      <c r="AW12" s="24" t="n"/>
-      <c r="AX12" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY12" s="24" t="n"/>
-      <c r="AZ12" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA12" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BB12" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC12" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD12" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BE12" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF12" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG12" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH12" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:42.939409Z</t>
-        </is>
-      </c>
-      <c r="BI12" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ12" s="25" t="n"/>
-      <c r="BK12" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL12" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM12" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN12" s="28" t="n"/>
-      <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
-      <c r="BR12" s="28" t="n"/>
-      <c r="BS12" s="28" t="n"/>
-      <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="25" t="n"/>
-      <c r="BV12" s="29" t="n"/>
-      <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="30" t="n"/>
-      <c r="BY12" s="27" t="n"/>
-      <c r="BZ12" s="24" t="n"/>
-      <c r="CA12" s="31" t="n"/>
-      <c r="CB12" s="24" t="n"/>
-      <c r="CC12" s="24" t="n"/>
-      <c r="CD12" s="24" t="n"/>
-      <c r="CE12" s="24" t="n"/>
-      <c r="CF12" s="24" t="n"/>
-      <c r="CG12" s="24" t="n"/>
-      <c r="CH12" s="24" t="n"/>
-      <c r="CI12" s="24" t="n"/>
-      <c r="CJ12" s="24" t="n"/>
-      <c r="CK12" s="24" t="n"/>
-      <c r="CL12" s="24" t="n"/>
-      <c r="CM12" s="24" t="n"/>
-      <c r="CN12" s="24" t="n"/>
-      <c r="CO12" s="24" t="n"/>
-      <c r="CP12" s="24" t="n"/>
-      <c r="CQ12" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>67e734c757684e31</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:48.546068Z</t>
-        </is>
-      </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>67569</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F13" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="G13" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="H13" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I13" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J13" s="25" t="n"/>
-      <c r="K13" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L13" s="26" t="n">
-        <v>-213</v>
-      </c>
-      <c r="M13" s="27" t="n">
-        <v>1.469484</v>
-      </c>
-      <c r="N13" s="28" t="n">
-        <v>0.680511</v>
-      </c>
-      <c r="O13" s="28" t="n">
-        <v>0.765185</v>
-      </c>
-      <c r="P13" s="28" t="n"/>
-      <c r="Q13" s="28" t="n">
-        <v>0.084674</v>
-      </c>
-      <c r="R13" s="26" t="n">
-        <v>62</v>
-      </c>
-      <c r="S13" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U13" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
-      <c r="Y13" s="25" t="n"/>
-      <c r="Z13" s="26" t="n"/>
-      <c r="AA13" s="28" t="n"/>
-      <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
-      <c r="AE13" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF13" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG13" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH13" s="24" t="n"/>
-      <c r="AI13" s="31" t="n"/>
-      <c r="AJ13" s="31" t="n"/>
-      <c r="AK13" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL13" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM13" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN13" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO13" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP13" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="AQ13" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="AR13" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="AS13" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="AT13" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="AU13" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="AV13" s="24" t="n"/>
-      <c r="AW13" s="24" t="n"/>
-      <c r="AX13" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY13" s="24" t="n"/>
-      <c r="AZ13" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA13" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BB13" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC13" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD13" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BE13" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF13" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG13" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH13" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:43.967259Z</t>
-        </is>
-      </c>
-      <c r="BI13" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ13" s="25" t="n"/>
-      <c r="BK13" s="26" t="n">
-        <v>-213</v>
-      </c>
-      <c r="BL13" s="27" t="n">
-        <v>1.469484</v>
-      </c>
-      <c r="BM13" s="28" t="n">
-        <v>0.680511</v>
-      </c>
-      <c r="BN13" s="28" t="n"/>
-      <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
-      <c r="BR13" s="28" t="n"/>
-      <c r="BS13" s="28" t="n"/>
-      <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="25" t="n"/>
-      <c r="BV13" s="29" t="n"/>
-      <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="30" t="n"/>
-      <c r="BY13" s="27" t="n"/>
-      <c r="BZ13" s="24" t="n"/>
-      <c r="CA13" s="31" t="n"/>
-      <c r="CB13" s="24" t="n"/>
-      <c r="CC13" s="24" t="n"/>
-      <c r="CD13" s="24" t="n"/>
-      <c r="CE13" s="24" t="n"/>
-      <c r="CF13" s="24" t="n"/>
-      <c r="CG13" s="24" t="n"/>
-      <c r="CH13" s="24" t="n"/>
-      <c r="CI13" s="24" t="n"/>
-      <c r="CJ13" s="24" t="n"/>
-      <c r="CK13" s="24" t="n"/>
-      <c r="CL13" s="24" t="n"/>
-      <c r="CM13" s="24" t="n"/>
-      <c r="CN13" s="24" t="n"/>
-      <c r="CO13" s="24" t="n"/>
-      <c r="CP13" s="24" t="n"/>
-      <c r="CQ13" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>68ea0465031e495b</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:48.546068Z</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>67987</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F14" s="24" t="inlineStr">
-        <is>
-          <t>The Spiders</t>
-        </is>
-      </c>
-      <c r="G14" s="24" t="inlineStr">
-        <is>
-          <t>HIMMERS</t>
-        </is>
-      </c>
-      <c r="H14" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L14" s="26" t="n">
-        <v>113</v>
-      </c>
-      <c r="M14" s="27" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="N14" s="28" t="n">
-        <v>0.469484</v>
-      </c>
-      <c r="O14" s="28" t="n">
-        <v>0.520495</v>
-      </c>
-      <c r="P14" s="28" t="n"/>
-      <c r="Q14" s="28" t="n">
-        <v>0.051011</v>
-      </c>
-      <c r="R14" s="26" t="n">
-        <v>46</v>
-      </c>
-      <c r="S14" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U14" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
-      <c r="Y14" s="25" t="n"/>
-      <c r="Z14" s="26" t="n"/>
-      <c r="AA14" s="28" t="n"/>
-      <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n"/>
-      <c r="AD14" s="24" t="n"/>
-      <c r="AE14" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-valorant-him-spi-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF14" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG14" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH14" s="24" t="n"/>
-      <c r="AI14" s="31" t="n"/>
-      <c r="AJ14" s="31" t="n"/>
-      <c r="AK14" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL14" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM14" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN14" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO14" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP14" s="24" t="inlineStr">
-        <is>
-          <t>The Spiders</t>
-        </is>
-      </c>
-      <c r="AQ14" s="24" t="inlineStr">
-        <is>
-          <t>The Spiders</t>
-        </is>
-      </c>
-      <c r="AR14" s="24" t="inlineStr">
-        <is>
-          <t>The Spiders</t>
-        </is>
-      </c>
-      <c r="AS14" s="24" t="inlineStr">
-        <is>
-          <t>HIMMERS</t>
-        </is>
-      </c>
-      <c r="AT14" s="24" t="inlineStr">
-        <is>
-          <t>HIMMERS</t>
-        </is>
-      </c>
-      <c r="AU14" s="24" t="inlineStr">
-        <is>
-          <t>HIMMERS</t>
-        </is>
-      </c>
-      <c r="AV14" s="24" t="n"/>
-      <c r="AW14" s="24" t="n"/>
-      <c r="AX14" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY14" s="24" t="n"/>
-      <c r="AZ14" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA14" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BB14" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC14" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD14" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BE14" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF14" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG14" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH14" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:45.603247Z</t>
-        </is>
-      </c>
-      <c r="BI14" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ14" s="25" t="n"/>
-      <c r="BK14" s="26" t="n">
-        <v>113</v>
-      </c>
-      <c r="BL14" s="27" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BM14" s="28" t="n">
-        <v>0.469484</v>
-      </c>
-      <c r="BN14" s="28" t="n"/>
-      <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
-      <c r="BR14" s="28" t="n"/>
-      <c r="BS14" s="28" t="n"/>
-      <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="25" t="n"/>
-      <c r="BV14" s="29" t="n"/>
-      <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="30" t="n"/>
-      <c r="BY14" s="27" t="n"/>
-      <c r="BZ14" s="24" t="n"/>
-      <c r="CA14" s="31" t="n"/>
-      <c r="CB14" s="24" t="n"/>
-      <c r="CC14" s="24" t="n"/>
-      <c r="CD14" s="24" t="n"/>
-      <c r="CE14" s="24" t="n"/>
-      <c r="CF14" s="24" t="n"/>
-      <c r="CG14" s="24" t="n"/>
-      <c r="CH14" s="24" t="n"/>
-      <c r="CI14" s="24" t="n"/>
-      <c r="CJ14" s="24" t="n"/>
-      <c r="CK14" s="24" t="n"/>
-      <c r="CL14" s="24" t="n"/>
-      <c r="CM14" s="24" t="n"/>
-      <c r="CN14" s="24" t="n"/>
-      <c r="CO14" s="24" t="n"/>
-      <c r="CP14" s="24" t="n"/>
-      <c r="CQ14" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>e4df25237f55473f</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:48.546068Z</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>67989</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
-        <is>
-          <t>SwimTrek Blue</t>
-        </is>
-      </c>
-      <c r="G15" s="24" t="inlineStr">
-        <is>
-          <t>FlyQuest RED</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L15" s="26" t="n">
-        <v>-194</v>
-      </c>
-      <c r="M15" s="27" t="n">
-        <v>1.515464</v>
-      </c>
-      <c r="N15" s="28" t="n">
-        <v>0.659864</v>
-      </c>
-      <c r="O15" s="28" t="n">
-        <v>0.569339</v>
-      </c>
-      <c r="P15" s="28" t="n"/>
-      <c r="Q15" s="28" t="n">
-        <v>-0.09052499999999999</v>
-      </c>
-      <c r="R15" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T15" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U15" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
-      <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
-      <c r="AE15" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-flyr-swim-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF15" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG15" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH15" s="24" t="n"/>
-      <c r="AI15" s="31" t="n"/>
-      <c r="AJ15" s="31" t="n"/>
-      <c r="AK15" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL15" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM15" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN15" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO15" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP15" s="24" t="inlineStr">
-        <is>
-          <t>SwimTrek Blue</t>
-        </is>
-      </c>
-      <c r="AQ15" s="24" t="inlineStr">
-        <is>
-          <t>SwimTrek Blue</t>
-        </is>
-      </c>
-      <c r="AR15" s="24" t="inlineStr">
-        <is>
-          <t>SwimTrek Blue</t>
-        </is>
-      </c>
-      <c r="AS15" s="24" t="inlineStr">
-        <is>
-          <t>FlyQuest RED</t>
-        </is>
-      </c>
-      <c r="AT15" s="24" t="inlineStr">
-        <is>
-          <t>FlyQuest RED</t>
-        </is>
-      </c>
-      <c r="AU15" s="24" t="inlineStr">
-        <is>
-          <t>FlyQuest RED</t>
-        </is>
-      </c>
-      <c r="AV15" s="24" t="n"/>
-      <c r="AW15" s="24" t="n"/>
-      <c r="AX15" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY15" s="24" t="n"/>
-      <c r="AZ15" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA15" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BB15" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC15" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD15" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BE15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG15" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:46.542257Z</t>
-        </is>
-      </c>
-      <c r="BI15" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ15" s="25" t="n"/>
-      <c r="BK15" s="26" t="n">
-        <v>-194</v>
-      </c>
-      <c r="BL15" s="27" t="n">
-        <v>1.515464</v>
-      </c>
-      <c r="BM15" s="28" t="n">
-        <v>0.659864</v>
-      </c>
-      <c r="BN15" s="28" t="n"/>
-      <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
-      <c r="BS15" s="28" t="n"/>
-      <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
-      <c r="BV15" s="29" t="n"/>
-      <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n"/>
-      <c r="BY15" s="27" t="n"/>
-      <c r="BZ15" s="24" t="n"/>
-      <c r="CA15" s="31" t="n"/>
-      <c r="CB15" s="24" t="n"/>
-      <c r="CC15" s="24" t="n"/>
-      <c r="CD15" s="24" t="n"/>
-      <c r="CE15" s="24" t="n"/>
-      <c r="CF15" s="24" t="n"/>
-      <c r="CG15" s="24" t="n"/>
-      <c r="CH15" s="24" t="n"/>
-      <c r="CI15" s="24" t="n"/>
-      <c r="CJ15" s="24" t="n"/>
-      <c r="CK15" s="24" t="n"/>
-      <c r="CL15" s="24" t="n"/>
-      <c r="CM15" s="24" t="n"/>
-      <c r="CN15" s="24" t="n"/>
-      <c r="CO15" s="24" t="n"/>
-      <c r="CP15" s="24" t="n"/>
-      <c r="CQ15" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>cfdd59d2171e426f</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:48.546068Z</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T23:30:00Z</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>68097</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>Revitalize GC</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Focus Amethyst</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L16" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M16" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N16" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O16" s="28" t="n">
-        <v>0.563407</v>
-      </c>
-      <c r="P16" s="28" t="n"/>
-      <c r="Q16" s="28" t="n">
-        <v>-0.076881</v>
-      </c>
-      <c r="R16" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U16" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
-      <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
-      <c r="AE16" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-efa-rev-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF16" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG16" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH16" s="24" t="n"/>
-      <c r="AI16" s="31" t="n"/>
-      <c r="AJ16" s="31" t="n"/>
-      <c r="AK16" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL16" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM16" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN16" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO16" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP16" s="24" t="inlineStr">
-        <is>
-          <t>Revitalize GC</t>
-        </is>
-      </c>
-      <c r="AQ16" s="24" t="inlineStr">
-        <is>
-          <t>Revitalize GC</t>
-        </is>
-      </c>
-      <c r="AR16" s="24" t="inlineStr">
-        <is>
-          <t>Revitalize GC</t>
-        </is>
-      </c>
-      <c r="AS16" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Focus Amethyst</t>
-        </is>
-      </c>
-      <c r="AT16" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Focus Amethyst</t>
-        </is>
-      </c>
-      <c r="AU16" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Focus Amethyst</t>
-        </is>
-      </c>
-      <c r="AV16" s="24" t="n"/>
-      <c r="AW16" s="24" t="n"/>
-      <c r="AX16" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY16" s="24" t="n"/>
-      <c r="AZ16" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA16" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BB16" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC16" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD16" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BE16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG16" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:48.544086Z</t>
-        </is>
-      </c>
-      <c r="BI16" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ16" s="25" t="n"/>
-      <c r="BK16" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL16" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM16" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN16" s="28" t="n"/>
-      <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
-      <c r="BS16" s="28" t="n"/>
-      <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
-      <c r="BV16" s="29" t="n"/>
-      <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n"/>
-      <c r="BY16" s="27" t="n"/>
-      <c r="BZ16" s="24" t="n"/>
-      <c r="CA16" s="31" t="n"/>
-      <c r="CB16" s="24" t="n"/>
-      <c r="CC16" s="24" t="n"/>
-      <c r="CD16" s="24" t="n"/>
-      <c r="CE16" s="24" t="n"/>
-      <c r="CF16" s="24" t="n"/>
-      <c r="CG16" s="24" t="n"/>
-      <c r="CH16" s="24" t="n"/>
-      <c r="CI16" s="24" t="n"/>
-      <c r="CJ16" s="24" t="n"/>
-      <c r="CK16" s="24" t="n"/>
-      <c r="CL16" s="24" t="n"/>
-      <c r="CM16" s="24" t="n"/>
-      <c r="CN16" s="24" t="n"/>
-      <c r="CO16" s="24" t="n"/>
-      <c r="CP16" s="24" t="n"/>
-      <c r="CQ16" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ9" headerRowCount="1">
-  <autoFilter ref="A1:CQ9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ15" headerRowCount="1">
+  <autoFilter ref="A1:CQ15"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$9)</f>
+        <f>COUNTA('Picks'!$A$2:$A$15)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$9,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$9,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")/(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$9)/SUM('Picks'!$BX$2:$BX$9),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$9)</f>
+        <f>SUM('Picks'!$BY$2:$BY$15)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$9,"&lt;&gt;",'Picks'!$AB$2:$AB$9),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$9,'Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ9"/>
+  <dimension ref="A1:CQ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3885,6 +3885,1608 @@
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
     </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>94ceb126079549cb</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:56.490286Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>66957</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Team Heretics</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.537865</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>-0.021606</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="n"/>
+      <c r="W10" s="26" t="n"/>
+      <c r="X10" s="26" t="n"/>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n"/>
+      <c r="AD10" s="24" t="n"/>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-valorant-fnc-th-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>Team Heretics</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>Team Heretics</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>Team Heretics</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:49.680825Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
+      <c r="CQ10" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>f2dd24a716e84ae0</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:56.490286Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>67311</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>KRÜ Esports</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.518772</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.098604</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n"/>
+      <c r="AD11" s="24" t="n"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-c9-kr-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>KRÜ Esports</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>KRÜ Esports</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>KRÜ Esports</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:50.165415Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>891a75f188994c50</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:56.490286Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>67386</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.626584</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>-0.013704</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="26" t="n"/>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n"/>
+      <c r="AD12" s="24" t="n"/>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-g2-sen-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:50.730936Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>493aced23d914965</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:56.490286Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.765185</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.074783</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>57</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:51.807690Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>42660a03f92044ad</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:56.490286Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>67987</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>HIMMERS</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.520495</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>0.110659</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="n"/>
+      <c r="W14" s="26" t="n"/>
+      <c r="X14" s="26" t="n"/>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n"/>
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-valorant-him-spi-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>HIMMERS</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>HIMMERS</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>HIMMERS</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:53.324618Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>c329265245074f77</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:56.490286Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>67989</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.569339</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>-0.09052499999999999</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-flyr-swim-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:54.386243Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ15" headerRowCount="1">
-  <autoFilter ref="A1:CQ15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ16" headerRowCount="1">
+  <autoFilter ref="A1:CQ16"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$15)</f>
+        <f>COUNTA('Picks'!$A$2:$A$16)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$16,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$16,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")/(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$16)/SUM('Picks'!$BX$2:$BX$16),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$15)</f>
+        <f>SUM('Picks'!$BY$2:$BY$16)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$16,"&lt;&gt;",'Picks'!$AB$2:$AB$16),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$16,'Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ15"/>
+  <dimension ref="A1:CQ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4155,12 +4155,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>f2dd24a716e84ae0</t>
+          <t>d22d290846004f8c</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:56.490286Z</t>
+          <t>2026-08-02T18:09:24.902767Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4214,11 +4214,11 @@
         <v>0.420168</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.518772</v>
+        <v>0.518775</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.098604</v>
+        <v>0.098607</v>
       </c>
       <c r="R11" s="26" t="n">
         <v>69</v>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:50.165415Z</t>
+          <t>2026-08-02T18:09:18.656978Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4422,12 +4422,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>891a75f188994c50</t>
+          <t>6d46e35997cd4159</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:56.490286Z</t>
+          <t>2026-08-02T18:09:24.902767Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4481,11 +4481,11 @@
         <v>0.640288</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.626584</v>
+        <v>0.626621</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>-0.013704</v>
+        <v>-0.013667</v>
       </c>
       <c r="R12" s="26" t="n">
         <v>13</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:50.730936Z</t>
+          <t>2026-08-02T18:09:19.194193Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4689,12 +4689,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>493aced23d914965</t>
+          <t>11719642d1be4a0d</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:56.490286Z</t>
+          <t>2026-08-02T18:09:24.902767Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4748,11 +4748,11 @@
         <v>0.690402</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.765185</v>
+        <v>0.765342</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.074783</v>
+        <v>0.07494000000000001</v>
       </c>
       <c r="R13" s="26" t="n">
         <v>57</v>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:51.807690Z</t>
+          <t>2026-08-02T18:09:20.414393Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4956,12 +4956,12 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>42660a03f92044ad</t>
+          <t>7effbe28e3324f86</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:56.490286Z</t>
+          <t>2026-08-02T18:09:24.902767Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:53.324618Z</t>
+          <t>2026-08-02T18:09:21.952693Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5223,12 +5223,12 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>c329265245074f77</t>
+          <t>4c90fbe615f74a89</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:56.490286Z</t>
+          <t>2026-08-02T18:09:24.902767Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:54.386243Z</t>
+          <t>2026-08-02T18:09:22.943314Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5487,6 +5487,273 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>e9769b6cd68141c1</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:09:24.902767Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>68095</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>ROSO GC</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.519652</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.149282</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>95</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-valorant-roso-mvs-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>ROSO GC</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>ROSO GC</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>ROSO GC</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:09:23.897138Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ16" headerRowCount="1">
-  <autoFilter ref="A1:CQ16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ10" headerRowCount="1">
+  <autoFilter ref="A1:CQ10"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$16)</f>
+        <f>COUNTA('Picks'!$A$2:$A$10)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$16,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$10,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$16,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$10,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")/(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")/(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$16)/SUM('Picks'!$BX$2:$BX$16),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$10)/SUM('Picks'!$BX$2:$BX$10),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$16)</f>
+        <f>SUM('Picks'!$BY$2:$BY$10)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$16,"&lt;&gt;",'Picks'!$AB$2:$AB$16),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$10,"&lt;&gt;",'Picks'!$AB$2:$AB$10),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$16,'Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$10,'Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ16"/>
+  <dimension ref="A1:CQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4152,1608 +4152,6 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>d22d290846004f8c</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:24.902767Z</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>67311</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t>KRÜ Esports</t>
-        </is>
-      </c>
-      <c r="G11" s="24" t="inlineStr">
-        <is>
-          <t>Cloud9</t>
-        </is>
-      </c>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I11" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L11" s="26" t="n">
-        <v>138</v>
-      </c>
-      <c r="M11" s="27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="N11" s="28" t="n">
-        <v>0.420168</v>
-      </c>
-      <c r="O11" s="28" t="n">
-        <v>0.518775</v>
-      </c>
-      <c r="P11" s="28" t="n"/>
-      <c r="Q11" s="28" t="n">
-        <v>0.098607</v>
-      </c>
-      <c r="R11" s="26" t="n">
-        <v>69</v>
-      </c>
-      <c r="S11" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U11" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
-      <c r="Y11" s="25" t="n"/>
-      <c r="Z11" s="26" t="n"/>
-      <c r="AA11" s="28" t="n"/>
-      <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
-      <c r="AE11" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-c9-kr-2026-08-02).</t>
-        </is>
-      </c>
-      <c r="AF11" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG11" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH11" s="24" t="n"/>
-      <c r="AI11" s="31" t="n"/>
-      <c r="AJ11" s="31" t="n"/>
-      <c r="AK11" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL11" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM11" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN11" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO11" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP11" s="24" t="inlineStr">
-        <is>
-          <t>KRÜ Esports</t>
-        </is>
-      </c>
-      <c r="AQ11" s="24" t="inlineStr">
-        <is>
-          <t>KRÜ Esports</t>
-        </is>
-      </c>
-      <c r="AR11" s="24" t="inlineStr">
-        <is>
-          <t>KRÜ Esports</t>
-        </is>
-      </c>
-      <c r="AS11" s="24" t="inlineStr">
-        <is>
-          <t>Cloud9</t>
-        </is>
-      </c>
-      <c r="AT11" s="24" t="inlineStr">
-        <is>
-          <t>Cloud9</t>
-        </is>
-      </c>
-      <c r="AU11" s="24" t="inlineStr">
-        <is>
-          <t>Cloud9</t>
-        </is>
-      </c>
-      <c r="AV11" s="24" t="n"/>
-      <c r="AW11" s="24" t="n"/>
-      <c r="AX11" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY11" s="24" t="n"/>
-      <c r="AZ11" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA11" s="24" t="inlineStr">
-        <is>
-          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
-        </is>
-      </c>
-      <c r="BB11" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC11" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD11" s="24" t="inlineStr">
-        <is>
-          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
-        </is>
-      </c>
-      <c r="BE11" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF11" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG11" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH11" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:18.656978Z</t>
-        </is>
-      </c>
-      <c r="BI11" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ11" s="25" t="n"/>
-      <c r="BK11" s="26" t="n">
-        <v>138</v>
-      </c>
-      <c r="BL11" s="27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BM11" s="28" t="n">
-        <v>0.420168</v>
-      </c>
-      <c r="BN11" s="28" t="n"/>
-      <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
-      <c r="BR11" s="28" t="n"/>
-      <c r="BS11" s="28" t="n"/>
-      <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="25" t="n"/>
-      <c r="BV11" s="29" t="n"/>
-      <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n"/>
-      <c r="BY11" s="27" t="n"/>
-      <c r="BZ11" s="24" t="n"/>
-      <c r="CA11" s="31" t="n"/>
-      <c r="CB11" s="24" t="n"/>
-      <c r="CC11" s="24" t="n"/>
-      <c r="CD11" s="24" t="n"/>
-      <c r="CE11" s="24" t="n"/>
-      <c r="CF11" s="24" t="n"/>
-      <c r="CG11" s="24" t="n"/>
-      <c r="CH11" s="24" t="n"/>
-      <c r="CI11" s="24" t="n"/>
-      <c r="CJ11" s="24" t="n"/>
-      <c r="CK11" s="24" t="n"/>
-      <c r="CL11" s="24" t="n"/>
-      <c r="CM11" s="24" t="n"/>
-      <c r="CN11" s="24" t="n"/>
-      <c r="CO11" s="24" t="n"/>
-      <c r="CP11" s="24" t="n"/>
-      <c r="CQ11" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>6d46e35997cd4159</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:24.902767Z</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>67386</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F12" s="24" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="G12" s="24" t="inlineStr">
-        <is>
-          <t>G2 Esports</t>
-        </is>
-      </c>
-      <c r="H12" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I12" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J12" s="25" t="n"/>
-      <c r="K12" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L12" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M12" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N12" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O12" s="28" t="n">
-        <v>0.626621</v>
-      </c>
-      <c r="P12" s="28" t="n"/>
-      <c r="Q12" s="28" t="n">
-        <v>-0.013667</v>
-      </c>
-      <c r="R12" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="S12" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T12" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U12" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
-      <c r="Y12" s="25" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="28" t="n"/>
-      <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
-      <c r="AE12" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-g2-sen-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF12" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG12" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH12" s="24" t="n"/>
-      <c r="AI12" s="31" t="n"/>
-      <c r="AJ12" s="31" t="n"/>
-      <c r="AK12" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL12" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM12" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN12" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO12" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP12" s="24" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="AQ12" s="24" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="AR12" s="24" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="AS12" s="24" t="inlineStr">
-        <is>
-          <t>G2 Esports</t>
-        </is>
-      </c>
-      <c r="AT12" s="24" t="inlineStr">
-        <is>
-          <t>G2 Esports</t>
-        </is>
-      </c>
-      <c r="AU12" s="24" t="inlineStr">
-        <is>
-          <t>G2 Esports</t>
-        </is>
-      </c>
-      <c r="AV12" s="24" t="n"/>
-      <c r="AW12" s="24" t="n"/>
-      <c r="AX12" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY12" s="24" t="n"/>
-      <c r="AZ12" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA12" s="24" t="inlineStr">
-        <is>
-          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
-        </is>
-      </c>
-      <c r="BB12" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC12" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD12" s="24" t="inlineStr">
-        <is>
-          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
-        </is>
-      </c>
-      <c r="BE12" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF12" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG12" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH12" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:19.194193Z</t>
-        </is>
-      </c>
-      <c r="BI12" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ12" s="25" t="n"/>
-      <c r="BK12" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL12" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM12" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN12" s="28" t="n"/>
-      <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
-      <c r="BR12" s="28" t="n"/>
-      <c r="BS12" s="28" t="n"/>
-      <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="25" t="n"/>
-      <c r="BV12" s="29" t="n"/>
-      <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="30" t="n"/>
-      <c r="BY12" s="27" t="n"/>
-      <c r="BZ12" s="24" t="n"/>
-      <c r="CA12" s="31" t="n"/>
-      <c r="CB12" s="24" t="n"/>
-      <c r="CC12" s="24" t="n"/>
-      <c r="CD12" s="24" t="n"/>
-      <c r="CE12" s="24" t="n"/>
-      <c r="CF12" s="24" t="n"/>
-      <c r="CG12" s="24" t="n"/>
-      <c r="CH12" s="24" t="n"/>
-      <c r="CI12" s="24" t="n"/>
-      <c r="CJ12" s="24" t="n"/>
-      <c r="CK12" s="24" t="n"/>
-      <c r="CL12" s="24" t="n"/>
-      <c r="CM12" s="24" t="n"/>
-      <c r="CN12" s="24" t="n"/>
-      <c r="CO12" s="24" t="n"/>
-      <c r="CP12" s="24" t="n"/>
-      <c r="CQ12" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>11719642d1be4a0d</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:24.902767Z</t>
-        </is>
-      </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>67569</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F13" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="G13" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="H13" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I13" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J13" s="25" t="n"/>
-      <c r="K13" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L13" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M13" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N13" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O13" s="28" t="n">
-        <v>0.765342</v>
-      </c>
-      <c r="P13" s="28" t="n"/>
-      <c r="Q13" s="28" t="n">
-        <v>0.07494000000000001</v>
-      </c>
-      <c r="R13" s="26" t="n">
-        <v>57</v>
-      </c>
-      <c r="S13" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U13" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
-      <c r="Y13" s="25" t="n"/>
-      <c r="Z13" s="26" t="n"/>
-      <c r="AA13" s="28" t="n"/>
-      <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
-      <c r="AE13" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF13" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG13" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH13" s="24" t="n"/>
-      <c r="AI13" s="31" t="n"/>
-      <c r="AJ13" s="31" t="n"/>
-      <c r="AK13" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL13" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM13" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN13" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO13" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP13" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="AQ13" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="AR13" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="AS13" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="AT13" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="AU13" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="AV13" s="24" t="n"/>
-      <c r="AW13" s="24" t="n"/>
-      <c r="AX13" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY13" s="24" t="n"/>
-      <c r="AZ13" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA13" s="24" t="inlineStr">
-        <is>
-          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
-        </is>
-      </c>
-      <c r="BB13" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC13" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD13" s="24" t="inlineStr">
-        <is>
-          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
-        </is>
-      </c>
-      <c r="BE13" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF13" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG13" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH13" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:20.414393Z</t>
-        </is>
-      </c>
-      <c r="BI13" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ13" s="25" t="n"/>
-      <c r="BK13" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL13" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM13" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN13" s="28" t="n"/>
-      <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
-      <c r="BR13" s="28" t="n"/>
-      <c r="BS13" s="28" t="n"/>
-      <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="25" t="n"/>
-      <c r="BV13" s="29" t="n"/>
-      <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="30" t="n"/>
-      <c r="BY13" s="27" t="n"/>
-      <c r="BZ13" s="24" t="n"/>
-      <c r="CA13" s="31" t="n"/>
-      <c r="CB13" s="24" t="n"/>
-      <c r="CC13" s="24" t="n"/>
-      <c r="CD13" s="24" t="n"/>
-      <c r="CE13" s="24" t="n"/>
-      <c r="CF13" s="24" t="n"/>
-      <c r="CG13" s="24" t="n"/>
-      <c r="CH13" s="24" t="n"/>
-      <c r="CI13" s="24" t="n"/>
-      <c r="CJ13" s="24" t="n"/>
-      <c r="CK13" s="24" t="n"/>
-      <c r="CL13" s="24" t="n"/>
-      <c r="CM13" s="24" t="n"/>
-      <c r="CN13" s="24" t="n"/>
-      <c r="CO13" s="24" t="n"/>
-      <c r="CP13" s="24" t="n"/>
-      <c r="CQ13" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>7effbe28e3324f86</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:24.902767Z</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>67987</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F14" s="24" t="inlineStr">
-        <is>
-          <t>The Spiders</t>
-        </is>
-      </c>
-      <c r="G14" s="24" t="inlineStr">
-        <is>
-          <t>HIMMERS</t>
-        </is>
-      </c>
-      <c r="H14" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L14" s="26" t="n">
-        <v>144</v>
-      </c>
-      <c r="M14" s="27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="N14" s="28" t="n">
-        <v>0.409836</v>
-      </c>
-      <c r="O14" s="28" t="n">
-        <v>0.520495</v>
-      </c>
-      <c r="P14" s="28" t="n"/>
-      <c r="Q14" s="28" t="n">
-        <v>0.110659</v>
-      </c>
-      <c r="R14" s="26" t="n">
-        <v>75</v>
-      </c>
-      <c r="S14" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U14" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
-      <c r="Y14" s="25" t="n"/>
-      <c r="Z14" s="26" t="n"/>
-      <c r="AA14" s="28" t="n"/>
-      <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n"/>
-      <c r="AD14" s="24" t="n"/>
-      <c r="AE14" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-valorant-him-spi-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF14" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG14" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH14" s="24" t="n"/>
-      <c r="AI14" s="31" t="n"/>
-      <c r="AJ14" s="31" t="n"/>
-      <c r="AK14" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL14" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM14" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN14" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO14" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP14" s="24" t="inlineStr">
-        <is>
-          <t>The Spiders</t>
-        </is>
-      </c>
-      <c r="AQ14" s="24" t="inlineStr">
-        <is>
-          <t>The Spiders</t>
-        </is>
-      </c>
-      <c r="AR14" s="24" t="inlineStr">
-        <is>
-          <t>The Spiders</t>
-        </is>
-      </c>
-      <c r="AS14" s="24" t="inlineStr">
-        <is>
-          <t>HIMMERS</t>
-        </is>
-      </c>
-      <c r="AT14" s="24" t="inlineStr">
-        <is>
-          <t>HIMMERS</t>
-        </is>
-      </c>
-      <c r="AU14" s="24" t="inlineStr">
-        <is>
-          <t>HIMMERS</t>
-        </is>
-      </c>
-      <c r="AV14" s="24" t="n"/>
-      <c r="AW14" s="24" t="n"/>
-      <c r="AX14" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY14" s="24" t="n"/>
-      <c r="AZ14" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA14" s="24" t="inlineStr">
-        <is>
-          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
-        </is>
-      </c>
-      <c r="BB14" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC14" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD14" s="24" t="inlineStr">
-        <is>
-          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
-        </is>
-      </c>
-      <c r="BE14" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF14" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG14" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH14" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:21.952693Z</t>
-        </is>
-      </c>
-      <c r="BI14" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ14" s="25" t="n"/>
-      <c r="BK14" s="26" t="n">
-        <v>144</v>
-      </c>
-      <c r="BL14" s="27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BM14" s="28" t="n">
-        <v>0.409836</v>
-      </c>
-      <c r="BN14" s="28" t="n"/>
-      <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
-      <c r="BR14" s="28" t="n"/>
-      <c r="BS14" s="28" t="n"/>
-      <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="25" t="n"/>
-      <c r="BV14" s="29" t="n"/>
-      <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="30" t="n"/>
-      <c r="BY14" s="27" t="n"/>
-      <c r="BZ14" s="24" t="n"/>
-      <c r="CA14" s="31" t="n"/>
-      <c r="CB14" s="24" t="n"/>
-      <c r="CC14" s="24" t="n"/>
-      <c r="CD14" s="24" t="n"/>
-      <c r="CE14" s="24" t="n"/>
-      <c r="CF14" s="24" t="n"/>
-      <c r="CG14" s="24" t="n"/>
-      <c r="CH14" s="24" t="n"/>
-      <c r="CI14" s="24" t="n"/>
-      <c r="CJ14" s="24" t="n"/>
-      <c r="CK14" s="24" t="n"/>
-      <c r="CL14" s="24" t="n"/>
-      <c r="CM14" s="24" t="n"/>
-      <c r="CN14" s="24" t="n"/>
-      <c r="CO14" s="24" t="n"/>
-      <c r="CP14" s="24" t="n"/>
-      <c r="CQ14" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>4c90fbe615f74a89</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:24.902767Z</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>67989</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
-        <is>
-          <t>SwimTrek Blue</t>
-        </is>
-      </c>
-      <c r="G15" s="24" t="inlineStr">
-        <is>
-          <t>FlyQuest RED</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L15" s="26" t="n">
-        <v>-194</v>
-      </c>
-      <c r="M15" s="27" t="n">
-        <v>1.515464</v>
-      </c>
-      <c r="N15" s="28" t="n">
-        <v>0.659864</v>
-      </c>
-      <c r="O15" s="28" t="n">
-        <v>0.569339</v>
-      </c>
-      <c r="P15" s="28" t="n"/>
-      <c r="Q15" s="28" t="n">
-        <v>-0.09052499999999999</v>
-      </c>
-      <c r="R15" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T15" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U15" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
-      <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
-      <c r="AE15" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-flyr-swim-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF15" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG15" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH15" s="24" t="n"/>
-      <c r="AI15" s="31" t="n"/>
-      <c r="AJ15" s="31" t="n"/>
-      <c r="AK15" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL15" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM15" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN15" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO15" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP15" s="24" t="inlineStr">
-        <is>
-          <t>SwimTrek Blue</t>
-        </is>
-      </c>
-      <c r="AQ15" s="24" t="inlineStr">
-        <is>
-          <t>SwimTrek Blue</t>
-        </is>
-      </c>
-      <c r="AR15" s="24" t="inlineStr">
-        <is>
-          <t>SwimTrek Blue</t>
-        </is>
-      </c>
-      <c r="AS15" s="24" t="inlineStr">
-        <is>
-          <t>FlyQuest RED</t>
-        </is>
-      </c>
-      <c r="AT15" s="24" t="inlineStr">
-        <is>
-          <t>FlyQuest RED</t>
-        </is>
-      </c>
-      <c r="AU15" s="24" t="inlineStr">
-        <is>
-          <t>FlyQuest RED</t>
-        </is>
-      </c>
-      <c r="AV15" s="24" t="n"/>
-      <c r="AW15" s="24" t="n"/>
-      <c r="AX15" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY15" s="24" t="n"/>
-      <c r="AZ15" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA15" s="24" t="inlineStr">
-        <is>
-          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
-        </is>
-      </c>
-      <c r="BB15" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC15" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD15" s="24" t="inlineStr">
-        <is>
-          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
-        </is>
-      </c>
-      <c r="BE15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG15" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:22.943314Z</t>
-        </is>
-      </c>
-      <c r="BI15" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ15" s="25" t="n"/>
-      <c r="BK15" s="26" t="n">
-        <v>-194</v>
-      </c>
-      <c r="BL15" s="27" t="n">
-        <v>1.515464</v>
-      </c>
-      <c r="BM15" s="28" t="n">
-        <v>0.659864</v>
-      </c>
-      <c r="BN15" s="28" t="n"/>
-      <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
-      <c r="BS15" s="28" t="n"/>
-      <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
-      <c r="BV15" s="29" t="n"/>
-      <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n"/>
-      <c r="BY15" s="27" t="n"/>
-      <c r="BZ15" s="24" t="n"/>
-      <c r="CA15" s="31" t="n"/>
-      <c r="CB15" s="24" t="n"/>
-      <c r="CC15" s="24" t="n"/>
-      <c r="CD15" s="24" t="n"/>
-      <c r="CE15" s="24" t="n"/>
-      <c r="CF15" s="24" t="n"/>
-      <c r="CG15" s="24" t="n"/>
-      <c r="CH15" s="24" t="n"/>
-      <c r="CI15" s="24" t="n"/>
-      <c r="CJ15" s="24" t="n"/>
-      <c r="CK15" s="24" t="n"/>
-      <c r="CL15" s="24" t="n"/>
-      <c r="CM15" s="24" t="n"/>
-      <c r="CN15" s="24" t="n"/>
-      <c r="CO15" s="24" t="n"/>
-      <c r="CP15" s="24" t="n"/>
-      <c r="CQ15" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>e9769b6cd68141c1</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:24.902767Z</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T23:30:00Z</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>68095</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>MVSK Secret</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>ROSO GC</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L16" s="26" t="n">
-        <v>170</v>
-      </c>
-      <c r="M16" s="27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N16" s="28" t="n">
-        <v>0.37037</v>
-      </c>
-      <c r="O16" s="28" t="n">
-        <v>0.519652</v>
-      </c>
-      <c r="P16" s="28" t="n"/>
-      <c r="Q16" s="28" t="n">
-        <v>0.149282</v>
-      </c>
-      <c r="R16" s="26" t="n">
-        <v>95</v>
-      </c>
-      <c r="S16" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U16" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
-      <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
-      <c r="AE16" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-valorant-roso-mvs-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF16" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG16" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH16" s="24" t="n"/>
-      <c r="AI16" s="31" t="n"/>
-      <c r="AJ16" s="31" t="n"/>
-      <c r="AK16" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL16" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM16" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN16" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO16" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP16" s="24" t="inlineStr">
-        <is>
-          <t>MVSK Secret</t>
-        </is>
-      </c>
-      <c r="AQ16" s="24" t="inlineStr">
-        <is>
-          <t>MVSK Secret</t>
-        </is>
-      </c>
-      <c r="AR16" s="24" t="inlineStr">
-        <is>
-          <t>MVSK Secret</t>
-        </is>
-      </c>
-      <c r="AS16" s="24" t="inlineStr">
-        <is>
-          <t>ROSO GC</t>
-        </is>
-      </c>
-      <c r="AT16" s="24" t="inlineStr">
-        <is>
-          <t>ROSO GC</t>
-        </is>
-      </c>
-      <c r="AU16" s="24" t="inlineStr">
-        <is>
-          <t>ROSO GC</t>
-        </is>
-      </c>
-      <c r="AV16" s="24" t="n"/>
-      <c r="AW16" s="24" t="n"/>
-      <c r="AX16" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY16" s="24" t="n"/>
-      <c r="AZ16" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA16" s="24" t="inlineStr">
-        <is>
-          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
-        </is>
-      </c>
-      <c r="BB16" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC16" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD16" s="24" t="inlineStr">
-        <is>
-          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
-        </is>
-      </c>
-      <c r="BE16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG16" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:23.897138Z</t>
-        </is>
-      </c>
-      <c r="BI16" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ16" s="25" t="n"/>
-      <c r="BK16" s="26" t="n">
-        <v>170</v>
-      </c>
-      <c r="BL16" s="27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BM16" s="28" t="n">
-        <v>0.37037</v>
-      </c>
-      <c r="BN16" s="28" t="n"/>
-      <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
-      <c r="BS16" s="28" t="n"/>
-      <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
-      <c r="BV16" s="29" t="n"/>
-      <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n"/>
-      <c r="BY16" s="27" t="n"/>
-      <c r="BZ16" s="24" t="n"/>
-      <c r="CA16" s="31" t="n"/>
-      <c r="CB16" s="24" t="n"/>
-      <c r="CC16" s="24" t="n"/>
-      <c r="CD16" s="24" t="n"/>
-      <c r="CE16" s="24" t="n"/>
-      <c r="CF16" s="24" t="n"/>
-      <c r="CG16" s="24" t="n"/>
-      <c r="CH16" s="24" t="n"/>
-      <c r="CI16" s="24" t="n"/>
-      <c r="CJ16" s="24" t="n"/>
-      <c r="CK16" s="24" t="n"/>
-      <c r="CL16" s="24" t="n"/>
-      <c r="CM16" s="24" t="n"/>
-      <c r="CN16" s="24" t="n"/>
-      <c r="CO16" s="24" t="n"/>
-      <c r="CP16" s="24" t="n"/>
-      <c r="CQ16" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ10" headerRowCount="1">
-  <autoFilter ref="A1:CQ10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ16" headerRowCount="1">
+  <autoFilter ref="A1:CQ16"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$10)</f>
+        <f>COUNTA('Picks'!$A$2:$A$16)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$16,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$10,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$16,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")/(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")/(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$10)/SUM('Picks'!$BX$2:$BX$10),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$16)/SUM('Picks'!$BX$2:$BX$16),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$10)</f>
+        <f>SUM('Picks'!$BY$2:$BY$16)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$10,"&lt;&gt;",'Picks'!$AB$2:$AB$10),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$16,"&lt;&gt;",'Picks'!$AB$2:$AB$16),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$10,'Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$16,'Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ10"/>
+  <dimension ref="A1:CQ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4152,6 +4152,1608 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>e480367c30274bb5</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:13.369760Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>67311</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>KRÜ Esports</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.518775</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.098607</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n"/>
+      <c r="AD11" s="24" t="n"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-c9-kr-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>KRÜ Esports</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>KRÜ Esports</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>KRÜ Esports</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:07.245341Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>77117156ac0c49b3</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:13.369760Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>67386</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.626621</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>-0.013667</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="26" t="n"/>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n"/>
+      <c r="AD12" s="24" t="n"/>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-g2-sen-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:07.777596Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>fa8da4d0d9b64ab8</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:13.369760Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.765342</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.07494000000000001</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>57</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:08.752039Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>b3446a6d779848c4</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:13.369760Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>67987</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>HIMMERS</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.520495</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>0.110659</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="n"/>
+      <c r="W14" s="26" t="n"/>
+      <c r="X14" s="26" t="n"/>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n"/>
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-valorant-him-spi-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>HIMMERS</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>HIMMERS</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>HIMMERS</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:10.234884Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>c5c8a291063d4acc</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:13.369760Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>67989</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.569339</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>-0.09052499999999999</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-flyr-swim-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:11.230445Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>ba8a256592314d90</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:13.369760Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>68095</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>ROSO GC</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.519652</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.149282</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>95</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-valorant-roso-mvs-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>ROSO GC</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>ROSO GC</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>ROSO GC</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:12.340375Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ16" headerRowCount="1">
-  <autoFilter ref="A1:CQ16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ21" headerRowCount="1">
+  <autoFilter ref="A1:CQ21"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$16)</f>
+        <f>COUNTA('Picks'!$A$2:$A$21)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$16,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$21,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$16,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$21,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")/(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")/(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$16)/SUM('Picks'!$BX$2:$BX$16),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$21)/SUM('Picks'!$BX$2:$BX$21),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$16)</f>
+        <f>SUM('Picks'!$BY$2:$BY$21)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$16,"&lt;&gt;",'Picks'!$AB$2:$AB$16),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$21,"&lt;&gt;",'Picks'!$AB$2:$AB$21),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$16,'Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$21,'Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ16"/>
+  <dimension ref="A1:CQ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3966,18 +3966,38 @@
       </c>
       <c r="U10" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y10" s="25" t="n"/>
-      <c r="Z10" s="26" t="n"/>
-      <c r="AA10" s="28" t="n"/>
-      <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
+      <c r="Z10" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA10" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB10" s="28" t="n">
+        <v>0.000529</v>
+      </c>
+      <c r="AC10" s="30" t="n">
+        <v>0.7874</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:13:22.740323Z</t>
+        </is>
+      </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-valorant-fnc-th-2026-08-02).</t>
@@ -4120,8 +4140,12 @@
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
       <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
-      <c r="BR10" s="28" t="n"/>
+      <c r="BQ10" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR10" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
       <c r="BU10" s="25" t="n"/>
@@ -4155,12 +4179,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>e480367c30274bb5</t>
+          <t>97e1abd6e51442d7</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:13.369760Z</t>
+          <t>2026-08-02T19:32:17.298754Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4205,23 +4229,23 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.409836</v>
       </c>
       <c r="O11" s="28" t="n">
         <v>0.518775</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.098607</v>
+        <v>0.108939</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="S11" s="29" t="n">
         <v>1</v>
@@ -4233,21 +4257,41 @@
       </c>
       <c r="U11" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y11" s="25" t="n"/>
-      <c r="Z11" s="26" t="n"/>
-      <c r="AA11" s="28" t="n"/>
-      <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
+      <c r="Z11" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="AA11" s="28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AB11" s="28" t="n">
+        <v>0.000164</v>
+      </c>
+      <c r="AC11" s="30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:13:23.977752Z</t>
+        </is>
+      </c>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-c9-kr-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-valorant-c9-kr-2026-08-02).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4331,7 +4375,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+          <t>c4c53479d60e7fd116280c4ec0788bb856af372afb2da0dd70796fd41ac0b643</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4346,7 +4390,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+          <t>c4c53479d60e7fd116280c4ec0788bb856af372afb2da0dd70796fd41ac0b643</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4366,7 +4410,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:07.245341Z</t>
+          <t>2026-08-02T19:32:11.428763Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4376,19 +4420,23 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.409836</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
       <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
-      <c r="BR11" s="28" t="n"/>
+      <c r="BQ11" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BR11" s="28" t="n">
+        <v>0.41</v>
+      </c>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
       <c r="BU11" s="25" t="n"/>
@@ -4422,12 +4470,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>77117156ac0c49b3</t>
+          <t>f523171e5677438d</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:13.369760Z</t>
+          <t>2026-08-02T23:17:28.942888Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4472,23 +4520,23 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-178</v>
+        <v>-170</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.588235</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.62963</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.626621</v>
+        <v>0.626789</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>-0.013667</v>
+        <v>-0.002841</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="S12" s="29" t="n">
         <v>1.5</v>
@@ -4500,21 +4548,41 @@
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y12" s="25" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="28" t="n"/>
-      <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
+      <c r="Z12" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="AA12" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB12" s="28" t="n">
+        <v>0.06037</v>
+      </c>
+      <c r="AC12" s="30" t="n">
+        <v>0.8824</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:34:46.902850Z</t>
+        </is>
+      </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-g2-sen-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-valorant-g2-sen-2026-08-03).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4598,7 +4666,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+          <t>b8ad95e67a1d231f7c1456f640a0121faebeb1a345256cde26610e3b0d16a846</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4613,7 +4681,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+          <t>b8ad95e67a1d231f7c1456f640a0121faebeb1a345256cde26610e3b0d16a846</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4633,7 +4701,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:07.777596Z</t>
+          <t>2026-08-02T23:17:23.058724Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4643,19 +4711,23 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-178</v>
+        <v>-170</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.588235</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.62963</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
       <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
-      <c r="BR12" s="28" t="n"/>
+      <c r="BQ12" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BR12" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
       <c r="BU12" s="25" t="n"/>
@@ -4689,12 +4761,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>fa8da4d0d9b64ab8</t>
+          <t>e166706ca9c144b5</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:13.369760Z</t>
+          <t>2026-08-03T13:30:41.417037Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4739,23 +4811,23 @@
         </is>
       </c>
       <c r="L13" s="26" t="n">
-        <v>-223</v>
+        <v>-163</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.613497</v>
       </c>
       <c r="N13" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.619772</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.765342</v>
+        <v>0.765423</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.07494000000000001</v>
+        <v>0.145651</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="S13" s="29" t="n">
         <v>2</v>
@@ -4767,21 +4839,41 @@
       </c>
       <c r="U13" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y13" s="25" t="n"/>
-      <c r="Z13" s="26" t="n"/>
-      <c r="AA13" s="28" t="n"/>
-      <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
+      <c r="Z13" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="AA13" s="28" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AB13" s="28" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="AC13" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:06:03.000740Z</t>
+        </is>
+      </c>
       <c r="AE13" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
         </is>
       </c>
       <c r="AF13" s="31" t="inlineStr">
@@ -4791,7 +4883,7 @@
       </c>
       <c r="AG13" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH13" s="24" t="n"/>
@@ -4865,7 +4957,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+          <t>afe2fffd3c666e0d8f9040dcc6dedae587629fd14dee7043c87557d9d9d9e6e5</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4880,7 +4972,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+          <t>afe2fffd3c666e0d8f9040dcc6dedae587629fd14dee7043c87557d9d9d9e6e5</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4900,7 +4992,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:08.752039Z</t>
+          <t>2026-08-03T13:30:33.637118Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4910,19 +5002,23 @@
       </c>
       <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
-        <v>-223</v>
+        <v>-163</v>
       </c>
       <c r="BL13" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.613497</v>
       </c>
       <c r="BM13" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.619772</v>
       </c>
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
       <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
-      <c r="BR13" s="28" t="n"/>
+      <c r="BQ13" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BR13" s="28" t="n">
+        <v>0.62</v>
+      </c>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
       <c r="BU13" s="25" t="n"/>
@@ -4956,22 +5052,22 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>b3446a6d779848c4</t>
+          <t>b89e1f0fd9dc49c5</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:13.369760Z</t>
+          <t>2026-08-03T17:08:47.849402Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T21:00:00Z</t>
+          <t>2026-08-03T18:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>67987</t>
+          <t>67658</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -4981,12 +5077,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>Barça eSports GC</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>HIMMERS</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -5006,49 +5102,69 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>144</v>
+        <v>-223</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>2.44</v>
+        <v>1.44843</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.690402</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.520495</v>
+        <v>0.6925519999999999</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.110659</v>
+        <v>0.00215</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="S14" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U14" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
       <c r="Y14" s="25" t="n"/>
-      <c r="Z14" s="26" t="n"/>
-      <c r="AA14" s="28" t="n"/>
-      <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n"/>
-      <c r="AD14" s="24" t="n"/>
+      <c r="Z14" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="AA14" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB14" s="28" t="n">
+        <v>-0.000402</v>
+      </c>
+      <c r="AC14" s="30" t="n">
+        <v>0.8969</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:52:13.667573Z</t>
+        </is>
+      </c>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-valorant-him-spi-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-tmo-beg-2026-08-03).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5089,32 +5205,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>Barça eSports GC</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>Barça eSports GC</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>Barça eSports GC</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>HIMMERS</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>HIMMERS</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>HIMMERS</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5132,7 +5248,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+          <t>6f1a88c65511fda132cb3c464f9d3012c11a7503cf913396060b5b8c9adc5f1b</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5147,7 +5263,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+          <t>6f1a88c65511fda132cb3c464f9d3012c11a7503cf913396060b5b8c9adc5f1b</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5167,7 +5283,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:10.234884Z</t>
+          <t>2026-08-03T17:08:42.423289Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5177,19 +5293,23 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>144</v>
+        <v>-223</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>2.44</v>
+        <v>1.44843</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.690402</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
       <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
-      <c r="BR14" s="28" t="n"/>
+      <c r="BQ14" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BR14" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
       <c r="BU14" s="25" t="n"/>
@@ -5223,12 +5343,12 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>c5c8a291063d4acc</t>
+          <t>fb160713f7af45d2</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:13.369760Z</t>
+          <t>2026-08-03T19:54:50.877637Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -5238,7 +5358,7 @@
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>67989</t>
+          <t>67987</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -5248,12 +5368,12 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -5263,7 +5383,7 @@
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J15" s="25" t="n"/>
@@ -5273,49 +5393,69 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>-194</v>
+        <v>108</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>1.515464</v>
+        <v>2.08</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.480769</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.569339</v>
+        <v>0.521748</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>-0.09052499999999999</v>
+        <v>0.040979</v>
       </c>
       <c r="R15" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S15" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T15" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U15" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
+      <c r="X15" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
+      <c r="Z15" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="AA15" s="28" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AB15" s="28" t="n">
+        <v>-0.000769</v>
+      </c>
+      <c r="AC15" s="30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T01:58:53.450701Z</t>
+        </is>
+      </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-flyr-swim-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-valorant-him-spi-2026-08-03).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5356,32 +5496,32 @@
       </c>
       <c r="AP15" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="AQ15" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="AR15" s="24" t="inlineStr">
         <is>
-          <t>SwimTrek Blue</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="AS15" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="AT15" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="AU15" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest RED</t>
+          <t>HIMMERS</t>
         </is>
       </c>
       <c r="AV15" s="24" t="n"/>
@@ -5399,7 +5539,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+          <t>b86d10213574fcb4e774a613f40c4fb8692dc4e3a085fafa8fe32b85c8b1f80d</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5414,7 +5554,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+          <t>b86d10213574fcb4e774a613f40c4fb8692dc4e3a085fafa8fe32b85c8b1f80d</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5434,7 +5574,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:11.230445Z</t>
+          <t>2026-08-03T19:54:45.430222Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5444,19 +5584,23 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>-194</v>
+        <v>108</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>1.515464</v>
+        <v>2.08</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.480769</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
       <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
+      <c r="BQ15" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR15" s="28" t="n">
+        <v>0.48</v>
+      </c>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
       <c r="BU15" s="25" t="n"/>
@@ -5483,19 +5627,19 @@
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>ba8a256592314d90</t>
+          <t>159e11ed91d64bf9</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:13.369760Z</t>
+          <t>2026-08-03T22:57:52.421939Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -5505,7 +5649,7 @@
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>68095</t>
+          <t>68094</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -5515,12 +5659,12 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>MVSK Secret</t>
+          <t>SaD GC</t>
         </is>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>ROSO GC</t>
+          <t>Los Chudeles</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -5540,23 +5684,23 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>2.7</v>
+        <v>2.04</v>
       </c>
       <c r="N16" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.490196</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.519652</v>
+        <v>0.504194</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>0.149282</v>
+        <v>0.013998</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="S16" s="29" t="n">
         <v>1</v>
@@ -5568,21 +5712,41 @@
       </c>
       <c r="U16" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
+      <c r="Z16" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="AA16" s="28" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB16" s="28" t="n">
+        <v>-0.000196</v>
+      </c>
+      <c r="AC16" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T03:58:20.298471Z</t>
+        </is>
+      </c>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-valorant-roso-mvs-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-valorant-lcd-sga-2026-08-03).</t>
         </is>
       </c>
       <c r="AF16" s="31" t="inlineStr">
@@ -5592,7 +5756,7 @@
       </c>
       <c r="AG16" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH16" s="24" t="n"/>
@@ -5623,32 +5787,32 @@
       </c>
       <c r="AP16" s="24" t="inlineStr">
         <is>
-          <t>MVSK Secret</t>
+          <t>SaD GC</t>
         </is>
       </c>
       <c r="AQ16" s="24" t="inlineStr">
         <is>
-          <t>MVSK Secret</t>
+          <t>SaD GC</t>
         </is>
       </c>
       <c r="AR16" s="24" t="inlineStr">
         <is>
-          <t>MVSK Secret</t>
+          <t>SaD GC</t>
         </is>
       </c>
       <c r="AS16" s="24" t="inlineStr">
         <is>
-          <t>ROSO GC</t>
+          <t>Los Chudeles</t>
         </is>
       </c>
       <c r="AT16" s="24" t="inlineStr">
         <is>
-          <t>ROSO GC</t>
+          <t>Los Chudeles</t>
         </is>
       </c>
       <c r="AU16" s="24" t="inlineStr">
         <is>
-          <t>ROSO GC</t>
+          <t>Los Chudeles</t>
         </is>
       </c>
       <c r="AV16" s="24" t="n"/>
@@ -5666,7 +5830,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+          <t>fd8b674cd95f5267545eeaa19ed09838dffe6e7f1115e6ac52a5152ecb6ed1bc</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5681,7 +5845,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+          <t>fd8b674cd95f5267545eeaa19ed09838dffe6e7f1115e6ac52a5152ecb6ed1bc</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5701,7 +5865,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:12.340375Z</t>
+          <t>2026-08-03T22:57:48.462085Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5711,19 +5875,23 @@
       </c>
       <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="BL16" s="27" t="n">
-        <v>2.7</v>
+        <v>2.04</v>
       </c>
       <c r="BM16" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.490196</v>
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
       <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
+      <c r="BQ16" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BR16" s="28" t="n">
+        <v>0.49</v>
+      </c>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
       <c r="BU16" s="25" t="n"/>
@@ -5754,6 +5922,1413 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>676ecadd2637400b</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:57:52.421939Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>68095</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>ROSO GC</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.521277</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>0.141049</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>91</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="AA17" s="28" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB17" s="28" t="n">
+        <v>-0.000228</v>
+      </c>
+      <c r="AC17" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T01:58:55.904940Z</t>
+        </is>
+      </c>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-valorant-roso-mvs-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>ROSO GC</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>ROSO GC</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>ROSO GC</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>fd8b674cd95f5267545eeaa19ed09838dffe6e7f1115e6ac52a5152ecb6ed1bc</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>fd8b674cd95f5267545eeaa19ed09838dffe6e7f1115e6ac52a5152ecb6ed1bc</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:57:49.075256Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BR17" s="28" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>746b3eb463074b2d</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:57:52.421939Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>68096</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>:3</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 GC</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.527317</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>-0.163085</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="AA18" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB18" s="28" t="n">
+        <v>-0.000402</v>
+      </c>
+      <c r="AC18" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T01:58:57.182367Z</t>
+        </is>
+      </c>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-c9gc-meow-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>:3</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>:3</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>:3</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 GC</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 GC</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 GC</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>fd8b674cd95f5267545eeaa19ed09838dffe6e7f1115e6ac52a5152ecb6ed1bc</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>fd8b674cd95f5267545eeaa19ed09838dffe6e7f1115e6ac52a5152ecb6ed1bc</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:57:49.589365Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BR18" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>1879dec1a9044fcf</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:57:52.421939Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>68097</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Revitalize GC</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.5614749999999999</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>-0.038525</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="AA19" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB19" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="30" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T01:58:58.496591Z</t>
+        </is>
+      </c>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-valorant-efa-rev-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>Revitalize GC</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>Revitalize GC</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>Revitalize GC</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>fd8b674cd95f5267545eeaa19ed09838dffe6e7f1115e6ac52a5152ecb6ed1bc</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>fd8b674cd95f5267545eeaa19ed09838dffe6e7f1115e6ac52a5152ecb6ed1bc</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:57:50.125387Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BR19" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>9218b90a73a4484d</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.244456Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>68481</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.528125</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>0.178475</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="n"/>
+      <c r="W20" s="26" t="n"/>
+      <c r="X20" s="26" t="n"/>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n"/>
+      <c r="AD20" s="24" t="n"/>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-valorant-kcg-fso-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>1fb02f7e107cb3c5f6846e4e923c4e1fcb9fc33096bb43ae15b18b13c7c43abe</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>1fb02f7e107cb3c5f6846e4e923c4e1fcb9fc33096bb43ae15b18b13c7c43abe</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:40.181000Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>c0b1f86fc0104300</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.244456Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.623225</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>-0.067177</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-skn-tmo-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>1fb02f7e107cb3c5f6846e4e923c4e1fcb9fc33096bb43ae15b18b13c7c43abe</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>1fb02f7e107cb3c5f6846e4e923c4e1fcb9fc33096bb43ae15b18b13c7c43abe</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.242400Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ21" headerRowCount="1">
-  <autoFilter ref="A1:CQ21"/>
-  <tableColumns count="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR23" headerRowCount="1">
+  <autoFilter ref="A1:CR23"/>
+  <tableColumns count="96">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -392,12 +392,13 @@
     <tableColumn id="87" name="unavailable_features"/>
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="rest_disparity"/>
-    <tableColumn id="91" name="back_to_back_gap"/>
-    <tableColumn id="92" name="games_last_7_gap"/>
-    <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="market_residual_probability"/>
-    <tableColumn id="95" name="trade_candidate"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -754,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$21)</f>
+        <f>COUNTA('Picks'!$A$2:$A$23)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$21,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$23,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$21,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$23,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")/(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")/(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$21)/SUM('Picks'!$BX$2:$BX$21),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$23)/SUM('Picks'!$BX$2:$BX$23),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$21)</f>
+        <f>SUM('Picks'!$BY$2:$BY$23)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$21,"&lt;&gt;",'Picks'!$AB$2:$AB$21),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$23,"&lt;&gt;",'Picks'!$AB$2:$AB$23),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$21,'Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$23,'Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ21"/>
+  <dimension ref="A1:CR23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1560,30 +1562,35 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1875,6 +1882,7 @@
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2162,6 +2170,7 @@
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2449,6 +2458,7 @@
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
+      <c r="CR4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2736,6 +2746,7 @@
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
+      <c r="CR5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3023,6 +3034,7 @@
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
+      <c r="CR6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3310,6 +3322,7 @@
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
+      <c r="CR7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3597,6 +3610,7 @@
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3884,6 +3898,7 @@
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4170,7 +4185,8 @@
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
-      <c r="CQ10" s="24" t="inlineStr">
+      <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4461,7 +4477,8 @@
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
-      <c r="CQ11" s="24" t="inlineStr">
+      <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4752,7 +4769,8 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
-      <c r="CQ12" s="24" t="inlineStr">
+      <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5043,7 +5061,8 @@
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
-      <c r="CQ13" s="24" t="inlineStr">
+      <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5334,7 +5353,8 @@
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
-      <c r="CQ14" s="24" t="inlineStr">
+      <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5625,7 +5645,8 @@
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
-      <c r="CQ15" s="24" t="inlineStr">
+      <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5916,7 +5937,8 @@
       <c r="CN16" s="24" t="n"/>
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
-      <c r="CQ16" s="24" t="inlineStr">
+      <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6207,7 +6229,8 @@
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
-      <c r="CQ17" s="24" t="inlineStr">
+      <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6498,7 +6521,8 @@
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
-      <c r="CQ18" s="24" t="inlineStr">
+      <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6789,7 +6813,8 @@
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
-      <c r="CQ19" s="24" t="inlineStr">
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6798,12 +6823,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>9218b90a73a4484d</t>
+          <t>95eec17196724f0b</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:41.244456Z</t>
+          <t>2026-08-04T08:56:26.878542Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -6848,20 +6873,20 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.359712</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.528125</v>
+        <v>0.528265</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>0.178475</v>
+        <v>0.168553</v>
       </c>
       <c r="R20" s="26" t="n">
         <v>100</v>
@@ -6890,7 +6915,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-valorant-kcg-fso-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-valorant-kcg-fso-2026-08-04).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6974,7 +6999,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>1fb02f7e107cb3c5f6846e4e923c4e1fcb9fc33096bb43ae15b18b13c7c43abe</t>
+          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6989,7 +7014,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>1fb02f7e107cb3c5f6846e4e923c4e1fcb9fc33096bb43ae15b18b13c7c43abe</t>
+          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -7009,7 +7034,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:40.181000Z</t>
+          <t>2026-08-04T08:56:22.352788Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -7019,13 +7044,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.359712</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -7056,7 +7081,8 @@
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
-      <c r="CQ20" s="24" t="inlineStr">
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7065,12 +7091,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>c0b1f86fc0104300</t>
+          <t>bdc55bce2d1f43f1</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:41.244456Z</t>
+          <t>2026-08-04T08:56:26.878542Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -7115,20 +7141,20 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>-223</v>
+        <v>-213</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.469484</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.680511</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.623225</v>
+        <v>0.6230599999999999</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>-0.067177</v>
+        <v>-0.057451</v>
       </c>
       <c r="R21" s="26" t="n">
         <v>0</v>
@@ -7157,7 +7183,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-skn-tmo-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-valorant-skn-tmo-2026-08-04).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7241,7 +7267,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>1fb02f7e107cb3c5f6846e4e923c4e1fcb9fc33096bb43ae15b18b13c7c43abe</t>
+          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7256,7 +7282,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>1fb02f7e107cb3c5f6846e4e923c4e1fcb9fc33096bb43ae15b18b13c7c43abe</t>
+          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7276,7 +7302,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:41.242400Z</t>
+          <t>2026-08-04T08:56:23.433159Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7286,13 +7312,13 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>-223</v>
+        <v>-213</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.469484</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.680511</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
@@ -7323,7 +7349,544 @@
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
-      <c r="CQ21" s="24" t="inlineStr">
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>a9947a3cf9a946fc</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:26.878542Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.568122</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>0.098638</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:24.642540Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>b3edfd9006d940d2</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:26.878542Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>69954</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>ALTERNATE aTTaX Ruby</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.685526</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>-0.014174</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-valorant-fso-aar-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>ALTERNATE aTTaX Ruby</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>ALTERNATE aTTaX Ruby</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>ALTERNATE aTTaX Ruby</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:26.316942Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR23" headerRowCount="1">
-  <autoFilter ref="A1:CR23"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS22" headerRowCount="1">
+  <autoFilter ref="A1:CS22"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -755,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$23)</f>
+        <f>COUNTA('Picks'!$A$2:$A$22)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$23,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$22,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")+COUNTIFS('Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -795,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$23,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$22,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")/(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")/(COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")+COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$23)/SUM('Picks'!$BX$2:$BX$23),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$22)/SUM('Picks'!$BX$2:$BX$22),0)</f>
         <v/>
       </c>
     </row>
@@ -835,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$23)</f>
+        <f>SUM('Picks'!$BY$2:$BY$22)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$23,"&lt;&gt;",'Picks'!$AB$2:$AB$23),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$22,"&lt;&gt;",'Picks'!$AB$2:$AB$22),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$22,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$23,'Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$22,'Picks'!$AM$2:$AM$22,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -902,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -918,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -933,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -949,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -964,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -980,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR23"/>
+  <dimension ref="A1:CS22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1883,6 +1890,7 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2171,6 +2179,7 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2459,6 +2468,7 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2747,6 +2757,7 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3035,6 +3046,7 @@
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
       <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3323,6 +3335,7 @@
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
       <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3611,6 +3624,7 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
       <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3899,6 +3913,7 @@
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
       <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4186,7 +4201,8 @@
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
-      <c r="CR10" s="24" t="inlineStr">
+      <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4478,7 +4494,8 @@
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
-      <c r="CR11" s="24" t="inlineStr">
+      <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4770,7 +4787,8 @@
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
-      <c r="CR12" s="24" t="inlineStr">
+      <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5062,7 +5080,8 @@
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
-      <c r="CR13" s="24" t="inlineStr">
+      <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5354,7 +5373,8 @@
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
-      <c r="CR14" s="24" t="inlineStr">
+      <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5646,7 +5666,8 @@
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
-      <c r="CR15" s="24" t="inlineStr">
+      <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5938,7 +5959,8 @@
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
-      <c r="CR16" s="24" t="inlineStr">
+      <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6230,7 +6252,8 @@
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
-      <c r="CR17" s="24" t="inlineStr">
+      <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6522,7 +6545,8 @@
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
       <c r="CQ18" s="24" t="n"/>
-      <c r="CR18" s="24" t="inlineStr">
+      <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6814,7 +6838,8 @@
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
       <c r="CQ19" s="24" t="n"/>
-      <c r="CR19" s="24" t="inlineStr">
+      <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6823,12 +6848,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>95eec17196724f0b</t>
+          <t>2672734d84af40ec</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:26.878542Z</t>
+          <t>2026-08-04T14:26:45.561526Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -6873,20 +6898,20 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.34965</v>
       </c>
       <c r="O20" s="28" t="n">
         <v>0.528265</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>0.168553</v>
+        <v>0.178615</v>
       </c>
       <c r="R20" s="26" t="n">
         <v>100</v>
@@ -6915,7 +6940,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-valorant-kcg-fso-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-valorant-kcg-fso-2026-08-04).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6999,7 +7024,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -7014,7 +7039,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -7034,7 +7059,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:22.352788Z</t>
+          <t>2026-08-04T14:26:40.372782Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -7044,13 +7069,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.34965</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -7082,7 +7107,8 @@
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
       <c r="CQ20" s="24" t="n"/>
-      <c r="CR20" s="24" t="inlineStr">
+      <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7091,12 +7117,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>bdc55bce2d1f43f1</t>
+          <t>13453213e0e6475e</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:26.878542Z</t>
+          <t>2026-08-04T14:26:45.561526Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -7141,23 +7167,23 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>-213</v>
+        <v>-186</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.537634</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.65035</v>
       </c>
       <c r="O21" s="28" t="n">
         <v>0.6230599999999999</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>-0.057451</v>
+        <v>-0.02729</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S21" s="29" t="n">
         <v>1.5</v>
@@ -7183,7 +7209,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-valorant-skn-tmo-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-valorant-skn-tmo-2026-08-04).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7267,7 +7293,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7282,7 +7308,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7302,7 +7328,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:23.433159Z</t>
+          <t>2026-08-04T14:26:41.796927Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7312,13 +7338,13 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>-213</v>
+        <v>-186</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.537634</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.65035</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
@@ -7350,7 +7376,8 @@
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
       <c r="CQ21" s="24" t="n"/>
-      <c r="CR21" s="24" t="inlineStr">
+      <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7359,12 +7386,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>a9947a3cf9a946fc</t>
+          <t>f244622dcbd649d5</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:26.878542Z</t>
+          <t>2026-08-04T14:26:45.561526Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7409,23 +7436,23 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.460829</v>
       </c>
       <c r="O22" s="28" t="n">
         <v>0.568122</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>0.098638</v>
+        <v>0.107293</v>
       </c>
       <c r="R22" s="26" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="S22" s="29" t="n">
         <v>1</v>
@@ -7451,7 +7478,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7535,7 +7562,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7550,7 +7577,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7570,7 +7597,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:24.642540Z</t>
+          <t>2026-08-04T14:26:42.943962Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7580,13 +7607,13 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.460829</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
@@ -7618,277 +7645,10 @@
       <c r="CO22" s="24" t="n"/>
       <c r="CP22" s="24" t="n"/>
       <c r="CQ22" s="24" t="n"/>
-      <c r="CR22" s="24" t="inlineStr">
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="inlineStr">
         <is>
           <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>b3edfd9006d940d2</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T08:56:26.878542Z</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>69954</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F23" s="24" t="inlineStr">
-        <is>
-          <t>ALTERNATE aTTaX Ruby</t>
-        </is>
-      </c>
-      <c r="G23" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="H23" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I23" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L23" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="M23" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="N23" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="O23" s="28" t="n">
-        <v>0.685526</v>
-      </c>
-      <c r="P23" s="28" t="n"/>
-      <c r="Q23" s="28" t="n">
-        <v>-0.014174</v>
-      </c>
-      <c r="R23" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="S23" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U23" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V23" s="24" t="n"/>
-      <c r="W23" s="26" t="n"/>
-      <c r="X23" s="26" t="n"/>
-      <c r="Y23" s="25" t="n"/>
-      <c r="Z23" s="26" t="n"/>
-      <c r="AA23" s="28" t="n"/>
-      <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n"/>
-      <c r="AD23" s="24" t="n"/>
-      <c r="AE23" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-valorant-fso-aar-2026-08-05).</t>
-        </is>
-      </c>
-      <c r="AF23" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG23" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH23" s="24" t="n"/>
-      <c r="AI23" s="31" t="n"/>
-      <c r="AJ23" s="31" t="n"/>
-      <c r="AK23" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL23" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM23" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN23" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO23" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP23" s="24" t="inlineStr">
-        <is>
-          <t>ALTERNATE aTTaX Ruby</t>
-        </is>
-      </c>
-      <c r="AQ23" s="24" t="inlineStr">
-        <is>
-          <t>ALTERNATE aTTaX Ruby</t>
-        </is>
-      </c>
-      <c r="AR23" s="24" t="inlineStr">
-        <is>
-          <t>ALTERNATE aTTaX Ruby</t>
-        </is>
-      </c>
-      <c r="AS23" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="AT23" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="AU23" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="AV23" s="24" t="n"/>
-      <c r="AW23" s="24" t="n"/>
-      <c r="AX23" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY23" s="24" t="n"/>
-      <c r="AZ23" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA23" s="24" t="inlineStr">
-        <is>
-          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
-        </is>
-      </c>
-      <c r="BB23" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC23" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD23" s="24" t="inlineStr">
-        <is>
-          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
-        </is>
-      </c>
-      <c r="BE23" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF23" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG23" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T08:56:26.316942Z</t>
-        </is>
-      </c>
-      <c r="BI23" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ23" s="25" t="n"/>
-      <c r="BK23" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="BL23" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="BM23" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="BN23" s="28" t="n"/>
-      <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
-      <c r="BR23" s="28" t="n"/>
-      <c r="BS23" s="28" t="n"/>
-      <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="25" t="n"/>
-      <c r="BV23" s="29" t="n"/>
-      <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="30" t="n"/>
-      <c r="BY23" s="27" t="n"/>
-      <c r="BZ23" s="24" t="n"/>
-      <c r="CA23" s="31" t="n"/>
-      <c r="CB23" s="24" t="n"/>
-      <c r="CC23" s="24" t="n"/>
-      <c r="CD23" s="24" t="n"/>
-      <c r="CE23" s="24" t="n"/>
-      <c r="CF23" s="24" t="n"/>
-      <c r="CG23" s="24" t="n"/>
-      <c r="CH23" s="24" t="n"/>
-      <c r="CI23" s="24" t="n"/>
-      <c r="CJ23" s="24" t="n"/>
-      <c r="CK23" s="24" t="n"/>
-      <c r="CL23" s="24" t="n"/>
-      <c r="CM23" s="24" t="n"/>
-      <c r="CN23" s="24" t="n"/>
-      <c r="CO23" s="24" t="n"/>
-      <c r="CP23" s="24" t="n"/>
-      <c r="CQ23" s="24" t="n"/>
-      <c r="CR23" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
         </is>
       </c>
     </row>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS22" headerRowCount="1">
-  <autoFilter ref="A1:CS22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS29" headerRowCount="1">
+  <autoFilter ref="A1:CS29"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$22)</f>
+        <f>COUNTA('Picks'!$A$2:$A$29)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$22,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$29,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$22,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")+COUNTIFS('Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$22,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$29,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")/(COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")+COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")/(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$22)/SUM('Picks'!$BX$2:$BX$22),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$29)/SUM('Picks'!$BX$2:$BX$29),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$22)</f>
+        <f>SUM('Picks'!$BY$2:$BY$29)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$22,"&lt;&gt;",'Picks'!$AB$2:$AB$22),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$29,"&lt;&gt;",'Picks'!$AB$2:$AB$29),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$22,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$22,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$22,'Picks'!$AM$2:$AM$22,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$29,'Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS22"/>
+  <dimension ref="A1:CS29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6926,18 +6926,38 @@
       </c>
       <c r="U20" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V20" s="24" t="n"/>
-      <c r="W20" s="26" t="n"/>
-      <c r="X20" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y20" s="25" t="n"/>
-      <c r="Z20" s="26" t="n"/>
-      <c r="AA20" s="28" t="n"/>
-      <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n"/>
-      <c r="AD20" s="24" t="n"/>
+      <c r="Z20" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="AA20" s="28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB20" s="28" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="AC20" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:46.006926Z</t>
+        </is>
+      </c>
       <c r="AE20" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-valorant-kcg-fso-2026-08-04).</t>
@@ -6950,7 +6970,7 @@
       </c>
       <c r="AG20" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH20" s="24" t="n"/>
@@ -7080,8 +7100,12 @@
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
       <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
-      <c r="BR20" s="28" t="n"/>
+      <c r="BQ20" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BR20" s="28" t="n">
+        <v>0.35</v>
+      </c>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
       <c r="BU20" s="25" t="n"/>
@@ -7117,12 +7141,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>13453213e0e6475e</t>
+          <t>4d7c5dd938d94f4c</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:45.561526Z</t>
+          <t>2026-08-04T16:54:18.134287Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -7167,49 +7191,69 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>-186</v>
+        <v>-163</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.613497</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.619772</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.6230599999999999</v>
+        <v>0.64657</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>-0.02729</v>
+        <v>0.026798</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="S21" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U21" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y21" s="25" t="n"/>
-      <c r="Z21" s="26" t="n"/>
-      <c r="AA21" s="28" t="n"/>
-      <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n"/>
-      <c r="AD21" s="24" t="n"/>
+      <c r="Z21" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA21" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB21" s="28" t="n">
+        <v>0.010228</v>
+      </c>
+      <c r="AC21" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:59:59.083380Z</t>
+        </is>
+      </c>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-valorant-skn-tmo-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-valorant-skn-tmo-2026-08-04).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7219,7 +7263,7 @@
       </c>
       <c r="AG21" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH21" s="24" t="n"/>
@@ -7227,7 +7271,7 @@
       <c r="AJ21" s="31" t="n"/>
       <c r="AK21" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL21" s="26" t="n">
@@ -7235,17 +7279,17 @@
       </c>
       <c r="AM21" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN21" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO21" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP21" s="24" t="inlineStr">
@@ -7293,7 +7337,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
+          <t>2a3a3c0d919df15db76d78df508a996bd8f684ec881c5b644b1e53da56868427</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7303,12 +7347,12 @@
       </c>
       <c r="BC21" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
+          <t>2a3a3c0d919df15db76d78df508a996bd8f684ec881c5b644b1e53da56868427</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7323,12 +7367,12 @@
       </c>
       <c r="BG21" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:41.796927Z</t>
+          <t>2026-08-04T16:54:14.515679Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7338,19 +7382,23 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>-186</v>
+        <v>-163</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.613497</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.619772</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
       <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
-      <c r="BR21" s="28" t="n"/>
+      <c r="BQ21" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR21" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
       <c r="BU21" s="25" t="n"/>
@@ -7379,19 +7427,19 @@
       <c r="CR21" s="24" t="n"/>
       <c r="CS21" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>f244622dcbd649d5</t>
+          <t>d2e458490c0d44e1</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:45.561526Z</t>
+          <t>2026-08-05T04:38:20.842798Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7436,30 +7484,30 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.45045</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.568122</v>
+        <v>0.575198</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>0.107293</v>
+        <v>0.124748</v>
       </c>
       <c r="R22" s="26" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="S22" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T22" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U22" s="24" t="inlineStr">
@@ -7478,7 +7526,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7562,7 +7610,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7572,12 +7620,12 @@
       </c>
       <c r="BC22" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7592,12 +7640,12 @@
       </c>
       <c r="BG22" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:42.943962Z</t>
+          <t>2026-08-05T04:38:10.028876Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7607,13 +7655,13 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.45045</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
@@ -7652,6 +7700,1889 @@
         </is>
       </c>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>fe194e58bbd84f4b</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.842798Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>FunPlus Phoenix</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.669245</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>0.05987</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-valorant-fpx-jdg-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>FunPlus Phoenix</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>FunPlus Phoenix</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>FunPlus Phoenix</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:14.218178Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>c0a6131c566e45d5</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.842798Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>70595</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Dragon Ranger Gaming</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Wolves Esports</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.618982</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>-0.021306</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-wol-drg-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>Dragon Ranger Gaming</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>Dragon Ranger Gaming</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>Dragon Ranger Gaming</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>Wolves Esports</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Wolves Esports</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Wolves Esports</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:15.077660Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>aa03c5d26d454a7b</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.842798Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.702781</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>0.312156</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n"/>
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-valorant-gx-sge-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:15.903165Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>8c15d0db8cd44263</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.842798Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>70725</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX GC</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.536052</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>-0.054112</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="26" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n"/>
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-valorant-gxgc-kcg-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX GC</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX GC</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX GC</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:16.712984Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>60c859f9166445fb</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.842798Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>70727</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.550011</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>-0.109853</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="n"/>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n"/>
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-fso-hbs-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:17.574738Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="n"/>
+      <c r="CS27" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>89b3e8305f934509</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.842798Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.564051</v>
+      </c>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="28" t="n">
+        <v>0.193681</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="n"/>
+      <c r="W28" s="26" t="n"/>
+      <c r="X28" s="26" t="n"/>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n"/>
+      <c r="AA28" s="28" t="n"/>
+      <c r="AB28" s="28" t="n"/>
+      <c r="AC28" s="30" t="n"/>
+      <c r="AD28" s="24" t="n"/>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-valorant-navi-jl-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG28" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AQ28" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AR28" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AS28" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AT28" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AU28" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BB28" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BE28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG28" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:18.444919Z</t>
+        </is>
+      </c>
+      <c r="BI28" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="BL28" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BM28" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="BN28" s="28" t="n"/>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
+      <c r="BR28" s="28" t="n"/>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="n"/>
+      <c r="CD28" s="24" t="n"/>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="n"/>
+      <c r="CJ28" s="24" t="n"/>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
+      <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="n"/>
+      <c r="CS28" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>68a5f387b04541af</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.842798Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.626622</v>
+      </c>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n">
+        <v>0.176172</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="n"/>
+      <c r="W29" s="26" t="n"/>
+      <c r="X29" s="26" t="n"/>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n"/>
+      <c r="AD29" s="24" t="n"/>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-valorant-eg-fur-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.044205Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN29" s="28" t="n"/>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n"/>
+      <c r="BY29" s="27" t="n"/>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="n"/>
+      <c r="CD29" s="24" t="n"/>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="n"/>
+      <c r="CJ29" s="24" t="n"/>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS29" headerRowCount="1">
-  <autoFilter ref="A1:CS29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS30" headerRowCount="1">
+  <autoFilter ref="A1:CS30"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$29)</f>
+        <f>COUNTA('Picks'!$A$2:$A$30)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$29,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$30,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$30,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")+COUNTIFS('Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$29,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$30,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")/(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"win")/(COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"win")+COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$29)/SUM('Picks'!$BX$2:$BX$29),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$30)/SUM('Picks'!$BX$2:$BX$30),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$29)</f>
+        <f>SUM('Picks'!$BY$2:$BY$30)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$29,"&lt;&gt;",'Picks'!$AB$2:$AB$29),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$30,"&lt;&gt;",'Picks'!$AB$2:$AB$30),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$30,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$30,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$29,'Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$30,'Picks'!$AM$2:$AM$30,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$30,'Picks'!$H$2:$H$30,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$30,'Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$30,'Picks'!$H$2:$H$30,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$30,'Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$30,'Picks'!$H$2:$H$30,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$30,'Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS29"/>
+  <dimension ref="A1:CS30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7512,18 +7512,38 @@
       </c>
       <c r="U22" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V22" s="24" t="n"/>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y22" s="25" t="n"/>
-      <c r="Z22" s="26" t="n"/>
-      <c r="AA22" s="28" t="n"/>
-      <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n"/>
-      <c r="AD22" s="24" t="n"/>
+      <c r="Z22" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA22" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB22" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC22" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:51:50.006749Z</t>
+        </is>
+      </c>
       <c r="AE22" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
@@ -7536,7 +7556,7 @@
       </c>
       <c r="AG22" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH22" s="24" t="n"/>
@@ -7666,8 +7686,12 @@
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
       <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
-      <c r="BR22" s="28" t="n"/>
+      <c r="BQ22" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR22" s="28" t="n">
+        <v>0.45</v>
+      </c>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
       <c r="BU22" s="25" t="n"/>
@@ -7703,22 +7727,22 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>fe194e58bbd84f4b</t>
+          <t>d9dbfdd14e3140e8</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.842798Z</t>
+          <t>2026-08-05T13:56:15.301935Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T08:00:00Z</t>
+          <t>2026-08-05T18:00:00Z</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>70564</t>
+          <t>69955</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -7728,12 +7752,12 @@
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>JD Gaming</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
         <is>
-          <t>FunPlus Phoenix</t>
+          <t>Gentle Mates GC</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -7753,26 +7777,26 @@
         </is>
       </c>
       <c r="L23" s="26" t="n">
-        <v>-156</v>
+        <v>-223</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.44843</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.690402</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.669245</v>
+        <v>0.689698</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>0.05987</v>
+        <v>-0.000704</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="S23" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T23" s="24" t="inlineStr">
         <is>
@@ -7795,7 +7819,7 @@
       <c r="AD23" s="24" t="n"/>
       <c r="AE23" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-valorant-fpx-jdg-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-m8gc-tmo-2026-08-05).</t>
         </is>
       </c>
       <c r="AF23" s="31" t="inlineStr">
@@ -7813,7 +7837,7 @@
       <c r="AJ23" s="31" t="n"/>
       <c r="AK23" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL23" s="26" t="n">
@@ -7821,47 +7845,47 @@
       </c>
       <c r="AM23" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN23" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO23" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP23" s="24" t="inlineStr">
         <is>
-          <t>JD Gaming</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AQ23" s="24" t="inlineStr">
         <is>
-          <t>JD Gaming</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AR23" s="24" t="inlineStr">
         <is>
-          <t>JD Gaming</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AS23" s="24" t="inlineStr">
         <is>
-          <t>FunPlus Phoenix</t>
+          <t>Gentle Mates GC</t>
         </is>
       </c>
       <c r="AT23" s="24" t="inlineStr">
         <is>
-          <t>FunPlus Phoenix</t>
+          <t>Gentle Mates GC</t>
         </is>
       </c>
       <c r="AU23" s="24" t="inlineStr">
         <is>
-          <t>FunPlus Phoenix</t>
+          <t>Gentle Mates GC</t>
         </is>
       </c>
       <c r="AV23" s="24" t="n"/>
@@ -7879,7 +7903,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7894,7 +7918,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7914,7 +7938,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:14.218178Z</t>
+          <t>2026-08-05T13:56:10.002030Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7924,13 +7948,13 @@
       </c>
       <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
-        <v>-156</v>
+        <v>-223</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.44843</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.690402</v>
       </c>
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
@@ -7965,29 +7989,29 @@
       <c r="CR23" s="24" t="n"/>
       <c r="CS23" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>c0a6131c566e45d5</t>
+          <t>9a73d4c20bdb4b65</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.842798Z</t>
+          <t>2026-08-05T13:56:15.301935Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T10:00:00Z</t>
+          <t>2026-08-06T08:00:00Z</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>70595</t>
+          <t>70564</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -7997,12 +8021,12 @@
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>Dragon Ranger Gaming</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
         <is>
-          <t>Wolves Esports</t>
+          <t>FunPlus Phoenix</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -8012,7 +8036,7 @@
       </c>
       <c r="I24" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J24" s="25" t="n"/>
@@ -8022,26 +8046,26 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>-178</v>
+        <v>-156</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.641026</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.609375</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.618982</v>
+        <v>0.667906</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>-0.021306</v>
+        <v>0.058531</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="S24" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T24" s="24" t="inlineStr">
         <is>
@@ -8064,7 +8088,7 @@
       <c r="AD24" s="24" t="n"/>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-wol-drg-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-valorant-fpx-jdg-2026-08-06).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -8082,7 +8106,7 @@
       <c r="AJ24" s="31" t="n"/>
       <c r="AK24" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL24" s="26" t="n">
@@ -8090,47 +8114,47 @@
       </c>
       <c r="AM24" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN24" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO24" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP24" s="24" t="inlineStr">
         <is>
-          <t>Dragon Ranger Gaming</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="AQ24" s="24" t="inlineStr">
         <is>
-          <t>Dragon Ranger Gaming</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="AR24" s="24" t="inlineStr">
         <is>
-          <t>Dragon Ranger Gaming</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="AS24" s="24" t="inlineStr">
         <is>
-          <t>Wolves Esports</t>
+          <t>FunPlus Phoenix</t>
         </is>
       </c>
       <c r="AT24" s="24" t="inlineStr">
         <is>
-          <t>Wolves Esports</t>
+          <t>FunPlus Phoenix</t>
         </is>
       </c>
       <c r="AU24" s="24" t="inlineStr">
         <is>
-          <t>Wolves Esports</t>
+          <t>FunPlus Phoenix</t>
         </is>
       </c>
       <c r="AV24" s="24" t="n"/>
@@ -8148,7 +8172,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -8163,7 +8187,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -8183,7 +8207,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:15.077660Z</t>
+          <t>2026-08-05T13:56:10.639279Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8193,13 +8217,13 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>-178</v>
+        <v>-156</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.641026</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.609375</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
@@ -8234,29 +8258,29 @@
       <c r="CR24" s="24" t="n"/>
       <c r="CS24" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>aa03c5d26d454a7b</t>
+          <t>176a57bc6f884790</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.842798Z</t>
+          <t>2026-08-05T13:56:15.301935Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T15:00:00Z</t>
+          <t>2026-08-06T10:00:00Z</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>70724</t>
+          <t>70595</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -8266,12 +8290,12 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Dragon Ranger Gaming</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>Wolves Esports</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -8291,26 +8315,26 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>156</v>
+        <v>-186</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>2.56</v>
+        <v>1.537634</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.65035</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.702781</v>
+        <v>0.618449</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>0.312156</v>
+        <v>-0.031901</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
@@ -8333,7 +8357,7 @@
       <c r="AD25" s="24" t="n"/>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-valorant-gx-sge-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-valorant-wol-drg-2026-08-06).</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -8351,7 +8375,7 @@
       <c r="AJ25" s="31" t="n"/>
       <c r="AK25" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL25" s="26" t="n">
@@ -8359,47 +8383,47 @@
       </c>
       <c r="AM25" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN25" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO25" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP25" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Dragon Ranger Gaming</t>
         </is>
       </c>
       <c r="AQ25" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Dragon Ranger Gaming</t>
         </is>
       </c>
       <c r="AR25" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Dragon Ranger Gaming</t>
         </is>
       </c>
       <c r="AS25" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>Wolves Esports</t>
         </is>
       </c>
       <c r="AT25" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>Wolves Esports</t>
         </is>
       </c>
       <c r="AU25" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>Wolves Esports</t>
         </is>
       </c>
       <c r="AV25" s="24" t="n"/>
@@ -8417,7 +8441,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8432,7 +8456,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8452,7 +8476,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:15.903165Z</t>
+          <t>2026-08-05T13:56:11.184348Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8462,13 +8486,13 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>156</v>
+        <v>-186</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>2.56</v>
+        <v>1.537634</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.65035</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
@@ -8503,19 +8527,19 @@
       <c r="CR25" s="24" t="n"/>
       <c r="CS25" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>8c15d0db8cd44263</t>
+          <t>0eb5dd3fc32a4757</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.842798Z</t>
+          <t>2026-08-05T13:56:15.301935Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8525,7 +8549,7 @@
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>70725</t>
+          <t>70724</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -8535,12 +8559,12 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp GC</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
         <is>
-          <t>GIANTX GC</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -8550,7 +8574,7 @@
       </c>
       <c r="I26" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J26" s="25" t="n"/>
@@ -8560,26 +8584,26 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>-144</v>
+        <v>156</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.56</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.390625</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.536052</v>
+        <v>0.701767</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>-0.054112</v>
+        <v>0.311142</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
@@ -8602,7 +8626,7 @@
       <c r="AD26" s="24" t="n"/>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-valorant-gxgc-kcg-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-valorant-gx-sge-2026-08-06).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8620,7 +8644,7 @@
       <c r="AJ26" s="31" t="n"/>
       <c r="AK26" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL26" s="26" t="n">
@@ -8628,47 +8652,47 @@
       </c>
       <c r="AM26" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN26" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO26" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP26" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp GC</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AQ26" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp GC</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AR26" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp GC</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AS26" s="24" t="inlineStr">
         <is>
-          <t>GIANTX GC</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="AT26" s="24" t="inlineStr">
         <is>
-          <t>GIANTX GC</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="AU26" s="24" t="inlineStr">
         <is>
-          <t>GIANTX GC</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="AV26" s="24" t="n"/>
@@ -8686,7 +8710,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8701,7 +8725,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8721,7 +8745,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:16.712984Z</t>
+          <t>2026-08-05T13:56:11.760518Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8731,13 +8755,13 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>-144</v>
+        <v>156</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.56</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.390625</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
@@ -8772,19 +8796,19 @@
       <c r="CR26" s="24" t="n"/>
       <c r="CS26" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>60c859f9166445fb</t>
+          <t>25e4b71449b345c8</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.842798Z</t>
+          <t>2026-08-05T13:56:15.301935Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -8794,7 +8818,7 @@
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>70727</t>
+          <t>70725</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -8804,12 +8828,12 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Karmine Corp GC</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>GIANTX GC</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -8829,20 +8853,20 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>-194</v>
+        <v>-138</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.724638</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.579832</v>
       </c>
       <c r="O27" s="28" t="n">
-        <v>0.550011</v>
+        <v>0.5358309999999999</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>-0.109853</v>
+        <v>-0.044001</v>
       </c>
       <c r="R27" s="26" t="n">
         <v>0</v>
@@ -8871,7 +8895,7 @@
       <c r="AD27" s="24" t="n"/>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-fso-hbs-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-valorant-gxgc-kcg-2026-08-06).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -8912,32 +8936,32 @@
       </c>
       <c r="AP27" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Karmine Corp GC</t>
         </is>
       </c>
       <c r="AQ27" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Karmine Corp GC</t>
         </is>
       </c>
       <c r="AR27" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Karmine Corp GC</t>
         </is>
       </c>
       <c r="AS27" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>GIANTX GC</t>
         </is>
       </c>
       <c r="AT27" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>GIANTX GC</t>
         </is>
       </c>
       <c r="AU27" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>GIANTX GC</t>
         </is>
       </c>
       <c r="AV27" s="24" t="n"/>
@@ -8955,7 +8979,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8970,7 +8994,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -8990,7 +9014,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:17.574738Z</t>
+          <t>2026-08-05T13:56:12.281637Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -9000,13 +9024,13 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>-194</v>
+        <v>-138</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.724638</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.579832</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
@@ -9048,22 +9072,22 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>89b3e8305f934509</t>
+          <t>c48e81c262904847</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.842798Z</t>
+          <t>2026-08-05T13:56:15.301935Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T18:00:00Z</t>
+          <t>2026-08-06T15:00:00Z</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>70912</t>
+          <t>70727</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
@@ -9073,12 +9097,12 @@
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Habos Babos</t>
         </is>
       </c>
       <c r="G28" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr">
@@ -9088,7 +9112,7 @@
       </c>
       <c r="I28" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J28" s="25" t="n"/>
@@ -9098,23 +9122,23 @@
         </is>
       </c>
       <c r="L28" s="26" t="n">
-        <v>170</v>
+        <v>-178</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>2.7</v>
+        <v>1.561798</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.640288</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>0.564051</v>
+        <v>0.54962</v>
       </c>
       <c r="P28" s="28" t="n"/>
       <c r="Q28" s="28" t="n">
-        <v>0.193681</v>
+        <v>-0.090668</v>
       </c>
       <c r="R28" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S28" s="29" t="n">
         <v>1</v>
@@ -9140,7 +9164,7 @@
       <c r="AD28" s="24" t="n"/>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-valorant-navi-jl-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-fso-hbs-2026-08-06).</t>
         </is>
       </c>
       <c r="AF28" s="31" t="inlineStr">
@@ -9158,7 +9182,7 @@
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL28" s="26" t="n">
@@ -9166,47 +9190,47 @@
       </c>
       <c r="AM28" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN28" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO28" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP28" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Habos Babos</t>
         </is>
       </c>
       <c r="AQ28" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Habos Babos</t>
         </is>
       </c>
       <c r="AR28" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Habos Babos</t>
         </is>
       </c>
       <c r="AS28" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="AT28" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="AU28" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="AV28" s="24" t="n"/>
@@ -9224,7 +9248,7 @@
       </c>
       <c r="BA28" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BB28" s="24" t="inlineStr">
@@ -9239,7 +9263,7 @@
       </c>
       <c r="BD28" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BE28" s="24" t="inlineStr">
@@ -9259,7 +9283,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:18.444919Z</t>
+          <t>2026-08-05T13:56:12.754904Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -9269,13 +9293,13 @@
       </c>
       <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
-        <v>170</v>
+        <v>-178</v>
       </c>
       <c r="BL28" s="27" t="n">
-        <v>2.7</v>
+        <v>1.561798</v>
       </c>
       <c r="BM28" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.640288</v>
       </c>
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
@@ -9310,29 +9334,29 @@
       <c r="CR28" s="24" t="n"/>
       <c r="CS28" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>68a5f387b04541af</t>
+          <t>f2617aae10be41fc</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.842798Z</t>
+          <t>2026-08-05T13:56:15.301935Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T21:00:00Z</t>
+          <t>2026-08-06T18:00:00Z</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>71315</t>
+          <t>70912</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -9342,12 +9366,12 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>FURIA Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr">
@@ -9357,7 +9381,7 @@
       </c>
       <c r="I29" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J29" s="25" t="n"/>
@@ -9367,26 +9391,26 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>2.22</v>
+        <v>2.7</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.37037</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.626622</v>
+        <v>0.563896</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>0.176172</v>
+        <v>0.193526</v>
       </c>
       <c r="R29" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S29" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T29" s="24" t="inlineStr">
         <is>
@@ -9409,7 +9433,7 @@
       <c r="AD29" s="24" t="n"/>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-valorant-eg-fur-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-valorant-navi-jl-2026-08-06).</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -9450,32 +9474,32 @@
       </c>
       <c r="AP29" s="24" t="inlineStr">
         <is>
-          <t>FURIA Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AQ29" s="24" t="inlineStr">
         <is>
-          <t>FURIA Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AR29" s="24" t="inlineStr">
         <is>
-          <t>FURIA Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AS29" s="24" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AT29" s="24" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AU29" s="24" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AV29" s="24" t="n"/>
@@ -9493,7 +9517,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -9508,7 +9532,7 @@
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -9528,7 +9552,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.044205Z</t>
+          <t>2026-08-05T13:56:13.229270Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9538,13 +9562,13 @@
       </c>
       <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>2.22</v>
+        <v>2.7</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.37037</v>
       </c>
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
@@ -9583,6 +9607,275 @@
         </is>
       </c>
     </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>1c6ec9b4a36c4023</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:15.301935Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.625458</v>
+      </c>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n">
+        <v>0.20529</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S30" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="n"/>
+      <c r="W30" s="26" t="n"/>
+      <c r="X30" s="26" t="n"/>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="28" t="n"/>
+      <c r="AC30" s="30" t="n"/>
+      <c r="AD30" s="24" t="n"/>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-eg-fur-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG30" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AQ30" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AR30" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AS30" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="AT30" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="AU30" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA30" s="24" t="inlineStr">
+        <is>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+        </is>
+      </c>
+      <c r="BB30" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC30" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:14.786413Z</t>
+        </is>
+      </c>
+      <c r="BI30" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL30" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM30" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN30" s="28" t="n"/>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
+      <c r="BR30" s="28" t="n"/>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n"/>
+      <c r="BY30" s="27" t="n"/>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="n"/>
+      <c r="CD30" s="24" t="n"/>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="n"/>
+      <c r="CJ30" s="24" t="n"/>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS30" headerRowCount="1">
-  <autoFilter ref="A1:CS30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS37" headerRowCount="1">
+  <autoFilter ref="A1:CS37"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$30)</f>
+        <f>COUNTA('Picks'!$A$2:$A$37)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$30,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$37,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$30,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")+COUNTIFS('Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")+COUNTIFS('Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$30,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$37,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"win")/(COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"win")+COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")/(COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")+COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$30)/SUM('Picks'!$BX$2:$BX$30),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$37)/SUM('Picks'!$BX$2:$BX$37),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$30)</f>
+        <f>SUM('Picks'!$BY$2:$BY$37)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$30,"&lt;&gt;",'Picks'!$AB$2:$AB$30),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$37,"&lt;&gt;",'Picks'!$AB$2:$AB$37),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$30,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$30,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$37,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$30,'Picks'!$AM$2:$AM$30,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$37,'Picks'!$AM$2:$AM$37,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$30,'Picks'!$H$2:$H$30,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$30,'Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$30,'Picks'!$H$2:$H$30,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$30,'Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$30,'Picks'!$H$2:$H$30,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$30,'Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS30"/>
+  <dimension ref="A1:CS37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7727,12 +7727,12 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>d9dbfdd14e3140e8</t>
+          <t>cdf578cf7d98458f</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:15.301935Z</t>
+          <t>2026-08-05T17:04:46.344950Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7777,26 +7777,26 @@
         </is>
       </c>
       <c r="L23" s="26" t="n">
-        <v>-223</v>
+        <v>-194</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.515464</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.659864</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.689698</v>
+        <v>0.6890849999999999</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>-0.000704</v>
+        <v>0.029221</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="S23" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T23" s="24" t="inlineStr">
         <is>
@@ -7805,21 +7805,41 @@
       </c>
       <c r="U23" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V23" s="24" t="n"/>
-      <c r="W23" s="26" t="n"/>
-      <c r="X23" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y23" s="25" t="n"/>
-      <c r="Z23" s="26" t="n"/>
-      <c r="AA23" s="28" t="n"/>
-      <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n"/>
-      <c r="AD23" s="24" t="n"/>
+      <c r="Z23" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="AA23" s="28" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AB23" s="28" t="n">
+        <v>-0.009864</v>
+      </c>
+      <c r="AC23" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:20.306504Z</t>
+        </is>
+      </c>
       <c r="AE23" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-m8gc-tmo-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-m8gc-tmo-2026-08-05).</t>
         </is>
       </c>
       <c r="AF23" s="31" t="inlineStr">
@@ -7829,7 +7849,7 @@
       </c>
       <c r="AG23" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH23" s="24" t="n"/>
@@ -7855,7 +7875,7 @@
       </c>
       <c r="AO23" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
         </is>
       </c>
       <c r="AP23" s="24" t="inlineStr">
@@ -7903,7 +7923,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>99605999cbefc3e4318aa2d50dc2b92c9ca2bafd08c79807b93ccfd4969eebcd</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7918,7 +7938,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>99605999cbefc3e4318aa2d50dc2b92c9ca2bafd08c79807b93ccfd4969eebcd</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7938,7 +7958,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:10.002030Z</t>
+          <t>2026-08-05T17:04:41.254236Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7948,19 +7968,23 @@
       </c>
       <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
-        <v>-223</v>
+        <v>-194</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.515464</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.659864</v>
       </c>
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
       <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
-      <c r="BR23" s="28" t="n"/>
+      <c r="BQ23" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BR23" s="28" t="n">
+        <v>0.65</v>
+      </c>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
       <c r="BU23" s="25" t="n"/>
@@ -7989,19 +8013,19 @@
       <c r="CR23" s="24" t="n"/>
       <c r="CS23" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>9a73d4c20bdb4b65</t>
+          <t>cb803518ea764ed5</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:15.301935Z</t>
+          <t>2026-08-06T00:24:39.463638Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -8046,26 +8070,26 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>-156</v>
+        <v>-170</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.588235</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.62963</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.667906</v>
+        <v>0.6551090000000001</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>0.058531</v>
+        <v>0.025479</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="S24" s="29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="T24" s="24" t="inlineStr">
         <is>
@@ -8074,21 +8098,35 @@
       </c>
       <c r="U24" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V24" s="24" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y24" s="25" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n"/>
-      <c r="AD24" s="24" t="n"/>
+      <c r="AC24" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:45.581929Z</t>
+        </is>
+      </c>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-valorant-fpx-jdg-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-valorant-fpx-jdg-2026-08-06).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -8098,7 +8136,7 @@
       </c>
       <c r="AG24" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH24" s="24" t="n"/>
@@ -8106,7 +8144,7 @@
       <c r="AJ24" s="31" t="n"/>
       <c r="AK24" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL24" s="26" t="n">
@@ -8114,17 +8152,17 @@
       </c>
       <c r="AM24" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN24" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO24" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
         </is>
       </c>
       <c r="AP24" s="24" t="inlineStr">
@@ -8172,7 +8210,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -8187,7 +8225,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -8207,7 +8245,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:10.639279Z</t>
+          <t>2026-08-06T00:24:35.545519Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8217,13 +8255,13 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>-156</v>
+        <v>-170</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.588235</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.62963</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
@@ -8265,12 +8303,12 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>176a57bc6f884790</t>
+          <t>59e51fb17d924b64</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:15.301935Z</t>
+          <t>2026-08-06T00:24:39.463638Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -8315,26 +8353,26 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>-186</v>
+        <v>-170</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.588235</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.62963</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.618449</v>
+        <v>0.619297</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>-0.031901</v>
+        <v>-0.010333</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
@@ -8343,21 +8381,35 @@
       </c>
       <c r="U25" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="n"/>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y25" s="25" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n"/>
-      <c r="AD25" s="24" t="n"/>
+      <c r="AC25" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:47.269533Z</t>
+        </is>
+      </c>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-valorant-wol-drg-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-valorant-wol-drg-2026-08-06).</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -8393,7 +8445,7 @@
       </c>
       <c r="AO25" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
         </is>
       </c>
       <c r="AP25" s="24" t="inlineStr">
@@ -8441,7 +8493,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8456,7 +8508,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8476,7 +8528,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:11.184348Z</t>
+          <t>2026-08-06T00:24:36.130397Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8486,13 +8538,13 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>-186</v>
+        <v>-170</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.588235</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.62963</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
@@ -8534,12 +8586,12 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>0eb5dd3fc32a4757</t>
+          <t>c79618f0ece446a0</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:15.301935Z</t>
+          <t>2026-08-06T00:24:39.463638Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8549,7 +8601,7 @@
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>70724</t>
+          <t>70725</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -8559,12 +8611,12 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Karmine Corp GC</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>GIANTX GC</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -8574,7 +8626,7 @@
       </c>
       <c r="I26" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J26" s="25" t="n"/>
@@ -8584,26 +8636,26 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>156</v>
+        <v>-108</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>2.56</v>
+        <v>1.925926</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.519231</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.701767</v>
+        <v>0.55231</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>0.311142</v>
+        <v>0.033079</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="S26" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
@@ -8612,21 +8664,35 @@
       </c>
       <c r="U26" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y26" s="25" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n"/>
-      <c r="AD26" s="24" t="n"/>
+      <c r="AC26" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:48.944178Z</t>
+        </is>
+      </c>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-valorant-gx-sge-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-valorant-gxgc-kcg-2026-08-06).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8636,7 +8702,7 @@
       </c>
       <c r="AG26" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH26" s="24" t="n"/>
@@ -8644,7 +8710,7 @@
       <c r="AJ26" s="31" t="n"/>
       <c r="AK26" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL26" s="26" t="n">
@@ -8652,47 +8718,47 @@
       </c>
       <c r="AM26" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN26" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO26" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
         </is>
       </c>
       <c r="AP26" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Karmine Corp GC</t>
         </is>
       </c>
       <c r="AQ26" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Karmine Corp GC</t>
         </is>
       </c>
       <c r="AR26" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Karmine Corp GC</t>
         </is>
       </c>
       <c r="AS26" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>GIANTX GC</t>
         </is>
       </c>
       <c r="AT26" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>GIANTX GC</t>
         </is>
       </c>
       <c r="AU26" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>GIANTX GC</t>
         </is>
       </c>
       <c r="AV26" s="24" t="n"/>
@@ -8710,7 +8776,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8725,7 +8791,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8745,7 +8811,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:11.760518Z</t>
+          <t>2026-08-06T00:24:36.602756Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8755,13 +8821,13 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>156</v>
+        <v>-108</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>2.56</v>
+        <v>1.925926</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.519231</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
@@ -8803,12 +8869,12 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>25e4b71449b345c8</t>
+          <t>19496ab933704b9f</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:15.301935Z</t>
+          <t>2026-08-06T00:24:39.463638Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -8818,7 +8884,7 @@
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>70725</t>
+          <t>70727</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -8828,12 +8894,12 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp GC</t>
+          <t>Habos Babos</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
         <is>
-          <t>GIANTX GC</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -8853,49 +8919,63 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>-138</v>
+        <v>-170</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.588235</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.62963</v>
       </c>
       <c r="O27" s="28" t="n">
-        <v>0.5358309999999999</v>
+        <v>0.537492</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>-0.044001</v>
+        <v>-0.092138</v>
       </c>
       <c r="R27" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T27" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U27" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
+      <c r="X27" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y27" s="25" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
+      <c r="AC27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:50.514524Z</t>
+        </is>
+      </c>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-valorant-gxgc-kcg-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-valorant-fso-hbs-2026-08-06).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -8905,7 +8985,7 @@
       </c>
       <c r="AG27" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH27" s="24" t="n"/>
@@ -8931,37 +9011,37 @@
       </c>
       <c r="AO27" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
         </is>
       </c>
       <c r="AP27" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp GC</t>
+          <t>Habos Babos</t>
         </is>
       </c>
       <c r="AQ27" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp GC</t>
+          <t>Habos Babos</t>
         </is>
       </c>
       <c r="AR27" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp GC</t>
+          <t>Habos Babos</t>
         </is>
       </c>
       <c r="AS27" s="24" t="inlineStr">
         <is>
-          <t>GIANTX GC</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="AT27" s="24" t="inlineStr">
         <is>
-          <t>GIANTX GC</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="AU27" s="24" t="inlineStr">
         <is>
-          <t>GIANTX GC</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="AV27" s="24" t="n"/>
@@ -8979,7 +9059,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8994,7 +9074,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -9014,7 +9094,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:12.281637Z</t>
+          <t>2026-08-06T00:24:37.090341Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -9024,13 +9104,13 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>-138</v>
+        <v>-170</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.588235</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.62963</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
@@ -9072,12 +9152,12 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>c48e81c262904847</t>
+          <t>95d8804e9f6742de</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:15.301935Z</t>
+          <t>2026-08-06T00:24:39.463638Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -9087,7 +9167,7 @@
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>70727</t>
+          <t>70724</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
@@ -9097,12 +9177,12 @@
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G28" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr">
@@ -9112,7 +9192,7 @@
       </c>
       <c r="I28" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J28" s="25" t="n"/>
@@ -9122,49 +9202,63 @@
         </is>
       </c>
       <c r="L28" s="26" t="n">
-        <v>-178</v>
+        <v>138</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.38</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.420168</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>0.54962</v>
+        <v>0.695761</v>
       </c>
       <c r="P28" s="28" t="n"/>
       <c r="Q28" s="28" t="n">
-        <v>-0.090668</v>
+        <v>0.275593</v>
       </c>
       <c r="R28" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S28" s="29" t="n">
+      <c r="X28" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T28" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U28" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V28" s="24" t="n"/>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
       <c r="Y28" s="25" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n"/>
-      <c r="AD28" s="24" t="n"/>
+      <c r="AC28" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:52.207320Z</t>
+        </is>
+      </c>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-fso-hbs-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-gx-sge-2026-08-06).</t>
         </is>
       </c>
       <c r="AF28" s="31" t="inlineStr">
@@ -9174,7 +9268,7 @@
       </c>
       <c r="AG28" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH28" s="24" t="n"/>
@@ -9182,7 +9276,7 @@
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL28" s="26" t="n">
@@ -9190,47 +9284,47 @@
       </c>
       <c r="AM28" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN28" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO28" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP28" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AQ28" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AR28" s="24" t="inlineStr">
         <is>
-          <t>Habos Babos</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AS28" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="AT28" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="AU28" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="AV28" s="24" t="n"/>
@@ -9248,7 +9342,7 @@
       </c>
       <c r="BA28" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BB28" s="24" t="inlineStr">
@@ -9263,7 +9357,7 @@
       </c>
       <c r="BD28" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BE28" s="24" t="inlineStr">
@@ -9283,7 +9377,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:12.754904Z</t>
+          <t>2026-08-06T00:24:37.569959Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -9293,13 +9387,13 @@
       </c>
       <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
-        <v>-178</v>
+        <v>138</v>
       </c>
       <c r="BL28" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.38</v>
       </c>
       <c r="BM28" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.420168</v>
       </c>
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
@@ -9334,19 +9428,19 @@
       <c r="CR28" s="24" t="n"/>
       <c r="CS28" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>f2617aae10be41fc</t>
+          <t>192f6189a99f40b2</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:15.301935Z</t>
+          <t>2026-08-06T00:24:39.463638Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -9391,20 +9485,20 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.359712</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.563896</v>
+        <v>0.563029</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>0.193526</v>
+        <v>0.203317</v>
       </c>
       <c r="R29" s="26" t="n">
         <v>100</v>
@@ -9419,21 +9513,35 @@
       </c>
       <c r="U29" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V29" s="24" t="n"/>
-      <c r="W29" s="26" t="n"/>
-      <c r="X29" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y29" s="25" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n"/>
-      <c r="AD29" s="24" t="n"/>
+      <c r="AC29" s="30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:01:46.955979Z</t>
+        </is>
+      </c>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-valorant-navi-jl-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-valorant-navi-jl-2026-08-06).</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -9517,7 +9625,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -9532,7 +9640,7 @@
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -9552,7 +9660,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:13.229270Z</t>
+          <t>2026-08-06T00:24:38.040365Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9562,13 +9670,13 @@
       </c>
       <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.359712</v>
       </c>
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
@@ -9610,12 +9718,12 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>1c6ec9b4a36c4023</t>
+          <t>29f26cb8522341d1</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:15.301935Z</t>
+          <t>2026-08-06T19:00:18.001858Z</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -9660,23 +9768,23 @@
         </is>
       </c>
       <c r="L30" s="26" t="n">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="N30" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.460829</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>0.625458</v>
+        <v>0.615411</v>
       </c>
       <c r="P30" s="28" t="n"/>
       <c r="Q30" s="28" t="n">
-        <v>0.20529</v>
+        <v>0.154582</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="S30" s="29" t="n">
         <v>1.5</v>
@@ -9688,21 +9796,41 @@
       </c>
       <c r="U30" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V30" s="24" t="n"/>
-      <c r="W30" s="26" t="n"/>
-      <c r="X30" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y30" s="25" t="n"/>
-      <c r="Z30" s="26" t="n"/>
-      <c r="AA30" s="28" t="n"/>
-      <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n"/>
-      <c r="AD30" s="24" t="n"/>
+      <c r="Z30" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="AA30" s="28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB30" s="28" t="n">
+        <v>-0.000829</v>
+      </c>
+      <c r="AC30" s="30" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:01:48.504320Z</t>
+        </is>
+      </c>
       <c r="AE30" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-eg-fur-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-eg-fur-2026-08-06).</t>
         </is>
       </c>
       <c r="AF30" s="31" t="inlineStr">
@@ -9786,7 +9914,7 @@
       </c>
       <c r="BA30" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
         </is>
       </c>
       <c r="BB30" s="24" t="inlineStr">
@@ -9801,7 +9929,7 @@
       </c>
       <c r="BD30" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
         </is>
       </c>
       <c r="BE30" s="24" t="inlineStr">
@@ -9821,7 +9949,7 @@
       </c>
       <c r="BH30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:14.786413Z</t>
+          <t>2026-08-06T19:00:13.149018Z</t>
         </is>
       </c>
       <c r="BI30" s="24" t="inlineStr">
@@ -9831,19 +9959,23 @@
       </c>
       <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="BL30" s="27" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="BM30" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.460829</v>
       </c>
       <c r="BN30" s="28" t="n"/>
       <c r="BO30" s="28" t="n"/>
       <c r="BP30" s="25" t="n"/>
-      <c r="BQ30" s="27" t="n"/>
-      <c r="BR30" s="28" t="n"/>
+      <c r="BQ30" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BR30" s="28" t="n">
+        <v>0.46</v>
+      </c>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
       <c r="BU30" s="25" t="n"/>
@@ -9876,6 +10008,1937 @@
         </is>
       </c>
     </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>d7b622e9018b43c2</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:11.884581Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>71675</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>DetonatioN FocusMe</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>Team Secret</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.653762</v>
+      </c>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="28" t="n">
+        <v>0.003412</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="AA31" s="28" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AB31" s="28" t="n">
+        <v>-0.00035</v>
+      </c>
+      <c r="AC31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:17.233910Z</t>
+        </is>
+      </c>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-valorant-ts-dfm-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG31" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="inlineStr">
+        <is>
+          <t>DetonatioN FocusMe</t>
+        </is>
+      </c>
+      <c r="AQ31" s="24" t="inlineStr">
+        <is>
+          <t>DetonatioN FocusMe</t>
+        </is>
+      </c>
+      <c r="AR31" s="24" t="inlineStr">
+        <is>
+          <t>DetonatioN FocusMe</t>
+        </is>
+      </c>
+      <c r="AS31" s="24" t="inlineStr">
+        <is>
+          <t>Team Secret</t>
+        </is>
+      </c>
+      <c r="AT31" s="24" t="inlineStr">
+        <is>
+          <t>Team Secret</t>
+        </is>
+      </c>
+      <c r="AU31" s="24" t="inlineStr">
+        <is>
+          <t>Team Secret</t>
+        </is>
+      </c>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA31" s="24" t="inlineStr">
+        <is>
+          <t>b73645bf1ecd543fdd6eef3fb18bf1f86790dae2d994242a68d3628f34298e3b</t>
+        </is>
+      </c>
+      <c r="BB31" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC31" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>b73645bf1ecd543fdd6eef3fb18bf1f86790dae2d994242a68d3628f34298e3b</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:59.654949Z</t>
+        </is>
+      </c>
+      <c r="BI31" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL31" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM31" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN31" s="28" t="n"/>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BR31" s="28" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n"/>
+      <c r="BY31" s="27" t="n"/>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="n"/>
+      <c r="CD31" s="24" t="n"/>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="n"/>
+      <c r="CJ31" s="24" t="n"/>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>f9a9f444e7804efc</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:28.912966Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>71752</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>FULL SENSE</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.781485</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>0.17211</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AA32" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB32" s="28" t="n">
+        <v>0.000625</v>
+      </c>
+      <c r="AC32" s="30" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="AD32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:01.811967Z</t>
+        </is>
+      </c>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-valorant-geng-fs-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>FULL SENSE</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>FULL SENSE</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>FULL SENSE</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:21.351080Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN32" s="28" t="n"/>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BR32" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="n"/>
+      <c r="CD32" s="24" t="n"/>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="n"/>
+      <c r="CJ32" s="24" t="n"/>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
+      <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="n"/>
+      <c r="CS32" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>9f013dd7475f4195</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:00.757019Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>72078</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.743264</v>
+      </c>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n">
+        <v>0.383552</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="n"/>
+      <c r="W33" s="26" t="n"/>
+      <c r="X33" s="26" t="n"/>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n"/>
+      <c r="AA33" s="28" t="n"/>
+      <c r="AB33" s="28" t="n"/>
+      <c r="AC33" s="30" t="n"/>
+      <c r="AD33" s="24" t="n"/>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-valorant-fnc-ep-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG33" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="AQ33" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="AR33" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="AS33" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AT33" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AU33" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA33" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BB33" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC33" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD33" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BE33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG33" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:54.113763Z</t>
+        </is>
+      </c>
+      <c r="BI33" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL33" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BM33" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="BN33" s="28" t="n"/>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
+      <c r="BR33" s="28" t="n"/>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+      <c r="CB33" s="24" t="n"/>
+      <c r="CC33" s="24" t="n"/>
+      <c r="CD33" s="24" t="n"/>
+      <c r="CE33" s="24" t="n"/>
+      <c r="CF33" s="24" t="n"/>
+      <c r="CG33" s="24" t="n"/>
+      <c r="CH33" s="24" t="n"/>
+      <c r="CI33" s="24" t="n"/>
+      <c r="CJ33" s="24" t="n"/>
+      <c r="CK33" s="24" t="n"/>
+      <c r="CL33" s="24" t="n"/>
+      <c r="CM33" s="24" t="n"/>
+      <c r="CN33" s="24" t="n"/>
+      <c r="CO33" s="24" t="n"/>
+      <c r="CP33" s="24" t="n"/>
+      <c r="CQ33" s="24" t="n"/>
+      <c r="CR33" s="24" t="n"/>
+      <c r="CS33" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>a929831281674ed7</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:00.757019Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>72723</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.577178</v>
+      </c>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n">
+        <v>-0.06311</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="n"/>
+      <c r="W34" s="26" t="n"/>
+      <c r="X34" s="26" t="n"/>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="30" t="n"/>
+      <c r="AD34" s="24" t="n"/>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-krx-t1-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG34" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AQ34" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AR34" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AS34" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="AT34" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="AU34" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA34" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BB34" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC34" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD34" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BE34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG34" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:56.286884Z</t>
+        </is>
+      </c>
+      <c r="BI34" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL34" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM34" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN34" s="28" t="n"/>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
+      <c r="BR34" s="28" t="n"/>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+      <c r="CB34" s="24" t="n"/>
+      <c r="CC34" s="24" t="n"/>
+      <c r="CD34" s="24" t="n"/>
+      <c r="CE34" s="24" t="n"/>
+      <c r="CF34" s="24" t="n"/>
+      <c r="CG34" s="24" t="n"/>
+      <c r="CH34" s="24" t="n"/>
+      <c r="CI34" s="24" t="n"/>
+      <c r="CJ34" s="24" t="n"/>
+      <c r="CK34" s="24" t="n"/>
+      <c r="CL34" s="24" t="n"/>
+      <c r="CM34" s="24" t="n"/>
+      <c r="CN34" s="24" t="n"/>
+      <c r="CO34" s="24" t="n"/>
+      <c r="CP34" s="24" t="n"/>
+      <c r="CQ34" s="24" t="n"/>
+      <c r="CR34" s="24" t="n"/>
+      <c r="CS34" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>eaa69166713b49cb</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:00.757019Z</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>73684</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>FunPlus Phoenix</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <v>0.542519</v>
+      </c>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n">
+        <v>-0.157181</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U35" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="n"/>
+      <c r="W35" s="26" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="28" t="n"/>
+      <c r="AB35" s="28" t="n"/>
+      <c r="AC35" s="30" t="n"/>
+      <c r="AD35" s="24" t="n"/>
+      <c r="AE35" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-valorant-kbg-fpx-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF35" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG35" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="n"/>
+      <c r="AK35" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM35" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP35" s="24" t="inlineStr">
+        <is>
+          <t>FunPlus Phoenix</t>
+        </is>
+      </c>
+      <c r="AQ35" s="24" t="inlineStr">
+        <is>
+          <t>FunPlus Phoenix</t>
+        </is>
+      </c>
+      <c r="AR35" s="24" t="inlineStr">
+        <is>
+          <t>FunPlus Phoenix</t>
+        </is>
+      </c>
+      <c r="AS35" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="AT35" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="AU35" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="AV35" s="24" t="n"/>
+      <c r="AW35" s="24" t="n"/>
+      <c r="AX35" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY35" s="24" t="n"/>
+      <c r="AZ35" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA35" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BB35" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC35" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD35" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BE35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG35" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:56.818736Z</t>
+        </is>
+      </c>
+      <c r="BI35" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ35" s="25" t="n"/>
+      <c r="BK35" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL35" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM35" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN35" s="28" t="n"/>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
+      <c r="BR35" s="28" t="n"/>
+      <c r="BS35" s="28" t="n"/>
+      <c r="BT35" s="28" t="n"/>
+      <c r="BU35" s="25" t="n"/>
+      <c r="BV35" s="29" t="n"/>
+      <c r="BW35" s="24" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
+      <c r="BZ35" s="24" t="n"/>
+      <c r="CA35" s="31" t="n"/>
+      <c r="CB35" s="24" t="n"/>
+      <c r="CC35" s="24" t="n"/>
+      <c r="CD35" s="24" t="n"/>
+      <c r="CE35" s="24" t="n"/>
+      <c r="CF35" s="24" t="n"/>
+      <c r="CG35" s="24" t="n"/>
+      <c r="CH35" s="24" t="n"/>
+      <c r="CI35" s="24" t="n"/>
+      <c r="CJ35" s="24" t="n"/>
+      <c r="CK35" s="24" t="n"/>
+      <c r="CL35" s="24" t="n"/>
+      <c r="CM35" s="24" t="n"/>
+      <c r="CN35" s="24" t="n"/>
+      <c r="CO35" s="24" t="n"/>
+      <c r="CP35" s="24" t="n"/>
+      <c r="CQ35" s="24" t="n"/>
+      <c r="CR35" s="24" t="n"/>
+      <c r="CS35" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>f835edf7b815480f</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:00.757019Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>74165</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.699272</v>
+      </c>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n">
+        <v>0.319044</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S36" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="n"/>
+      <c r="W36" s="26" t="n"/>
+      <c r="X36" s="26" t="n"/>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="28" t="n"/>
+      <c r="AC36" s="30" t="n"/>
+      <c r="AD36" s="24" t="n"/>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-valorant-ef-jl-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG36" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AQ36" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AR36" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AS36" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="AT36" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="AU36" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA36" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BB36" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC36" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD36" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BE36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG36" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:59.578708Z</t>
+        </is>
+      </c>
+      <c r="BI36" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL36" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM36" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN36" s="28" t="n"/>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
+      <c r="BR36" s="28" t="n"/>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+      <c r="CB36" s="24" t="n"/>
+      <c r="CC36" s="24" t="n"/>
+      <c r="CD36" s="24" t="n"/>
+      <c r="CE36" s="24" t="n"/>
+      <c r="CF36" s="24" t="n"/>
+      <c r="CG36" s="24" t="n"/>
+      <c r="CH36" s="24" t="n"/>
+      <c r="CI36" s="24" t="n"/>
+      <c r="CJ36" s="24" t="n"/>
+      <c r="CK36" s="24" t="n"/>
+      <c r="CL36" s="24" t="n"/>
+      <c r="CM36" s="24" t="n"/>
+      <c r="CN36" s="24" t="n"/>
+      <c r="CO36" s="24" t="n"/>
+      <c r="CP36" s="24" t="n"/>
+      <c r="CQ36" s="24" t="n"/>
+      <c r="CR36" s="24" t="n"/>
+      <c r="CS36" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>f92bfe3dd5f9459b</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:00.757019Z</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>73525</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>Leviatán Esports</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N37" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O37" s="28" t="n">
+        <v>0.700273</v>
+      </c>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n">
+        <v>0.100273</v>
+      </c>
+      <c r="R37" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="S37" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T37" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U37" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="n"/>
+      <c r="W37" s="26" t="n"/>
+      <c r="X37" s="26" t="n"/>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="26" t="n"/>
+      <c r="AA37" s="28" t="n"/>
+      <c r="AB37" s="28" t="n"/>
+      <c r="AC37" s="30" t="n"/>
+      <c r="AD37" s="24" t="n"/>
+      <c r="AE37" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-valorant-lev-mibr-2026-08-09).</t>
+        </is>
+      </c>
+      <c r="AF37" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG37" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH37" s="24" t="n"/>
+      <c r="AI37" s="31" t="n"/>
+      <c r="AJ37" s="31" t="n"/>
+      <c r="AK37" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL37" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN37" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO37" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP37" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="AQ37" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="AR37" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="AS37" s="24" t="inlineStr">
+        <is>
+          <t>Leviatán Esports</t>
+        </is>
+      </c>
+      <c r="AT37" s="24" t="inlineStr">
+        <is>
+          <t>Leviatán Esports</t>
+        </is>
+      </c>
+      <c r="AU37" s="24" t="inlineStr">
+        <is>
+          <t>Leviatán Esports</t>
+        </is>
+      </c>
+      <c r="AV37" s="24" t="n"/>
+      <c r="AW37" s="24" t="n"/>
+      <c r="AX37" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY37" s="24" t="n"/>
+      <c r="AZ37" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA37" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BB37" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC37" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD37" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BE37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG37" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:00.754763Z</t>
+        </is>
+      </c>
+      <c r="BI37" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ37" s="25" t="n"/>
+      <c r="BK37" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL37" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM37" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN37" s="28" t="n"/>
+      <c r="BO37" s="28" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
+      <c r="BR37" s="28" t="n"/>
+      <c r="BS37" s="28" t="n"/>
+      <c r="BT37" s="28" t="n"/>
+      <c r="BU37" s="25" t="n"/>
+      <c r="BV37" s="29" t="n"/>
+      <c r="BW37" s="24" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
+      <c r="BZ37" s="24" t="n"/>
+      <c r="CA37" s="31" t="n"/>
+      <c r="CB37" s="24" t="n"/>
+      <c r="CC37" s="24" t="n"/>
+      <c r="CD37" s="24" t="n"/>
+      <c r="CE37" s="24" t="n"/>
+      <c r="CF37" s="24" t="n"/>
+      <c r="CG37" s="24" t="n"/>
+      <c r="CH37" s="24" t="n"/>
+      <c r="CI37" s="24" t="n"/>
+      <c r="CJ37" s="24" t="n"/>
+      <c r="CK37" s="24" t="n"/>
+      <c r="CL37" s="24" t="n"/>
+      <c r="CM37" s="24" t="n"/>
+      <c r="CN37" s="24" t="n"/>
+      <c r="CO37" s="24" t="n"/>
+      <c r="CP37" s="24" t="n"/>
+      <c r="CQ37" s="24" t="n"/>
+      <c r="CR37" s="24" t="n"/>
+      <c r="CS37" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/valorant.xlsx
+++ b/data/research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS37" headerRowCount="1">
-  <autoFilter ref="A1:CS37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS38" headerRowCount="1">
+  <autoFilter ref="A1:CS38"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$37)</f>
+        <f>COUNTA('Picks'!$A$2:$A$38)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$37,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$38,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$37,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")+COUNTIFS('Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")+COUNTIFS('Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$37,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$38,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")/(COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")+COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")/(COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")+COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$37)/SUM('Picks'!$BX$2:$BX$37),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$38)/SUM('Picks'!$BX$2:$BX$38),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$37)</f>
+        <f>SUM('Picks'!$BY$2:$BY$38)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$37,"&lt;&gt;",'Picks'!$AB$2:$AB$37),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$38,"&lt;&gt;",'Picks'!$AB$2:$AB$38),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$37,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$37,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$38,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$37,'Picks'!$AM$2:$AM$37,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$38,'Picks'!$AM$2:$AM$38,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS37"/>
+  <dimension ref="A1:CS38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10866,12 +10866,12 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>a929831281674ed7</t>
+          <t>b4e483bdd2ff4f24</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:00.757019Z</t>
+          <t>2026-08-07T18:31:15.157040Z</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -10925,11 +10925,11 @@
         <v>0.640288</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>0.577178</v>
+        <v>0.577074</v>
       </c>
       <c r="P34" s="28" t="n"/>
       <c r="Q34" s="28" t="n">
-        <v>-0.06311</v>
+        <v>-0.06321400000000001</v>
       </c>
       <c r="R34" s="26" t="n">
         <v>0</v>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="BA34" s="24" t="inlineStr">
         <is>
-          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
         </is>
       </c>
       <c r="BB34" s="24" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="BD34" s="24" t="inlineStr">
         <is>
-          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
         </is>
       </c>
       <c r="BE34" s="24" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:56.286884Z</t>
+          <t>2026-08-07T18:31:09.718182Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -11135,12 +11135,12 @@
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>eaa69166713b49cb</t>
+          <t>2b36021dc6c64f3b</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:00.757019Z</t>
+          <t>2026-08-07T18:31:15.157040Z</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -11194,11 +11194,11 @@
         <v>0.6997</v>
       </c>
       <c r="O35" s="28" t="n">
-        <v>0.542519</v>
+        <v>0.542435</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>-0.157181</v>
+        <v>-0.157265</v>
       </c>
       <c r="R35" s="26" t="n">
         <v>0</v>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="BA35" s="24" t="inlineStr">
         <is>
-          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
         </is>
       </c>
       <c r="BB35" s="24" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="BD35" s="24" t="inlineStr">
         <is>
-          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
         </is>
       </c>
       <c r="BE35" s="24" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:56.818736Z</t>
+          <t>2026-08-07T18:31:10.347731Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -11404,22 +11404,22 @@
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>f835edf7b815480f</t>
+          <t>ec2aa304f09443af</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:00.757019Z</t>
+          <t>2026-08-07T18:31:15.157040Z</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-08T18:00:00Z</t>
+          <t>2026-08-08T17:00:00Z</t>
         </is>
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>74165</t>
+          <t>74125</t>
         </is>
       </c>
       <c r="E36" s="24" t="inlineStr">
@@ -11429,12 +11429,12 @@
       </c>
       <c r="F36" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Lost Puppies GC</t>
         </is>
       </c>
       <c r="G36" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire</t>
+          <t>ALTERNATE aTTaX Ruby</t>
         </is>
       </c>
       <c r="H36" s="24" t="inlineStr">
@@ -11454,26 +11454,26 @@
         </is>
       </c>
       <c r="L36" s="26" t="n">
-        <v>163</v>
+        <v>-113</v>
       </c>
       <c r="M36" s="27" t="n">
-        <v>2.63</v>
+        <v>1.884956</v>
       </c>
       <c r="N36" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.530516</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>0.699272</v>
+        <v>0.637346</v>
       </c>
       <c r="P36" s="28" t="n"/>
       <c r="Q36" s="28" t="n">
-        <v>0.319044</v>
+        <v>0.10683</v>
       </c>
       <c r="R36" s="26" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="S36" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T36" s="24" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-valorant-ef-jl-2026-08-08).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-valorant-aar-lpg-2026-08-08).</t>
         </is>
       </c>
       <c r="AF36" s="31" t="inlineStr">
@@ -11537,32 +11537,32 @@
       </c>
       <c r="AP36" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Lost Puppies GC</t>
         </is>
       </c>
       <c r="AQ36" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Lost Puppies GC</t>
         </is>
       </c>
       <c r="AR36" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Lost Puppies GC</t>
         </is>
       </c>
       <c r="AS36" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire</t>
+          <t>ALTERNATE aTTaX Ruby</t>
         </is>
       </c>
       <c r="AT36" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire</t>
+          <t>ALTERNATE aTTaX Ruby</t>
         </is>
       </c>
       <c r="AU36" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire</t>
+          <t>ALTERNATE aTTaX Ruby</t>
         </is>
       </c>
       <c r="AV36" s="24" t="n"/>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="BA36" s="24" t="inlineStr">
         <is>
-          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
         </is>
       </c>
       <c r="BB36" s="24" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="BD36" s="24" t="inlineStr">
         <is>
-          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
         </is>
       </c>
       <c r="BE36" s="24" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="BH36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:59.578708Z</t>
+          <t>2026-08-07T18:31:13.105417Z</t>
         </is>
       </c>
       <c r="BI36" s="24" t="inlineStr">
@@ -11625,13 +11625,13 @@
       </c>
       <c r="BJ36" s="25" t="n"/>
       <c r="BK36" s="26" t="n">
-        <v>163</v>
+        <v>-113</v>
       </c>
       <c r="BL36" s="27" t="n">
-        <v>2.63</v>
+        <v>1.884956</v>
       </c>
       <c r="BM36" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.530516</v>
       </c>
       <c r="BN36" s="28" t="n"/>
       <c r="BO36" s="28" t="n"/>
@@ -11673,22 +11673,22 @@
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>f92bfe3dd5f9459b</t>
+          <t>aae9e4147e25448f</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:00.757019Z</t>
+          <t>2026-08-07T18:31:15.157040Z</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-09T00:00:00Z</t>
+          <t>2026-08-08T18:00:00Z</t>
         </is>
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>73525</t>
+          <t>74165</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
-          <t>MIBR</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="G37" s="24" t="inlineStr">
         <is>
-          <t>Leviatán Esports</t>
+          <t>Eternal Fire</t>
         </is>
       </c>
       <c r="H37" s="24" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I37" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J37" s="25" t="n"/>
@@ -11723,23 +11723,23 @@
         </is>
       </c>
       <c r="L37" s="26" t="n">
-        <v>-150</v>
+        <v>163</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.63</v>
       </c>
       <c r="N37" s="28" t="n">
-        <v>0.6</v>
+        <v>0.380228</v>
       </c>
       <c r="O37" s="28" t="n">
-        <v>0.700273</v>
+        <v>0.698711</v>
       </c>
       <c r="P37" s="28" t="n"/>
       <c r="Q37" s="28" t="n">
-        <v>0.100273</v>
+        <v>0.318483</v>
       </c>
       <c r="R37" s="26" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="S37" s="29" t="n">
         <v>2</v>
@@ -11765,7 +11765,7 @@
       <c r="AD37" s="24" t="n"/>
       <c r="AE37" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-valorant-lev-mibr-2026-08-09).</t>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-valorant-ef-jl-2026-08-08).</t>
         </is>
       </c>
       <c r="AF37" s="31" t="inlineStr">
@@ -11783,7 +11783,7 @@
       <c r="AJ37" s="31" t="n"/>
       <c r="AK37" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL37" s="26" t="n">
@@ -11791,47 +11791,47 @@
       </c>
       <c r="AM37" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN37" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO37" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP37" s="24" t="inlineStr">
         <is>
-          <t>MIBR</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AQ37" s="24" t="inlineStr">
         <is>
-          <t>MIBR</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AR37" s="24" t="inlineStr">
         <is>
-          <t>MIBR</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AS37" s="24" t="inlineStr">
         <is>
-          <t>Leviatán Esports</t>
+          <t>Eternal Fire</t>
         </is>
       </c>
       <c r="AT37" s="24" t="inlineStr">
         <is>
-          <t>Leviatán Esports</t>
+          <t>Eternal Fire</t>
         </is>
       </c>
       <c r="AU37" s="24" t="inlineStr">
         <is>
-          <t>Leviatán Esports</t>
+          <t>Eternal Fire</t>
         </is>
       </c>
       <c r="AV37" s="24" t="n"/>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="BA37" s="24" t="inlineStr">
         <is>
-          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
         </is>
       </c>
       <c r="BB37" s="24" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="BD37" s="24" t="inlineStr">
         <is>
-          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
         </is>
       </c>
       <c r="BE37" s="24" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="BH37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:00.754763Z</t>
+          <t>2026-08-07T18:31:13.626555Z</t>
         </is>
       </c>
       <c r="BI37" s="24" t="inlineStr">
@@ -11894,13 +11894,13 @@
       </c>
       <c r="BJ37" s="25" t="n"/>
       <c r="BK37" s="26" t="n">
-        <v>-150</v>
+        <v>163</v>
       </c>
       <c r="BL37" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.63</v>
       </c>
       <c r="BM37" s="28" t="n">
-        <v>0.6</v>
+        <v>0.380228</v>
       </c>
       <c r="BN37" s="28" t="n"/>
       <c r="BO37" s="28" t="n"/>
@@ -11939,6 +11939,275 @@
         </is>
       </c>
     </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>2504e73adc4c404a</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:15.157040Z</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>73525</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>Leviatán Esports</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N38" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O38" s="28" t="n">
+        <v>0.700072</v>
+      </c>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n">
+        <v>0.100072</v>
+      </c>
+      <c r="R38" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="S38" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T38" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U38" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="n"/>
+      <c r="W38" s="26" t="n"/>
+      <c r="X38" s="26" t="n"/>
+      <c r="Y38" s="25" t="n"/>
+      <c r="Z38" s="26" t="n"/>
+      <c r="AA38" s="28" t="n"/>
+      <c r="AB38" s="28" t="n"/>
+      <c r="AC38" s="30" t="n"/>
+      <c r="AD38" s="24" t="n"/>
+      <c r="AE38" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-valorant-lev-mibr-2026-08-09).</t>
+        </is>
+      </c>
+      <c r="AF38" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG38" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH38" s="24" t="n"/>
+      <c r="AI38" s="31" t="n"/>
+      <c r="AJ38" s="31" t="n"/>
+      <c r="AK38" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM38" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN38" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO38" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP38" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="AQ38" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="AR38" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="AS38" s="24" t="inlineStr">
+        <is>
+          <t>Leviatán Esports</t>
+        </is>
+      </c>
+      <c r="AT38" s="24" t="inlineStr">
+        <is>
+          <t>Leviatán Esports</t>
+        </is>
+      </c>
+      <c r="AU38" s="24" t="inlineStr">
+        <is>
+          <t>Leviatán Esports</t>
+        </is>
+      </c>
+      <c r="AV38" s="24" t="n"/>
+      <c r="AW38" s="24" t="n"/>
+      <c r="AX38" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY38" s="24" t="n"/>
+      <c r="AZ38" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA38" s="24" t="inlineStr">
+        <is>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
+        </is>
+      </c>
+      <c r="BB38" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC38" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD38" s="24" t="inlineStr">
+        <is>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
+        </is>
+      </c>
+      <c r="BE38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG38" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:15.156257Z</t>
+        </is>
+      </c>
+      <c r="BI38" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ38" s="25" t="n"/>
+      <c r="BK38" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL38" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM38" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN38" s="28" t="n"/>
+      <c r="BO38" s="28" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
+      <c r="BR38" s="28" t="n"/>
+      <c r="BS38" s="28" t="n"/>
+      <c r="BT38" s="28" t="n"/>
+      <c r="BU38" s="25" t="n"/>
+      <c r="BV38" s="29" t="n"/>
+      <c r="BW38" s="24" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
+      <c r="BZ38" s="24" t="n"/>
+      <c r="CA38" s="31" t="n"/>
+      <c r="CB38" s="24" t="n"/>
+      <c r="CC38" s="24" t="n"/>
+      <c r="CD38" s="24" t="n"/>
+      <c r="CE38" s="24" t="n"/>
+      <c r="CF38" s="24" t="n"/>
+      <c r="CG38" s="24" t="n"/>
+      <c r="CH38" s="24" t="n"/>
+      <c r="CI38" s="24" t="n"/>
+      <c r="CJ38" s="24" t="n"/>
+      <c r="CK38" s="24" t="n"/>
+      <c r="CL38" s="24" t="n"/>
+      <c r="CM38" s="24" t="n"/>
+      <c r="CN38" s="24" t="n"/>
+      <c r="CO38" s="24" t="n"/>
+      <c r="CP38" s="24" t="n"/>
+      <c r="CQ38" s="24" t="n"/>
+      <c r="CR38" s="24" t="n"/>
+      <c r="CS38" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
